--- a/REFERENCE.xlsx
+++ b/REFERENCE.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2455" uniqueCount="1617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2459" uniqueCount="1621">
   <si>
     <t xml:space="preserve">MATERIAL NAME</t>
   </si>
@@ -2514,6 +2514,12 @@
     <t xml:space="preserve">C159</t>
   </si>
   <si>
+    <t xml:space="preserve">BLACK FOREST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C160</t>
+  </si>
+  <si>
     <t xml:space="preserve">RAL COLOUR NAME</t>
   </si>
   <si>
@@ -3148,6 +3154,12 @@
   </si>
   <si>
     <t xml:space="preserve">R204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAL 1019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R205</t>
   </si>
   <si>
     <t xml:space="preserve">TEAKWOOD</t>
@@ -6738,178 +6750,178 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="38" t="s">
-        <v>1497</v>
+        <v>1501</v>
       </c>
       <c r="B1" s="38" t="s">
-        <v>1498</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="39" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>1499</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="39" t="s">
-        <v>1500</v>
+        <v>1504</v>
       </c>
       <c r="B3" s="40" t="s">
-        <v>1501</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="39" t="s">
-        <v>1502</v>
+        <v>1506</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>1503</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="39" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>1504</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="39" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>1506</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="39" t="s">
-        <v>1507</v>
+        <v>1511</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>1508</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="39" t="s">
-        <v>1509</v>
+        <v>1513</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>1510</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="39" t="s">
-        <v>1238</v>
+        <v>1242</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>1271</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="39" t="s">
-        <v>1511</v>
+        <v>1515</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="39" t="s">
-        <v>1512</v>
+        <v>1516</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>1513</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="39" t="s">
-        <v>1514</v>
+        <v>1518</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="39" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>1517</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="39" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="39" t="s">
-        <v>1518</v>
+        <v>1522</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>1519</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="39" t="s">
-        <v>1520</v>
+        <v>1524</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="39" t="s">
-        <v>1246</v>
+        <v>1250</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>1522</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="39" t="s">
-        <v>1523</v>
+        <v>1527</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>1524</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="39" t="s">
-        <v>1525</v>
+        <v>1529</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>1526</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="39" t="s">
-        <v>1527</v>
+        <v>1531</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>1528</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="39" t="s">
-        <v>1529</v>
+        <v>1533</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>1530</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="39" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="B22" s="40" t="s">
-        <v>1531</v>
+        <v>1535</v>
       </c>
     </row>
   </sheetData>
@@ -6941,99 +6953,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="41" t="s">
-        <v>1532</v>
+        <v>1536</v>
       </c>
       <c r="C1" s="41" t="s">
-        <v>1533</v>
+        <v>1537</v>
       </c>
       <c r="D1" s="41" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
       <c r="E1" s="41" t="s">
-        <v>1535</v>
+        <v>1539</v>
       </c>
       <c r="F1" s="41" t="s">
-        <v>1536</v>
+        <v>1540</v>
       </c>
       <c r="G1" s="41" t="s">
-        <v>1537</v>
+        <v>1541</v>
       </c>
       <c r="H1" s="41" t="s">
-        <v>1538</v>
+        <v>1542</v>
       </c>
       <c r="I1" s="41" t="s">
-        <v>1539</v>
+        <v>1543</v>
       </c>
       <c r="J1" s="41" t="s">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="K1" s="41" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="L1" s="41" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="M1" s="41" t="s">
-        <v>1543</v>
+        <v>1547</v>
       </c>
       <c r="N1" s="41" t="s">
-        <v>1544</v>
+        <v>1548</v>
       </c>
       <c r="O1" s="41" t="s">
-        <v>1545</v>
+        <v>1549</v>
       </c>
       <c r="P1" s="41" t="s">
-        <v>1546</v>
+        <v>1550</v>
       </c>
       <c r="Q1" s="41" t="s">
-        <v>1547</v>
+        <v>1551</v>
       </c>
       <c r="R1" s="41" t="s">
-        <v>1548</v>
+        <v>1552</v>
       </c>
       <c r="S1" s="41" t="s">
-        <v>1549</v>
+        <v>1553</v>
       </c>
       <c r="T1" s="41" t="s">
-        <v>1550</v>
+        <v>1554</v>
       </c>
       <c r="U1" s="41" t="s">
-        <v>1551</v>
+        <v>1555</v>
       </c>
       <c r="V1" s="41" t="s">
-        <v>1552</v>
+        <v>1556</v>
       </c>
       <c r="W1" s="41" t="s">
-        <v>1553</v>
+        <v>1557</v>
       </c>
       <c r="X1" s="41" t="s">
-        <v>1554</v>
+        <v>1558</v>
       </c>
       <c r="Y1" s="41" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="Z1" s="41" t="s">
-        <v>1556</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="35" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>1379</v>
+        <v>1383</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="E2" s="35" t="s">
         <v>160</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="G2" s="36"/>
       <c r="H2" s="36"/>
@@ -7061,10 +7073,10 @@
         <v>143</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>1558</v>
+        <v>1562</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>1559</v>
+        <v>1563</v>
       </c>
       <c r="D3" s="35"/>
       <c r="E3" s="35"/>
@@ -7095,64 +7107,64 @@
         <v>93</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>1382</v>
+        <v>1386</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1383</v>
+        <v>1387</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1384</v>
+        <v>1388</v>
       </c>
       <c r="G4" s="36" t="s">
-        <v>1385</v>
+        <v>1389</v>
       </c>
       <c r="H4" s="36" t="s">
-        <v>1386</v>
+        <v>1390</v>
       </c>
       <c r="I4" s="36" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>1388</v>
+        <v>1392</v>
       </c>
       <c r="K4" s="36" t="s">
-        <v>1389</v>
+        <v>1393</v>
       </c>
       <c r="L4" s="36" t="s">
-        <v>1390</v>
+        <v>1394</v>
       </c>
       <c r="M4" s="36" t="s">
-        <v>1391</v>
+        <v>1395</v>
       </c>
       <c r="N4" s="36" t="s">
-        <v>1392</v>
+        <v>1396</v>
       </c>
       <c r="O4" s="36" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="P4" s="36" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="Q4" s="36" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="R4" s="36" t="s">
-        <v>1396</v>
+        <v>1400</v>
       </c>
       <c r="S4" s="36" t="s">
-        <v>1397</v>
+        <v>1401</v>
       </c>
       <c r="T4" s="36" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
       <c r="U4" s="43" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="V4" s="36"/>
       <c r="W4" s="42"/>
@@ -7165,22 +7177,22 @@
         <v>136</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>1400</v>
+        <v>1404</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>1402</v>
+        <v>1406</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1404</v>
+        <v>1408</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
       <c r="H5" s="36"/>
       <c r="I5" s="36"/>
@@ -7207,19 +7219,19 @@
         <v>23</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>1560</v>
+        <v>1564</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
@@ -7247,13 +7259,13 @@
         <v>85</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="E7" s="35"/>
       <c r="F7" s="35"/>
@@ -7280,16 +7292,16 @@
     </row>
     <row r="8" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="35" t="s">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="E8" s="35" t="s">
         <v>245</v>
@@ -7321,13 +7333,13 @@
         <v>28</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>1414</v>
+        <v>1418</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
       <c r="E9" s="35"/>
       <c r="F9" s="35"/>
@@ -7354,25 +7366,25 @@
     </row>
     <row r="10" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="35" t="s">
-        <v>1272</v>
+        <v>1276</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1418</v>
+        <v>1422</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1419</v>
+        <v>1423</v>
       </c>
       <c r="G10" s="36" t="s">
-        <v>1420</v>
+        <v>1424</v>
       </c>
       <c r="H10" s="36"/>
       <c r="I10" s="36"/>
@@ -7399,10 +7411,10 @@
         <v>111</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>1421</v>
+        <v>1425</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
@@ -7430,28 +7442,28 @@
     </row>
     <row r="12" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="37" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>1425</v>
+        <v>1429</v>
       </c>
       <c r="G12" s="36" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="H12" s="36" t="s">
-        <v>1426</v>
+        <v>1430</v>
       </c>
       <c r="I12" s="36"/>
       <c r="J12" s="36"/>
@@ -7477,10 +7489,10 @@
         <v>42</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="37"/>
@@ -7511,16 +7523,16 @@
         <v>97</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="F14" s="37"/>
       <c r="G14" s="36"/>
@@ -7549,96 +7561,96 @@
         <v>6</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>1566</v>
+        <v>1570</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>1568</v>
+        <v>1572</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>1569</v>
+        <v>1573</v>
       </c>
       <c r="G15" s="36" t="s">
-        <v>1570</v>
+        <v>1574</v>
       </c>
       <c r="H15" s="36" t="s">
-        <v>1571</v>
+        <v>1575</v>
       </c>
       <c r="I15" s="36" t="s">
-        <v>1572</v>
+        <v>1576</v>
       </c>
       <c r="J15" s="36" t="s">
-        <v>1573</v>
+        <v>1577</v>
       </c>
       <c r="K15" s="36" t="s">
-        <v>1404</v>
+        <v>1408</v>
       </c>
       <c r="L15" s="36" t="s">
-        <v>1574</v>
+        <v>1578</v>
       </c>
       <c r="M15" s="36" t="s">
-        <v>1575</v>
+        <v>1579</v>
       </c>
       <c r="N15" s="36" t="s">
-        <v>1576</v>
+        <v>1580</v>
       </c>
       <c r="O15" s="36" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
       <c r="P15" s="36" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="Q15" s="36" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="R15" s="36" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="S15" s="36" t="s">
-        <v>1580</v>
+        <v>1584</v>
       </c>
       <c r="T15" s="36" t="s">
-        <v>1581</v>
+        <v>1585</v>
       </c>
       <c r="U15" s="36" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="V15" s="36" t="s">
-        <v>1583</v>
+        <v>1587</v>
       </c>
       <c r="W15" s="36" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="X15" s="36" t="s">
-        <v>1584</v>
+        <v>1588</v>
       </c>
       <c r="Y15" s="36" t="s">
-        <v>1585</v>
+        <v>1589</v>
       </c>
       <c r="Z15" s="44" t="s">
-        <v>1586</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="37" t="s">
-        <v>1431</v>
+        <v>1435</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>1432</v>
+        <v>1436</v>
       </c>
       <c r="C16" s="37" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="F16" s="37"/>
       <c r="G16" s="36"/>
@@ -7664,13 +7676,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="37" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="37"/>
@@ -7701,7 +7713,7 @@
         <v>125</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>1435</v>
+        <v>1439</v>
       </c>
       <c r="C18" s="37"/>
       <c r="D18" s="37"/>
@@ -7730,10 +7742,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="37" t="s">
-        <v>1436</v>
+        <v>1440</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>1437</v>
+        <v>1441</v>
       </c>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
@@ -7765,7 +7777,7 @@
         <v>182</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="37"/>
@@ -7794,10 +7806,10 @@
     </row>
     <row r="21" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="37" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="37"/>
@@ -7829,28 +7841,28 @@
         <v>74</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>1587</v>
+        <v>1591</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>1588</v>
+        <v>1592</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>1589</v>
+        <v>1593</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>1590</v>
+        <v>1594</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>1524</v>
+        <v>1528</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>1591</v>
+        <v>1595</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
       <c r="M22" s="36"/>
       <c r="N22" s="36"/>
@@ -7869,10 +7881,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="37" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="C23" s="37"/>
       <c r="D23" s="37"/>
@@ -7904,28 +7916,28 @@
         <v>99</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>1447</v>
+        <v>1451</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>1448</v>
+        <v>1452</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>1450</v>
+        <v>1454</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>1451</v>
+        <v>1455</v>
       </c>
       <c r="G24" s="36" t="s">
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="H24" s="36" t="s">
-        <v>1453</v>
+        <v>1457</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>1454</v>
+        <v>1458</v>
       </c>
       <c r="J24" s="36"/>
       <c r="K24" s="36"/>
@@ -7950,7 +7962,7 @@
         <v>262</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="C25" s="37"/>
       <c r="D25" s="37"/>
@@ -7982,10 +7994,10 @@
         <v>46</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>1455</v>
+        <v>1459</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>1456</v>
+        <v>1460</v>
       </c>
       <c r="D26" s="37"/>
       <c r="E26" s="37"/>
@@ -8013,10 +8025,10 @@
     </row>
     <row r="27" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="37" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="C27" s="37"/>
       <c r="D27" s="37"/>
@@ -8048,7 +8060,7 @@
         <v>202</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>1458</v>
+        <v>1462</v>
       </c>
       <c r="C28" s="37"/>
       <c r="D28" s="37"/>
@@ -8080,7 +8092,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>1459</v>
+        <v>1463</v>
       </c>
       <c r="C29" s="37"/>
       <c r="D29" s="37"/>
@@ -8112,7 +8124,7 @@
         <v>140</v>
       </c>
       <c r="B30" s="37" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="C30" s="37"/>
       <c r="D30" s="37"/>
@@ -8144,76 +8156,76 @@
         <v>8</v>
       </c>
       <c r="B31" s="36" t="s">
+        <v>1591</v>
+      </c>
+      <c r="C31" s="36" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D31" s="36" t="s">
+        <v>1592</v>
+      </c>
+      <c r="E31" s="36" t="s">
+        <v>1598</v>
+      </c>
+      <c r="F31" s="37" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G31" s="37" t="s">
+        <v>1528</v>
+      </c>
+      <c r="H31" s="37" t="s">
+        <v>1595</v>
+      </c>
+      <c r="I31" s="37" t="s">
+        <v>1599</v>
+      </c>
+      <c r="J31" s="37" t="s">
+        <v>1600</v>
+      </c>
+      <c r="K31" s="37" t="s">
+        <v>1601</v>
+      </c>
+      <c r="L31" s="37" t="s">
+        <v>1602</v>
+      </c>
+      <c r="M31" s="37" t="s">
+        <v>1603</v>
+      </c>
+      <c r="N31" s="36" t="s">
+        <v>1604</v>
+      </c>
+      <c r="O31" s="37" t="s">
+        <v>1605</v>
+      </c>
+      <c r="P31" s="36" t="s">
+        <v>1416</v>
+      </c>
+      <c r="Q31" s="36" t="s">
+        <v>1606</v>
+      </c>
+      <c r="R31" s="36" t="s">
+        <v>1607</v>
+      </c>
+      <c r="S31" s="36" t="s">
+        <v>1583</v>
+      </c>
+      <c r="T31" s="36" t="s">
+        <v>1608</v>
+      </c>
+      <c r="U31" s="36" t="s">
         <v>1587</v>
       </c>
-      <c r="C31" s="36" t="s">
-        <v>1593</v>
-      </c>
-      <c r="D31" s="36" t="s">
-        <v>1588</v>
-      </c>
-      <c r="E31" s="36" t="s">
-        <v>1594</v>
-      </c>
-      <c r="F31" s="37" t="s">
-        <v>1590</v>
-      </c>
-      <c r="G31" s="37" t="s">
-        <v>1524</v>
-      </c>
-      <c r="H31" s="37" t="s">
-        <v>1591</v>
-      </c>
-      <c r="I31" s="37" t="s">
-        <v>1595</v>
-      </c>
-      <c r="J31" s="37" t="s">
-        <v>1596</v>
-      </c>
-      <c r="K31" s="37" t="s">
-        <v>1597</v>
-      </c>
-      <c r="L31" s="37" t="s">
-        <v>1598</v>
-      </c>
-      <c r="M31" s="37" t="s">
-        <v>1599</v>
-      </c>
-      <c r="N31" s="36" t="s">
-        <v>1600</v>
-      </c>
-      <c r="O31" s="37" t="s">
-        <v>1601</v>
-      </c>
-      <c r="P31" s="36" t="s">
+      <c r="V31" s="36" t="s">
         <v>1412</v>
       </c>
-      <c r="Q31" s="36" t="s">
-        <v>1602</v>
-      </c>
-      <c r="R31" s="36" t="s">
-        <v>1603</v>
-      </c>
-      <c r="S31" s="36" t="s">
-        <v>1579</v>
-      </c>
-      <c r="T31" s="36" t="s">
-        <v>1604</v>
-      </c>
-      <c r="U31" s="36" t="s">
-        <v>1583</v>
-      </c>
-      <c r="V31" s="36" t="s">
-        <v>1408</v>
-      </c>
       <c r="W31" s="36" t="s">
-        <v>1605</v>
+        <v>1609</v>
       </c>
       <c r="X31" s="36" t="s">
-        <v>1606</v>
+        <v>1610</v>
       </c>
       <c r="Y31" s="36" t="s">
-        <v>1607</v>
+        <v>1611</v>
       </c>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
@@ -8263,79 +8275,79 @@
         <v>3</v>
       </c>
       <c r="B33" s="36" t="s">
+        <v>1591</v>
+      </c>
+      <c r="C33" s="36" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D33" s="36" t="s">
+        <v>1592</v>
+      </c>
+      <c r="E33" s="36" t="s">
+        <v>1593</v>
+      </c>
+      <c r="F33" s="37" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G33" s="37" t="s">
+        <v>1528</v>
+      </c>
+      <c r="H33" s="37" t="s">
+        <v>1595</v>
+      </c>
+      <c r="I33" s="37" t="s">
+        <v>1596</v>
+      </c>
+      <c r="J33" s="36" t="s">
+        <v>1612</v>
+      </c>
+      <c r="K33" s="36" t="s">
+        <v>1444</v>
+      </c>
+      <c r="L33" s="36" t="s">
+        <v>1445</v>
+      </c>
+      <c r="M33" s="36" t="s">
+        <v>1446</v>
+      </c>
+      <c r="N33" s="36" t="s">
+        <v>1447</v>
+      </c>
+      <c r="O33" s="36" t="s">
+        <v>1448</v>
+      </c>
+      <c r="P33" s="36" t="s">
+        <v>1449</v>
+      </c>
+      <c r="Q33" s="37" t="s">
+        <v>1423</v>
+      </c>
+      <c r="R33" s="37" t="s">
+        <v>1237</v>
+      </c>
+      <c r="S33" s="37" t="s">
+        <v>1613</v>
+      </c>
+      <c r="T33" s="36" t="s">
+        <v>1614</v>
+      </c>
+      <c r="U33" s="36" t="s">
+        <v>1252</v>
+      </c>
+      <c r="V33" s="36" t="s">
+        <v>1615</v>
+      </c>
+      <c r="W33" s="36" t="s">
+        <v>1616</v>
+      </c>
+      <c r="X33" s="36" t="s">
+        <v>1617</v>
+      </c>
+      <c r="Y33" s="36" t="s">
         <v>1587</v>
       </c>
-      <c r="C33" s="36" t="s">
-        <v>1221</v>
-      </c>
-      <c r="D33" s="36" t="s">
-        <v>1588</v>
-      </c>
-      <c r="E33" s="36" t="s">
-        <v>1589</v>
-      </c>
-      <c r="F33" s="37" t="s">
-        <v>1590</v>
-      </c>
-      <c r="G33" s="37" t="s">
-        <v>1524</v>
-      </c>
-      <c r="H33" s="37" t="s">
-        <v>1591</v>
-      </c>
-      <c r="I33" s="37" t="s">
-        <v>1592</v>
-      </c>
-      <c r="J33" s="36" t="s">
-        <v>1608</v>
-      </c>
-      <c r="K33" s="36" t="s">
-        <v>1440</v>
-      </c>
-      <c r="L33" s="36" t="s">
-        <v>1441</v>
-      </c>
-      <c r="M33" s="36" t="s">
-        <v>1442</v>
-      </c>
-      <c r="N33" s="36" t="s">
-        <v>1443</v>
-      </c>
-      <c r="O33" s="36" t="s">
-        <v>1444</v>
-      </c>
-      <c r="P33" s="36" t="s">
-        <v>1445</v>
-      </c>
-      <c r="Q33" s="37" t="s">
-        <v>1419</v>
-      </c>
-      <c r="R33" s="37" t="s">
-        <v>1233</v>
-      </c>
-      <c r="S33" s="37" t="s">
-        <v>1609</v>
-      </c>
-      <c r="T33" s="36" t="s">
-        <v>1610</v>
-      </c>
-      <c r="U33" s="36" t="s">
-        <v>1248</v>
-      </c>
-      <c r="V33" s="36" t="s">
-        <v>1611</v>
-      </c>
-      <c r="W33" s="36" t="s">
-        <v>1612</v>
-      </c>
-      <c r="X33" s="36" t="s">
-        <v>1613</v>
-      </c>
-      <c r="Y33" s="36" t="s">
-        <v>1583</v>
-      </c>
       <c r="Z33" s="36" t="s">
-        <v>1614</v>
+        <v>1618</v>
       </c>
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
@@ -8350,10 +8362,10 @@
     </row>
     <row r="34" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="37" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>1460</v>
+        <v>1464</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -8385,7 +8397,7 @@
         <v>282</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="C35" s="37"/>
       <c r="D35" s="37"/>
@@ -8417,7 +8429,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="37" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="C36" s="37"/>
       <c r="D36" s="37"/>
@@ -8446,10 +8458,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="37" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="B37" s="37" t="s">
-        <v>1461</v>
+        <v>1465</v>
       </c>
       <c r="C37" s="37"/>
       <c r="D37" s="37"/>
@@ -8481,16 +8493,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>1463</v>
+        <v>1467</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F38" s="37"/>
       <c r="G38" s="36"/>
@@ -8519,22 +8531,22 @@
         <v>95</v>
       </c>
       <c r="B39" s="37" t="s">
-        <v>1466</v>
+        <v>1470</v>
       </c>
       <c r="C39" s="37" t="s">
-        <v>1437</v>
+        <v>1441</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>1468</v>
+        <v>1472</v>
       </c>
       <c r="G39" s="36" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
       <c r="H39" s="36"/>
       <c r="I39" s="36"/>
@@ -8558,25 +8570,25 @@
     </row>
     <row r="40" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="37" t="s">
-        <v>1341</v>
+        <v>1345</v>
       </c>
       <c r="B40" s="37" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>1471</v>
+        <v>1475</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>1472</v>
+        <v>1476</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
       <c r="G40" s="36" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="H40" s="36"/>
       <c r="I40" s="36"/>
@@ -8600,10 +8612,10 @@
     </row>
     <row r="41" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="37" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="B41" s="37" t="s">
-        <v>1474</v>
+        <v>1478</v>
       </c>
       <c r="C41" s="37"/>
       <c r="D41" s="37"/>
@@ -8632,10 +8644,10 @@
     </row>
     <row r="42" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="37" t="s">
-        <v>1345</v>
+        <v>1349</v>
       </c>
       <c r="B42" s="37" t="s">
-        <v>1475</v>
+        <v>1479</v>
       </c>
       <c r="C42" s="37"/>
       <c r="D42" s="37"/>
@@ -8667,13 +8679,13 @@
         <v>123</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>1476</v>
+        <v>1480</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="D43" s="37" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="E43" s="37"/>
       <c r="F43" s="37"/>
@@ -8703,7 +8715,7 @@
         <v>228</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>1477</v>
+        <v>1481</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -8732,13 +8744,13 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="37" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="B45" s="37" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="C45" s="37" t="s">
-        <v>1479</v>
+        <v>1483</v>
       </c>
       <c r="D45" s="37"/>
       <c r="E45" s="37"/>
@@ -8769,58 +8781,58 @@
         <v>456</v>
       </c>
       <c r="B46" s="37" t="s">
-        <v>1480</v>
+        <v>1484</v>
       </c>
       <c r="C46" s="37" t="s">
-        <v>1481</v>
+        <v>1485</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="E46" s="37" t="s">
-        <v>1482</v>
+        <v>1486</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>1483</v>
+        <v>1487</v>
       </c>
       <c r="G46" s="36" t="s">
-        <v>1484</v>
+        <v>1488</v>
       </c>
       <c r="H46" s="36" t="s">
-        <v>1485</v>
+        <v>1489</v>
       </c>
       <c r="I46" s="36" t="s">
-        <v>1486</v>
+        <v>1490</v>
       </c>
       <c r="J46" s="36" t="s">
-        <v>1487</v>
+        <v>1491</v>
       </c>
       <c r="K46" s="36" t="s">
-        <v>1488</v>
+        <v>1492</v>
       </c>
       <c r="L46" s="36" t="s">
-        <v>1489</v>
+        <v>1493</v>
       </c>
       <c r="M46" s="36" t="s">
-        <v>1490</v>
+        <v>1494</v>
       </c>
       <c r="N46" s="36" t="s">
-        <v>1491</v>
+        <v>1495</v>
       </c>
       <c r="O46" s="36" t="s">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="P46" s="36" t="s">
-        <v>1493</v>
+        <v>1497</v>
       </c>
       <c r="Q46" s="36" t="s">
-        <v>1494</v>
+        <v>1498</v>
       </c>
       <c r="R46" s="36" t="s">
-        <v>1495</v>
+        <v>1499</v>
       </c>
       <c r="S46" s="36" t="s">
-        <v>1496</v>
+        <v>1500</v>
       </c>
       <c r="T46" s="36"/>
       <c r="U46" s="36"/>
@@ -8855,10 +8867,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="46" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="B1" s="46" t="s">
-        <v>1616</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10920,7 +10932,7 @@
     <tabColor rgb="FF2F5496"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B160"/>
+  <dimension ref="A1:B161"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
@@ -12205,6 +12217,14 @@
       </c>
       <c r="B160" s="10" t="s">
         <v>826</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="B161" s="13" t="s">
+        <v>828</v>
       </c>
     </row>
   </sheetData>
@@ -12224,7 +12244,7 @@
     <tabColor rgb="FF2F5496"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B106"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
@@ -12233,850 +12253,858 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="14" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="14" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="14" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="14" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="14" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="14" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="14" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="14" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="14" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="14" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="14" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="14" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="14" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="14" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="14" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="16" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="14" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="14" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="14" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="14" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="14" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="14" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="14" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="14" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B67" s="14" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="14" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="14" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="B69" s="14" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="14" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="16" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="14" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="14" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="16" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="14" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="14" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="14" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="B77" s="14" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="14" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="16" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="B79" s="14" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="14" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="14" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="14" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="B82" s="14" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="16" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="B83" s="14" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="14" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="B84" s="14" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="14" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="B85" s="14" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="14" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="B86" s="14" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="14" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="B87" s="14" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="14" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="14" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="B89" s="14" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="14" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="B90" s="14" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="14" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="16" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="B92" s="14" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="14" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="B93" s="14" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="14" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="B94" s="14" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="17" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="B95" s="14" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="16" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="B96" s="18" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="14" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B97" s="18" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="14" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="B98" s="18" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="14" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="B99" s="18" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="16" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="B100" s="18" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="14" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="B101" s="18" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="14" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B102" s="18" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="16" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="B103" s="18" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="14" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="B104" s="18" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="14" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="B105" s="18" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="19" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="B106" s="19" t="s">
-        <v>1038</v>
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="19" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B107" s="19" t="s">
+        <v>1042</v>
       </c>
     </row>
   </sheetData>
@@ -13151,7 +13179,7 @@
         <v>93</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="F1" s="20" t="s">
         <v>43</v>
@@ -13166,7 +13194,7 @@
         <v>136</v>
       </c>
       <c r="J1" s="20" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="K1" s="20" t="s">
         <v>28</v>
@@ -13175,19 +13203,19 @@
         <v>111</v>
       </c>
       <c r="M1" s="20" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="N1" s="20" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="O1" s="20" t="s">
         <v>143</v>
       </c>
       <c r="P1" s="20" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="Q1" s="20" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="R1" s="21" t="s">
         <v>350</v>
@@ -13199,10 +13227,10 @@
         <v>97</v>
       </c>
       <c r="U1" s="21" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="V1" s="21" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="W1" s="21" t="s">
         <v>99</v>
@@ -13211,13 +13239,13 @@
         <v>128</v>
       </c>
       <c r="Y1" s="21" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="Z1" s="21" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="AA1" s="21" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="AB1" s="21" t="s">
         <v>182</v>
@@ -13232,7 +13260,7 @@
         <v>228</v>
       </c>
       <c r="AF1" s="21" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="AG1" s="21" t="s">
         <v>85</v>
@@ -13261,570 +13289,570 @@
     </row>
     <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="H2" s="10" t="s">
+        <v>1062</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>1064</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>1065</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>1066</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>1067</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>1068</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>1068</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>1069</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>1070</v>
+      </c>
+      <c r="R2" s="10" t="s">
+        <v>1059</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>1058</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="V2" s="10" t="s">
         <v>1059</v>
       </c>
-      <c r="J2" s="10" t="s">
-        <v>1060</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>1061</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>1062</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>1063</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>1064</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>1064</v>
-      </c>
-      <c r="P2" s="10" t="s">
-        <v>1065</v>
-      </c>
-      <c r="Q2" s="10" t="s">
-        <v>1066</v>
-      </c>
-      <c r="R2" s="10" t="s">
-        <v>1055</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>1067</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>1068</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>1054</v>
-      </c>
-      <c r="V2" s="10" t="s">
-        <v>1055</v>
-      </c>
       <c r="W2" s="1" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>456</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="AB2" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="AD2" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="AE2" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="AG2" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="AN2" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="J3" s="10" t="s">
         <v>456</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="N3" s="10" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="O3" s="10" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="P3" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="Q3" s="10" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="R3" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="S3" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="U3" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="V3" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="Y3" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="Z3" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="AA3" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="AB3" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="AC3" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="AD3" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="AE3" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="AG3" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="AH3" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="AI3" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="AJ3" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="AK3" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="AL3" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="AM3" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="AN3" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>1096</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>1060</v>
+      </c>
+      <c r="I4" s="22" t="s">
+        <v>1102</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>1079</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>1096</v>
+      </c>
+      <c r="M4" s="10" t="s">
         <v>1092</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>1093</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>1094</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>1095</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>1096</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>1097</v>
-      </c>
-      <c r="G4" s="10" t="s">
+      <c r="N4" s="10" t="s">
+        <v>1059</v>
+      </c>
+      <c r="O4" s="10" t="s">
+        <v>1059</v>
+      </c>
+      <c r="P4" s="10" t="s">
         <v>1092</v>
       </c>
-      <c r="H4" s="10" t="s">
-        <v>1056</v>
-      </c>
-      <c r="I4" s="22" t="s">
-        <v>1098</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>1075</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>1052</v>
-      </c>
-      <c r="L4" s="10" t="s">
+      <c r="Q4" s="10" t="s">
+        <v>1059</v>
+      </c>
+      <c r="R4" s="10" t="s">
+        <v>1103</v>
+      </c>
+      <c r="S4" s="10" t="s">
         <v>1092</v>
       </c>
-      <c r="M4" s="10" t="s">
-        <v>1088</v>
-      </c>
-      <c r="N4" s="10" t="s">
-        <v>1055</v>
-      </c>
-      <c r="O4" s="10" t="s">
-        <v>1055</v>
-      </c>
-      <c r="P4" s="10" t="s">
-        <v>1088</v>
-      </c>
-      <c r="Q4" s="10" t="s">
-        <v>1055</v>
-      </c>
-      <c r="R4" s="10" t="s">
-        <v>1099</v>
-      </c>
-      <c r="S4" s="10" t="s">
-        <v>1088</v>
-      </c>
       <c r="T4" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="U4" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="V4" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="Y4" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="Z4" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="AA4" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="AB4" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="AC4" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="AD4" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="AE4" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="AF4" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="AG4" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="AH4" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="AI4" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="AJ4" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="AK4" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="AL4" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="AM4" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="AN4" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="H5" s="10" t="s">
         <v>456</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="O5" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="Q5" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="S5" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="T5" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="U5" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="Y5" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="Z5" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="AA5" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="AB5" s="10"/>
       <c r="AC5" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="AD5" s="10"/>
       <c r="AF5" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="AH5" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="AK5" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="AL5" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="AM5" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="O6" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="P6" s="22"/>
       <c r="Q6" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="T6" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="AF6" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
@@ -13832,44 +13860,44 @@
       <c r="P7" s="22"/>
       <c r="Q7" s="22"/>
       <c r="W7" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="I8" s="22"/>
       <c r="J8" s="22"/>
       <c r="K8" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
@@ -13877,44 +13905,44 @@
       <c r="P8" s="22"/>
       <c r="Q8" s="22"/>
       <c r="W8" s="1" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="X8" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="I9" s="22"/>
       <c r="J9" s="22"/>
       <c r="K9" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="M9" s="22"/>
       <c r="N9" s="22"/>
@@ -13922,42 +13950,42 @@
       <c r="P9" s="22"/>
       <c r="Q9" s="22"/>
       <c r="W9" s="1" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="X9" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="E10" s="22"/>
       <c r="F10" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="I10" s="22"/>
       <c r="J10" s="22"/>
       <c r="K10" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="M10" s="22"/>
       <c r="N10" s="22"/>
@@ -13965,38 +13993,38 @@
       <c r="P10" s="22"/>
       <c r="Q10" s="22"/>
       <c r="W10" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="X10" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="E11" s="22"/>
       <c r="F11" s="22"/>
       <c r="G11" s="10" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="I11" s="22"/>
       <c r="J11" s="22"/>
       <c r="K11" s="22"/>
       <c r="L11" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="M11" s="22"/>
       <c r="N11" s="22"/>
@@ -14004,29 +14032,29 @@
       <c r="P11" s="22"/>
       <c r="Q11" s="22"/>
       <c r="W11" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
       <c r="E12" s="22"/>
       <c r="F12" s="22"/>
       <c r="G12" s="10" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="I12" s="22"/>
       <c r="J12" s="22"/>
@@ -14038,29 +14066,29 @@
       <c r="P12" s="22"/>
       <c r="Q12" s="22"/>
       <c r="W12" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="E13" s="22"/>
       <c r="F13" s="22"/>
       <c r="G13" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="I13" s="22"/>
       <c r="J13" s="22"/>
@@ -14074,24 +14102,24 @@
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="E14" s="22"/>
       <c r="F14" s="22"/>
       <c r="G14" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="I14" s="22"/>
       <c r="J14" s="22"/>
@@ -14105,24 +14133,24 @@
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="E15" s="22"/>
       <c r="F15" s="22"/>
       <c r="G15" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="I15" s="22"/>
       <c r="J15" s="22"/>
@@ -14136,20 +14164,20 @@
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
       <c r="F16" s="22"/>
       <c r="G16" s="22"/>
       <c r="H16" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="I16" s="22"/>
       <c r="J16" s="22"/>
@@ -14163,20 +14191,20 @@
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="D17" s="22"/>
       <c r="E17" s="22"/>
       <c r="F17" s="22"/>
       <c r="G17" s="22"/>
       <c r="H17" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="I17" s="22"/>
       <c r="J17" s="22"/>
@@ -14190,13 +14218,13 @@
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="D18" s="22"/>
       <c r="E18" s="22"/>
@@ -14215,13 +14243,13 @@
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="D19" s="22"/>
       <c r="E19" s="22"/>
@@ -14240,13 +14268,13 @@
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
       <c r="D20" s="22"/>
       <c r="E20" s="22"/>
@@ -14265,13 +14293,13 @@
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="D21" s="22"/>
       <c r="E21" s="22"/>
@@ -14290,13 +14318,13 @@
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="22"/>
@@ -14315,13 +14343,13 @@
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="D23" s="22"/>
       <c r="E23" s="22"/>
@@ -14340,13 +14368,13 @@
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="D24" s="22"/>
       <c r="E24" s="22"/>
@@ -14365,13 +14393,13 @@
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="D25" s="22"/>
       <c r="E25" s="22"/>
@@ -14390,13 +14418,13 @@
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B26" s="22" t="s">
         <v>1178</v>
       </c>
-      <c r="B26" s="22" t="s">
-        <v>1174</v>
-      </c>
       <c r="C26" s="10" t="s">
-        <v>1179</v>
+        <v>1183</v>
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="22"/>
@@ -14415,13 +14443,13 @@
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B27" s="22" t="s">
         <v>1180</v>
       </c>
-      <c r="B27" s="22" t="s">
-        <v>1176</v>
-      </c>
       <c r="C27" s="10" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="D27" s="22"/>
       <c r="E27" s="22"/>
@@ -14440,13 +14468,13 @@
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="D28" s="22"/>
       <c r="E28" s="22"/>
@@ -14465,13 +14493,13 @@
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>1179</v>
+        <v>1183</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="D29" s="22"/>
       <c r="E29" s="22"/>
@@ -14490,13 +14518,13 @@
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
       <c r="D30" s="22"/>
       <c r="E30" s="22"/>
@@ -14515,13 +14543,13 @@
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="D31" s="22"/>
       <c r="E31" s="22"/>
@@ -14540,13 +14568,13 @@
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="D32" s="22"/>
       <c r="E32" s="22"/>
@@ -14565,13 +14593,13 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="D33" s="22"/>
       <c r="E33" s="22"/>
@@ -14590,13 +14618,13 @@
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="B34" s="22" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="D34" s="22"/>
       <c r="E34" s="22"/>
@@ -14615,13 +14643,13 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B35" s="22" t="s">
         <v>1195</v>
       </c>
-      <c r="B35" s="22" t="s">
-        <v>1191</v>
-      </c>
       <c r="C35" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="D35" s="22"/>
       <c r="E35" s="22"/>
@@ -14640,13 +14668,13 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="D36" s="22"/>
       <c r="E36" s="22"/>
@@ -14665,10 +14693,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="C37" s="22"/>
       <c r="D37" s="22"/>
@@ -14688,10 +14716,10 @@
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>1198</v>
+        <v>1202</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="C38" s="22"/>
       <c r="D38" s="22"/>
@@ -14711,10 +14739,10 @@
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="C39" s="22"/>
       <c r="D39" s="22"/>
@@ -14734,7 +14762,7 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="B40" s="22"/>
       <c r="C40" s="22"/>
@@ -14755,7 +14783,7 @@
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="B41" s="22"/>
       <c r="C41" s="22"/>
@@ -14776,7 +14804,7 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
     </row>
   </sheetData>
@@ -14804,92 +14832,92 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="24" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>1209</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="24" t="s">
-        <v>1210</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14899,7 +14927,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
     </row>
   </sheetData>
@@ -14928,159 +14956,159 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1217</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>1228</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>1234</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>1237</v>
+        <v>1241</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>1238</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>1243</v>
+        <v>1247</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>1245</v>
+        <v>1249</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>1246</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
       <c r="B20" s="23"/>
     </row>
@@ -15112,31 +15140,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
       <c r="E1" s="26"/>
     </row>
     <row r="2" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="E2" s="28"/>
     </row>
@@ -15145,13 +15173,13 @@
         <v>143</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
       <c r="E3" s="28"/>
     </row>
@@ -15160,43 +15188,43 @@
         <v>93</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>1261</v>
+        <v>1265</v>
       </c>
       <c r="E4" s="28"/>
     </row>
     <row r="5" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1263</v>
+        <v>1267</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="E5" s="28"/>
     </row>
     <row r="6" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
       <c r="E6" s="28"/>
     </row>
@@ -15205,13 +15233,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1269</v>
+        <v>1273</v>
       </c>
       <c r="E7" s="28"/>
     </row>
@@ -15220,43 +15248,43 @@
         <v>28</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="E8" s="28"/>
     </row>
     <row r="9" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B9" s="27" t="s">
         <v>1271</v>
       </c>
-      <c r="B9" s="27" t="s">
-        <v>1267</v>
-      </c>
       <c r="C9" s="27" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="E9" s="28"/>
     </row>
     <row r="10" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>1272</v>
+        <v>1276</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="E10" s="28"/>
     </row>
@@ -15265,73 +15293,73 @@
         <v>111</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1273</v>
+        <v>1277</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1274</v>
+        <v>1278</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1275</v>
+        <v>1279</v>
       </c>
       <c r="E11" s="28"/>
     </row>
     <row r="12" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>1278</v>
+        <v>1282</v>
       </c>
       <c r="E12" s="28"/>
     </row>
     <row r="13" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1282</v>
+        <v>1286</v>
       </c>
       <c r="E13" s="28"/>
     </row>
     <row r="14" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
-        <v>1283</v>
+        <v>1287</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>1269</v>
+        <v>1273</v>
       </c>
       <c r="E14" s="28"/>
     </row>
     <row r="15" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1286</v>
+        <v>1290</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="E15" s="28"/>
     </row>
@@ -15340,13 +15368,13 @@
         <v>97</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="E16" s="28"/>
     </row>
@@ -15355,13 +15383,13 @@
         <v>6</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>1291</v>
+        <v>1295</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>1261</v>
+        <v>1265</v>
       </c>
       <c r="E17" s="28"/>
     </row>
@@ -15370,22 +15398,22 @@
         <v>43</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="E18" s="28"/>
     </row>
     <row r="19" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
       <c r="C19" s="27"/>
       <c r="D19" s="27"/>
@@ -15393,16 +15421,16 @@
     </row>
     <row r="20" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="27" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B20" s="27" t="s">
         <v>1296</v>
       </c>
-      <c r="B20" s="27" t="s">
-        <v>1292</v>
-      </c>
       <c r="C20" s="27" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="E20" s="28"/>
     </row>
@@ -15411,13 +15439,13 @@
         <v>125</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>1298</v>
+        <v>1302</v>
       </c>
       <c r="E21" s="28"/>
     </row>
@@ -15426,43 +15454,43 @@
         <v>182</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>1299</v>
+        <v>1303</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
       <c r="E22" s="28"/>
     </row>
     <row r="23" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="30" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
       <c r="E23" s="28"/>
     </row>
     <row r="24" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="E24" s="28"/>
     </row>
@@ -15471,67 +15499,67 @@
         <v>74</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>1305</v>
+        <v>1309</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
       <c r="E25" s="28"/>
     </row>
     <row r="26" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="27" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="B26" s="30" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>1274</v>
+        <v>1278</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>1275</v>
+        <v>1279</v>
       </c>
       <c r="E26" s="28"/>
     </row>
     <row r="27" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>1306</v>
+        <v>1310</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>1278</v>
+        <v>1282</v>
       </c>
       <c r="E27" s="28"/>
     </row>
     <row r="28" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="27" t="s">
-        <v>1307</v>
+        <v>1311</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>1308</v>
+        <v>1312</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>1309</v>
+        <v>1313</v>
       </c>
       <c r="E28" s="28"/>
     </row>
     <row r="29" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="C29" s="27"/>
       <c r="D29" s="27"/>
@@ -15542,7 +15570,7 @@
         <v>160</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>1310</v>
+        <v>1314</v>
       </c>
       <c r="C30" s="27"/>
       <c r="D30" s="27"/>
@@ -15553,13 +15581,13 @@
         <v>99</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>1311</v>
+        <v>1315</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>1312</v>
+        <v>1316</v>
       </c>
       <c r="E31" s="28"/>
     </row>
@@ -15568,7 +15596,7 @@
         <v>262</v>
       </c>
       <c r="B32" s="32" t="s">
-        <v>1313</v>
+        <v>1317</v>
       </c>
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
@@ -15576,16 +15604,16 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="26" t="s">
-        <v>1314</v>
+        <v>1318</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>1315</v>
+        <v>1319</v>
       </c>
       <c r="E33" s="26"/>
     </row>
@@ -15594,7 +15622,7 @@
         <v>46</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>1316</v>
+        <v>1320</v>
       </c>
       <c r="C34" s="26"/>
       <c r="D34" s="26"/>
@@ -15602,10 +15630,10 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="26" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="C35" s="26"/>
       <c r="D35" s="26"/>
@@ -15613,16 +15641,16 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="26" t="s">
-        <v>1318</v>
+        <v>1322</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>1319</v>
+        <v>1323</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>1321</v>
+        <v>1325</v>
       </c>
       <c r="E36" s="26"/>
     </row>
@@ -15631,7 +15659,7 @@
         <v>202</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>1322</v>
+        <v>1326</v>
       </c>
       <c r="C37" s="26"/>
       <c r="D37" s="26"/>
@@ -15642,7 +15670,7 @@
         <v>205</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>1323</v>
+        <v>1327</v>
       </c>
       <c r="C38" s="26"/>
       <c r="D38" s="26"/>
@@ -15653,7 +15681,7 @@
         <v>140</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="C39" s="26"/>
       <c r="D39" s="26"/>
@@ -15661,25 +15689,25 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="26" t="s">
-        <v>1324</v>
+        <v>1328</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>1325</v>
+        <v>1329</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>1326</v>
+        <v>1330</v>
       </c>
       <c r="E40" s="26"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="26" t="s">
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>1328</v>
+        <v>1332</v>
       </c>
       <c r="C41" s="26"/>
       <c r="D41" s="26"/>
@@ -15687,16 +15715,16 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="26" t="s">
-        <v>1329</v>
+        <v>1333</v>
       </c>
       <c r="B42" s="26" t="s">
-        <v>1291</v>
+        <v>1295</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>1330</v>
+        <v>1334</v>
       </c>
       <c r="D42" s="26" t="s">
-        <v>1331</v>
+        <v>1335</v>
       </c>
       <c r="E42" s="26"/>
     </row>
@@ -15705,7 +15733,7 @@
         <v>350</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>1310</v>
+        <v>1314</v>
       </c>
       <c r="C43" s="26"/>
       <c r="D43" s="26"/>
@@ -15713,34 +15741,34 @@
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="26" t="s">
-        <v>1332</v>
+        <v>1336</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>1291</v>
+        <v>1295</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>1333</v>
+        <v>1337</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>1334</v>
+        <v>1338</v>
       </c>
       <c r="E44" s="26"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="26" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>1336</v>
+        <v>1340</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
       <c r="D45" s="26" t="s">
-        <v>1298</v>
+        <v>1302</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15748,7 +15776,7 @@
         <v>133</v>
       </c>
       <c r="B46" s="26" t="s">
-        <v>1337</v>
+        <v>1341</v>
       </c>
       <c r="C46" s="26"/>
       <c r="D46" s="26"/>
@@ -15756,10 +15784,10 @@
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="26" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>1313</v>
+        <v>1317</v>
       </c>
       <c r="C47" s="26"/>
       <c r="D47" s="26"/>
@@ -15770,7 +15798,7 @@
         <v>128</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="C48" s="26"/>
       <c r="D48" s="26"/>
@@ -15781,67 +15809,67 @@
         <v>95</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>1338</v>
+        <v>1342</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>1340</v>
+        <v>1344</v>
       </c>
       <c r="E49" s="26"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="26" t="s">
-        <v>1341</v>
+        <v>1345</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>1342</v>
+        <v>1346</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="D50" s="26" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="E50" s="26"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="26" t="s">
-        <v>1343</v>
+        <v>1347</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
       <c r="D51" s="26" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
       <c r="E51" s="26"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="26" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
       <c r="B52" s="26" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="C52" s="26" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="D52" s="26" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
       <c r="E52" s="26"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="26" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
       <c r="C53" s="26"/>
       <c r="D53" s="26"/>
@@ -15849,10 +15877,10 @@
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="26" t="s">
-        <v>1345</v>
+        <v>1349</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
       <c r="C54" s="26"/>
       <c r="D54" s="26"/>
@@ -15860,10 +15888,10 @@
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="26" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="C55" s="26"/>
       <c r="D55" s="26"/>
@@ -15871,10 +15899,10 @@
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="26" t="s">
-        <v>1349</v>
+        <v>1353</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>1350</v>
+        <v>1354</v>
       </c>
       <c r="C56" s="26"/>
       <c r="D56" s="26"/>
@@ -15882,10 +15910,10 @@
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="26" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="C57" s="26"/>
       <c r="D57" s="26"/>
@@ -15893,10 +15921,10 @@
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="26" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="C58" s="26"/>
       <c r="D58" s="26"/>
@@ -15907,10 +15935,10 @@
         <v>456</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D59" s="26"/>
       <c r="E59" s="26"/>
@@ -15944,99 +15972,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="34" t="s">
-        <v>1353</v>
+        <v>1357</v>
       </c>
       <c r="C1" s="34" t="s">
-        <v>1354</v>
+        <v>1358</v>
       </c>
       <c r="D1" s="34" t="s">
-        <v>1355</v>
+        <v>1359</v>
       </c>
       <c r="E1" s="34" t="s">
-        <v>1356</v>
+        <v>1360</v>
       </c>
       <c r="F1" s="34" t="s">
-        <v>1357</v>
+        <v>1361</v>
       </c>
       <c r="G1" s="34" t="s">
-        <v>1358</v>
+        <v>1362</v>
       </c>
       <c r="H1" s="34" t="s">
-        <v>1359</v>
+        <v>1363</v>
       </c>
       <c r="I1" s="34" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J1" s="34" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="K1" s="34" t="s">
-        <v>1362</v>
+        <v>1366</v>
       </c>
       <c r="L1" s="34" t="s">
-        <v>1363</v>
+        <v>1367</v>
       </c>
       <c r="M1" s="34" t="s">
-        <v>1364</v>
+        <v>1368</v>
       </c>
       <c r="N1" s="34" t="s">
-        <v>1365</v>
+        <v>1369</v>
       </c>
       <c r="O1" s="34" t="s">
-        <v>1366</v>
+        <v>1370</v>
       </c>
       <c r="P1" s="34" t="s">
-        <v>1367</v>
+        <v>1371</v>
       </c>
       <c r="Q1" s="34" t="s">
-        <v>1368</v>
+        <v>1372</v>
       </c>
       <c r="R1" s="34" t="s">
-        <v>1369</v>
+        <v>1373</v>
       </c>
       <c r="S1" s="34" t="s">
-        <v>1370</v>
+        <v>1374</v>
       </c>
       <c r="T1" s="34" t="s">
-        <v>1371</v>
+        <v>1375</v>
       </c>
       <c r="U1" s="34" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="V1" s="34" t="s">
-        <v>1373</v>
+        <v>1377</v>
       </c>
       <c r="W1" s="34" t="s">
-        <v>1374</v>
+        <v>1378</v>
       </c>
       <c r="X1" s="34" t="s">
-        <v>1375</v>
+        <v>1379</v>
       </c>
       <c r="Y1" s="34" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="Z1" s="34" t="s">
-        <v>1377</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="35" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>1378</v>
+        <v>1382</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>1379</v>
+        <v>1383</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="E2" s="35" t="s">
         <v>160</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="G2" s="36"/>
       <c r="H2" s="36"/>
@@ -16064,7 +16092,7 @@
         <v>143</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>1381</v>
+        <v>1385</v>
       </c>
       <c r="C3" s="35"/>
       <c r="D3" s="35"/>
@@ -16096,64 +16124,64 @@
         <v>93</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>1382</v>
+        <v>1386</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1383</v>
+        <v>1387</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1384</v>
+        <v>1388</v>
       </c>
       <c r="G4" s="36" t="s">
-        <v>1385</v>
+        <v>1389</v>
       </c>
       <c r="H4" s="36" t="s">
-        <v>1386</v>
+        <v>1390</v>
       </c>
       <c r="I4" s="36" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>1388</v>
+        <v>1392</v>
       </c>
       <c r="K4" s="36" t="s">
-        <v>1389</v>
+        <v>1393</v>
       </c>
       <c r="L4" s="36" t="s">
-        <v>1390</v>
+        <v>1394</v>
       </c>
       <c r="M4" s="36" t="s">
-        <v>1391</v>
+        <v>1395</v>
       </c>
       <c r="N4" s="36" t="s">
-        <v>1392</v>
+        <v>1396</v>
       </c>
       <c r="O4" s="36" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="P4" s="36" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="Q4" s="36" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="R4" s="36" t="s">
-        <v>1396</v>
+        <v>1400</v>
       </c>
       <c r="S4" s="36" t="s">
-        <v>1397</v>
+        <v>1401</v>
       </c>
       <c r="T4" s="36" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
       <c r="U4" s="36" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="V4" s="36"/>
       <c r="W4" s="36"/>
@@ -16166,22 +16194,22 @@
         <v>136</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>1400</v>
+        <v>1404</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>1402</v>
+        <v>1406</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1404</v>
+        <v>1408</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
       <c r="H5" s="36"/>
       <c r="I5" s="36"/>
@@ -16211,16 +16239,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
@@ -16251,25 +16279,25 @@
         <v>5</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="G7" s="36" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="H7" s="36" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="I7" s="36" t="s">
-        <v>1271</v>
+        <v>1275</v>
       </c>
       <c r="J7" s="36"/>
       <c r="K7" s="36"/>
@@ -16291,16 +16319,16 @@
     </row>
     <row r="8" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="35" t="s">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="E8" s="35" t="s">
         <v>245</v>
@@ -16332,13 +16360,13 @@
         <v>28</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>1414</v>
+        <v>1418</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
       <c r="E9" s="35"/>
       <c r="F9" s="35"/>
@@ -16365,25 +16393,25 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="35" t="s">
-        <v>1272</v>
+        <v>1276</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1418</v>
+        <v>1422</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1419</v>
+        <v>1423</v>
       </c>
       <c r="G10" s="36" t="s">
-        <v>1420</v>
+        <v>1424</v>
       </c>
       <c r="H10" s="36"/>
       <c r="I10" s="36"/>
@@ -16410,10 +16438,10 @@
         <v>111</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>1421</v>
+        <v>1425</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
@@ -16441,28 +16469,28 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="37" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>1425</v>
+        <v>1429</v>
       </c>
       <c r="G12" s="36" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="H12" s="36" t="s">
-        <v>1426</v>
+        <v>1430</v>
       </c>
       <c r="I12" s="36"/>
       <c r="J12" s="36"/>
@@ -16488,10 +16516,10 @@
         <v>42</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="37"/>
@@ -16522,16 +16550,16 @@
         <v>97</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="F14" s="37"/>
       <c r="G14" s="36"/>
@@ -16563,25 +16591,25 @@
         <v>5</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="G15" s="36" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="H15" s="36" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="I15" s="36" t="s">
-        <v>1271</v>
+        <v>1275</v>
       </c>
       <c r="J15" s="36"/>
       <c r="K15" s="36"/>
@@ -16603,19 +16631,19 @@
     </row>
     <row r="16" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="37" t="s">
-        <v>1431</v>
+        <v>1435</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>1432</v>
+        <v>1436</v>
       </c>
       <c r="C16" s="37" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="F16" s="37"/>
       <c r="G16" s="36"/>
@@ -16641,13 +16669,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="37" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="37"/>
@@ -16678,7 +16706,7 @@
         <v>125</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>1435</v>
+        <v>1439</v>
       </c>
       <c r="C18" s="37"/>
       <c r="D18" s="37"/>
@@ -16707,10 +16735,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="37" t="s">
-        <v>1436</v>
+        <v>1440</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>1437</v>
+        <v>1441</v>
       </c>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
@@ -16742,7 +16770,7 @@
         <v>182</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="37"/>
@@ -16771,10 +16799,10 @@
     </row>
     <row r="21" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="37" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="37"/>
@@ -16809,43 +16837,43 @@
         <v>5</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="G22" s="36" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
       <c r="H22" s="36" t="s">
-        <v>1441</v>
+        <v>1445</v>
       </c>
       <c r="I22" s="36" t="s">
-        <v>1442</v>
+        <v>1446</v>
       </c>
       <c r="J22" s="36" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="K22" s="36" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
       <c r="L22" s="36" t="s">
-        <v>1445</v>
+        <v>1449</v>
       </c>
       <c r="M22" s="36" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="N22" s="36" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="O22" s="36" t="s">
-        <v>1271</v>
+        <v>1275</v>
       </c>
       <c r="P22" s="36"/>
       <c r="Q22" s="36"/>
@@ -16861,10 +16889,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="37" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="C23" s="37"/>
       <c r="D23" s="37"/>
@@ -16896,28 +16924,28 @@
         <v>99</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>1447</v>
+        <v>1451</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>1448</v>
+        <v>1452</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>1450</v>
+        <v>1454</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>1451</v>
+        <v>1455</v>
       </c>
       <c r="G24" s="36" t="s">
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="H24" s="36" t="s">
-        <v>1453</v>
+        <v>1457</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>1454</v>
+        <v>1458</v>
       </c>
       <c r="J24" s="36"/>
       <c r="K24" s="36"/>
@@ -16942,7 +16970,7 @@
         <v>262</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="C25" s="37"/>
       <c r="D25" s="37"/>
@@ -16974,10 +17002,10 @@
         <v>46</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>1455</v>
+        <v>1459</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>1456</v>
+        <v>1460</v>
       </c>
       <c r="D26" s="37"/>
       <c r="E26" s="37"/>
@@ -17005,10 +17033,10 @@
     </row>
     <row r="27" customFormat="false" ht="31.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="37" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="C27" s="37"/>
       <c r="D27" s="37"/>
@@ -17040,7 +17068,7 @@
         <v>202</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>1458</v>
+        <v>1462</v>
       </c>
       <c r="C28" s="37"/>
       <c r="D28" s="37"/>
@@ -17072,7 +17100,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>1459</v>
+        <v>1463</v>
       </c>
       <c r="C29" s="37"/>
       <c r="D29" s="37"/>
@@ -17104,7 +17132,7 @@
         <v>140</v>
       </c>
       <c r="B30" s="37" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="C30" s="37"/>
       <c r="D30" s="37"/>
@@ -17139,25 +17167,25 @@
         <v>5</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="D31" s="36" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="G31" s="36" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="H31" s="36" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="I31" s="36" t="s">
-        <v>1271</v>
+        <v>1275</v>
       </c>
       <c r="J31" s="37"/>
       <c r="K31" s="37"/>
@@ -17217,43 +17245,43 @@
         <v>5</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="G33" s="36" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
       <c r="H33" s="36" t="s">
-        <v>1441</v>
+        <v>1445</v>
       </c>
       <c r="I33" s="36" t="s">
-        <v>1442</v>
+        <v>1446</v>
       </c>
       <c r="J33" s="36" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="K33" s="36" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
       <c r="L33" s="36" t="s">
-        <v>1445</v>
+        <v>1449</v>
       </c>
       <c r="M33" s="36" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="N33" s="36" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="O33" s="36" t="s">
-        <v>1271</v>
+        <v>1275</v>
       </c>
       <c r="P33" s="36"/>
       <c r="Q33" s="37"/>
@@ -17269,10 +17297,10 @@
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="37" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>1460</v>
+        <v>1464</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -17304,7 +17332,7 @@
         <v>282</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="C35" s="37"/>
       <c r="D35" s="37"/>
@@ -17336,7 +17364,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="37" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="C36" s="37"/>
       <c r="D36" s="37"/>
@@ -17365,10 +17393,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="37" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="B37" s="37" t="s">
-        <v>1461</v>
+        <v>1465</v>
       </c>
       <c r="C37" s="37"/>
       <c r="D37" s="37"/>
@@ -17400,16 +17428,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>1463</v>
+        <v>1467</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F38" s="37"/>
       <c r="G38" s="36"/>
@@ -17438,22 +17466,22 @@
         <v>95</v>
       </c>
       <c r="B39" s="37" t="s">
-        <v>1466</v>
+        <v>1470</v>
       </c>
       <c r="C39" s="37" t="s">
-        <v>1437</v>
+        <v>1441</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>1468</v>
+        <v>1472</v>
       </c>
       <c r="G39" s="36" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
       <c r="H39" s="36"/>
       <c r="I39" s="36"/>
@@ -17477,25 +17505,25 @@
     </row>
     <row r="40" customFormat="false" ht="31.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="37" t="s">
-        <v>1341</v>
+        <v>1345</v>
       </c>
       <c r="B40" s="37" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>1471</v>
+        <v>1475</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>1472</v>
+        <v>1476</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
       <c r="G40" s="36" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="H40" s="36"/>
       <c r="I40" s="36"/>
@@ -17519,10 +17547,10 @@
     </row>
     <row r="41" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="37" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="B41" s="37" t="s">
-        <v>1474</v>
+        <v>1478</v>
       </c>
       <c r="C41" s="37"/>
       <c r="D41" s="37"/>
@@ -17551,10 +17579,10 @@
     </row>
     <row r="42" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="37" t="s">
-        <v>1345</v>
+        <v>1349</v>
       </c>
       <c r="B42" s="37" t="s">
-        <v>1475</v>
+        <v>1479</v>
       </c>
       <c r="C42" s="37"/>
       <c r="D42" s="37"/>
@@ -17586,13 +17614,13 @@
         <v>123</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>1476</v>
+        <v>1480</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="D43" s="37" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="E43" s="37"/>
       <c r="F43" s="37"/>
@@ -17622,7 +17650,7 @@
         <v>228</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>1477</v>
+        <v>1481</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -17651,13 +17679,13 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="37" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="B45" s="37" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="C45" s="37" t="s">
-        <v>1479</v>
+        <v>1483</v>
       </c>
       <c r="D45" s="37"/>
       <c r="E45" s="37"/>
@@ -17688,58 +17716,58 @@
         <v>456</v>
       </c>
       <c r="B46" s="37" t="s">
-        <v>1480</v>
+        <v>1484</v>
       </c>
       <c r="C46" s="37" t="s">
-        <v>1481</v>
+        <v>1485</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="E46" s="37" t="s">
-        <v>1482</v>
+        <v>1486</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>1483</v>
+        <v>1487</v>
       </c>
       <c r="G46" s="36" t="s">
-        <v>1484</v>
+        <v>1488</v>
       </c>
       <c r="H46" s="36" t="s">
-        <v>1485</v>
+        <v>1489</v>
       </c>
       <c r="I46" s="36" t="s">
-        <v>1486</v>
+        <v>1490</v>
       </c>
       <c r="J46" s="36" t="s">
-        <v>1487</v>
+        <v>1491</v>
       </c>
       <c r="K46" s="36" t="s">
-        <v>1488</v>
+        <v>1492</v>
       </c>
       <c r="L46" s="36" t="s">
-        <v>1489</v>
+        <v>1493</v>
       </c>
       <c r="M46" s="36" t="s">
-        <v>1490</v>
+        <v>1494</v>
       </c>
       <c r="N46" s="36" t="s">
-        <v>1491</v>
+        <v>1495</v>
       </c>
       <c r="O46" s="36" t="s">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="P46" s="36" t="s">
-        <v>1493</v>
+        <v>1497</v>
       </c>
       <c r="Q46" s="36" t="s">
-        <v>1494</v>
+        <v>1498</v>
       </c>
       <c r="R46" s="36" t="s">
-        <v>1495</v>
+        <v>1499</v>
       </c>
       <c r="S46" s="36" t="s">
-        <v>1496</v>
+        <v>1500</v>
       </c>
       <c r="T46" s="36"/>
       <c r="U46" s="36"/>

--- a/REFERENCE.xlsx
+++ b/REFERENCE.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="MATERIALS" sheetId="1" state="visible" r:id="rId2"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2459" uniqueCount="1621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2461" uniqueCount="1622">
   <si>
     <t xml:space="preserve">MATERIAL NAME</t>
   </si>
@@ -3160,6 +3160,9 @@
   </si>
   <si>
     <t xml:space="preserve">R205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R206</t>
   </si>
   <si>
     <t xml:space="preserve">TEAKWOOD</t>
@@ -6750,178 +6753,178 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="38" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B1" s="38" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="39" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="39" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B3" s="40" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="39" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="39" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="39" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="39" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="39" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="39" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="39" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="39" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="39" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="39" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="39" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="39" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="39" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="39" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="39" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="39" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="39" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="39" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="39" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B22" s="40" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
     </row>
   </sheetData>
@@ -6953,99 +6956,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="41" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="C1" s="41" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="D1" s="41" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="E1" s="41" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="F1" s="41" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="G1" s="41" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="H1" s="41" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="I1" s="41" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="J1" s="41" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="K1" s="41" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="L1" s="41" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="M1" s="41" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="N1" s="41" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="O1" s="41" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="P1" s="41" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="Q1" s="41" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="R1" s="41" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="S1" s="41" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="T1" s="41" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="U1" s="41" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="V1" s="41" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="W1" s="41" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="X1" s="41" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="Y1" s="41" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="Z1" s="41" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="35" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="E2" s="35" t="s">
         <v>160</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="G2" s="36"/>
       <c r="H2" s="36"/>
@@ -7073,10 +7076,10 @@
         <v>143</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="D3" s="35"/>
       <c r="E3" s="35"/>
@@ -7107,64 +7110,64 @@
         <v>93</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="G4" s="36" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="H4" s="36" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="I4" s="36" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="K4" s="36" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="L4" s="36" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="M4" s="36" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="N4" s="36" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="O4" s="36" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="P4" s="36" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="Q4" s="36" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="R4" s="36" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="S4" s="36" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="T4" s="36" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="U4" s="43" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="V4" s="36"/>
       <c r="W4" s="42"/>
@@ -7177,22 +7180,22 @@
         <v>136</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="H5" s="36"/>
       <c r="I5" s="36"/>
@@ -7219,19 +7222,19 @@
         <v>23</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
@@ -7259,13 +7262,13 @@
         <v>85</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="E7" s="35"/>
       <c r="F7" s="35"/>
@@ -7292,16 +7295,16 @@
     </row>
     <row r="8" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="35" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="E8" s="35" t="s">
         <v>245</v>
@@ -7333,13 +7336,13 @@
         <v>28</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="E9" s="35"/>
       <c r="F9" s="35"/>
@@ -7366,25 +7369,25 @@
     </row>
     <row r="10" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="35" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="G10" s="36" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H10" s="36"/>
       <c r="I10" s="36"/>
@@ -7411,10 +7414,10 @@
         <v>111</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
@@ -7442,28 +7445,28 @@
     </row>
     <row r="12" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="37" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="G12" s="36" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="H12" s="36" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="I12" s="36"/>
       <c r="J12" s="36"/>
@@ -7489,10 +7492,10 @@
         <v>42</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="37"/>
@@ -7523,16 +7526,16 @@
         <v>97</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="F14" s="37"/>
       <c r="G14" s="36"/>
@@ -7561,96 +7564,96 @@
         <v>6</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="G15" s="36" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="H15" s="36" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="I15" s="36" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="J15" s="36" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="K15" s="36" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="L15" s="36" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="M15" s="36" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="N15" s="36" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="O15" s="36" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="P15" s="36" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="Q15" s="36" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="R15" s="36" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="S15" s="36" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="T15" s="36" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="U15" s="36" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="V15" s="36" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="W15" s="36" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="X15" s="36" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="Y15" s="36" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="Z15" s="44" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="37" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="C16" s="37" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="F16" s="37"/>
       <c r="G16" s="36"/>
@@ -7676,13 +7679,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="37" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="37"/>
@@ -7713,7 +7716,7 @@
         <v>125</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="C18" s="37"/>
       <c r="D18" s="37"/>
@@ -7742,10 +7745,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="37" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
@@ -7777,7 +7780,7 @@
         <v>182</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="37"/>
@@ -7806,10 +7809,10 @@
     </row>
     <row r="21" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="37" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="37"/>
@@ -7841,28 +7844,28 @@
         <v>74</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="M22" s="36"/>
       <c r="N22" s="36"/>
@@ -7881,10 +7884,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="37" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="C23" s="37"/>
       <c r="D23" s="37"/>
@@ -7916,28 +7919,28 @@
         <v>99</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="G24" s="36" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="H24" s="36" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="J24" s="36"/>
       <c r="K24" s="36"/>
@@ -7962,7 +7965,7 @@
         <v>262</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="C25" s="37"/>
       <c r="D25" s="37"/>
@@ -7994,10 +7997,10 @@
         <v>46</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="D26" s="37"/>
       <c r="E26" s="37"/>
@@ -8025,10 +8028,10 @@
     </row>
     <row r="27" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="37" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="C27" s="37"/>
       <c r="D27" s="37"/>
@@ -8060,7 +8063,7 @@
         <v>202</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="C28" s="37"/>
       <c r="D28" s="37"/>
@@ -8092,7 +8095,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="C29" s="37"/>
       <c r="D29" s="37"/>
@@ -8124,7 +8127,7 @@
         <v>140</v>
       </c>
       <c r="B30" s="37" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="C30" s="37"/>
       <c r="D30" s="37"/>
@@ -8156,76 +8159,76 @@
         <v>8</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="D31" s="36" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="H31" s="37" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="I31" s="37" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="J31" s="37" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="K31" s="37" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="L31" s="37" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="M31" s="37" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="N31" s="36" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="O31" s="37" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="P31" s="36" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="Q31" s="36" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="R31" s="36" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="S31" s="36" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="T31" s="36" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="U31" s="36" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="V31" s="36" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="W31" s="36" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="X31" s="36" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="Y31" s="36" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
@@ -8275,79 +8278,79 @@
         <v>3</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="J33" s="36" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="K33" s="36" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="L33" s="36" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="M33" s="36" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="N33" s="36" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="O33" s="36" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="P33" s="36" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="Q33" s="37" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="R33" s="37" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="S33" s="37" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="T33" s="36" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="U33" s="36" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="V33" s="36" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="W33" s="36" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="X33" s="36" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="Y33" s="36" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="Z33" s="36" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
@@ -8362,10 +8365,10 @@
     </row>
     <row r="34" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="37" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -8397,7 +8400,7 @@
         <v>282</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="C35" s="37"/>
       <c r="D35" s="37"/>
@@ -8429,7 +8432,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="37" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="C36" s="37"/>
       <c r="D36" s="37"/>
@@ -8458,10 +8461,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="37" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B37" s="37" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="C37" s="37"/>
       <c r="D37" s="37"/>
@@ -8493,16 +8496,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="F38" s="37"/>
       <c r="G38" s="36"/>
@@ -8531,22 +8534,22 @@
         <v>95</v>
       </c>
       <c r="B39" s="37" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="C39" s="37" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="G39" s="36" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="H39" s="36"/>
       <c r="I39" s="36"/>
@@ -8570,25 +8573,25 @@
     </row>
     <row r="40" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="37" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B40" s="37" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="G40" s="36" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="H40" s="36"/>
       <c r="I40" s="36"/>
@@ -8612,10 +8615,10 @@
     </row>
     <row r="41" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="37" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B41" s="37" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="C41" s="37"/>
       <c r="D41" s="37"/>
@@ -8644,10 +8647,10 @@
     </row>
     <row r="42" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="37" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B42" s="37" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="C42" s="37"/>
       <c r="D42" s="37"/>
@@ -8679,13 +8682,13 @@
         <v>123</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="D43" s="37" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="E43" s="37"/>
       <c r="F43" s="37"/>
@@ -8715,7 +8718,7 @@
         <v>228</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -8744,13 +8747,13 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="37" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B45" s="37" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="C45" s="37" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="D45" s="37"/>
       <c r="E45" s="37"/>
@@ -8781,58 +8784,58 @@
         <v>456</v>
       </c>
       <c r="B46" s="37" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="C46" s="37" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="E46" s="37" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="G46" s="36" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="H46" s="36" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="I46" s="36" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="J46" s="36" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="K46" s="36" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="L46" s="36" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="M46" s="36" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="N46" s="36" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="O46" s="36" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="P46" s="36" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="Q46" s="36" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="R46" s="36" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="S46" s="36" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="T46" s="36"/>
       <c r="U46" s="36"/>
@@ -8867,10 +8870,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="46" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B1" s="46" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12244,7 +12247,7 @@
     <tabColor rgb="FF2F5496"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B107"/>
+  <dimension ref="A1:B108"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
@@ -13105,6 +13108,14 @@
       </c>
       <c r="B107" s="19" t="s">
         <v>1042</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="19" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B108" s="19" t="s">
+        <v>1043</v>
       </c>
     </row>
   </sheetData>
@@ -13179,7 +13190,7 @@
         <v>93</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F1" s="20" t="s">
         <v>43</v>
@@ -13194,7 +13205,7 @@
         <v>136</v>
       </c>
       <c r="J1" s="20" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="K1" s="20" t="s">
         <v>28</v>
@@ -13203,19 +13214,19 @@
         <v>111</v>
       </c>
       <c r="M1" s="20" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="N1" s="20" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="O1" s="20" t="s">
         <v>143</v>
       </c>
       <c r="P1" s="20" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="Q1" s="20" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="R1" s="21" t="s">
         <v>350</v>
@@ -13227,10 +13238,10 @@
         <v>97</v>
       </c>
       <c r="U1" s="21" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="V1" s="21" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="W1" s="21" t="s">
         <v>99</v>
@@ -13239,13 +13250,13 @@
         <v>128</v>
       </c>
       <c r="Y1" s="21" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="Z1" s="21" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="AA1" s="21" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="AB1" s="21" t="s">
         <v>182</v>
@@ -13260,7 +13271,7 @@
         <v>228</v>
       </c>
       <c r="AF1" s="21" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="AG1" s="21" t="s">
         <v>85</v>
@@ -13289,570 +13300,570 @@
     </row>
     <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="E2" s="10" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>1063</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>1064</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>1065</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>1066</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>1067</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>1068</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>1069</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>1069</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>1070</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>1071</v>
+      </c>
+      <c r="R2" s="10" t="s">
+        <v>1060</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>1059</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="V2" s="10" t="s">
         <v>1060</v>
       </c>
-      <c r="G2" s="10" t="s">
-        <v>1061</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>1062</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>1063</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>1064</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>1065</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>1066</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>1067</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>1068</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>1068</v>
-      </c>
-      <c r="P2" s="10" t="s">
-        <v>1069</v>
-      </c>
-      <c r="Q2" s="10" t="s">
-        <v>1070</v>
-      </c>
-      <c r="R2" s="10" t="s">
-        <v>1059</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>1071</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>1058</v>
-      </c>
-      <c r="V2" s="10" t="s">
-        <v>1059</v>
-      </c>
       <c r="W2" s="1" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>456</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="AB2" s="10" t="s">
+        <v>1060</v>
+      </c>
+      <c r="AC2" s="1" t="s">
         <v>1059</v>
       </c>
-      <c r="AC2" s="1" t="s">
-        <v>1058</v>
-      </c>
       <c r="AD2" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="AE2" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="AG2" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="AN2" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="J3" s="10" t="s">
         <v>456</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="N3" s="10" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="O3" s="10" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="P3" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="Q3" s="10" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="R3" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="S3" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="T3" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="U3" s="10" t="s">
+        <v>1060</v>
+      </c>
+      <c r="V3" s="10" t="s">
         <v>1093</v>
       </c>
-      <c r="U3" s="10" t="s">
-        <v>1059</v>
-      </c>
-      <c r="V3" s="10" t="s">
-        <v>1092</v>
-      </c>
       <c r="W3" s="1" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="Y3" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="Z3" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="AA3" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="AB3" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="AC3" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="AD3" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="AE3" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="AG3" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="AH3" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="AI3" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="AJ3" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="AK3" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="AL3" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="AM3" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="AN3" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>1102</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>1097</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>1098</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>1099</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>1100</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>1101</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>1096</v>
-      </c>
       <c r="H4" s="10" t="s">
+        <v>1061</v>
+      </c>
+      <c r="I4" s="22" t="s">
+        <v>1103</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>1080</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>1057</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>1097</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>1093</v>
+      </c>
+      <c r="N4" s="10" t="s">
         <v>1060</v>
       </c>
-      <c r="I4" s="22" t="s">
-        <v>1102</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>1079</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>1056</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>1096</v>
-      </c>
-      <c r="M4" s="10" t="s">
-        <v>1092</v>
-      </c>
-      <c r="N4" s="10" t="s">
-        <v>1059</v>
-      </c>
       <c r="O4" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="P4" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="Q4" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="R4" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="S4" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="T4" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="U4" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="V4" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="X4" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="Y4" s="10" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Z4" s="10" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AA4" s="10" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AB4" s="10" t="s">
         <v>1104</v>
       </c>
-      <c r="Y4" s="10" t="s">
-        <v>1092</v>
-      </c>
-      <c r="Z4" s="10" t="s">
-        <v>1092</v>
-      </c>
-      <c r="AA4" s="10" t="s">
-        <v>1092</v>
-      </c>
-      <c r="AB4" s="10" t="s">
-        <v>1103</v>
-      </c>
       <c r="AC4" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="AD4" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="AE4" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="AF4" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="AG4" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="AH4" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="AI4" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="AJ4" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="AK4" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="AL4" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="AM4" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="AN4" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H5" s="10" t="s">
         <v>456</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="K5" s="10" t="s">
+        <v>1113</v>
+      </c>
+      <c r="L5" s="10" t="s">
         <v>1112</v>
       </c>
-      <c r="L5" s="10" t="s">
-        <v>1111</v>
-      </c>
       <c r="M5" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="O5" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="Q5" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="S5" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="T5" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="U5" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="W5" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="X5" s="1" t="s">
         <v>1113</v>
       </c>
-      <c r="X5" s="1" t="s">
-        <v>1112</v>
-      </c>
       <c r="Y5" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="Z5" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="AA5" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="AB5" s="10"/>
       <c r="AC5" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="AD5" s="10"/>
       <c r="AF5" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="AH5" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="AK5" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="AL5" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="AM5" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H6" s="10" t="s">
+        <v>1120</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>1093</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>1093</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>1121</v>
+      </c>
+      <c r="L6" s="10" t="s">
         <v>1119</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>1092</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>1092</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>1120</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>1118</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="O6" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="P6" s="22"/>
       <c r="Q6" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="T6" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="AF6" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H7" s="10" t="s">
+        <v>1127</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>1104</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>1104</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L7" s="10" t="s">
         <v>1126</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>1103</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>1103</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>1127</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>1125</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
@@ -13860,44 +13871,44 @@
       <c r="P7" s="22"/>
       <c r="Q7" s="22"/>
       <c r="W7" s="1" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="I8" s="22"/>
       <c r="J8" s="22"/>
       <c r="K8" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
@@ -13905,44 +13916,44 @@
       <c r="P8" s="22"/>
       <c r="Q8" s="22"/>
       <c r="W8" s="1" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="X8" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="I9" s="22"/>
       <c r="J9" s="22"/>
       <c r="K9" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="M9" s="22"/>
       <c r="N9" s="22"/>
@@ -13950,42 +13961,42 @@
       <c r="P9" s="22"/>
       <c r="Q9" s="22"/>
       <c r="W9" s="1" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="X9" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="E10" s="22"/>
       <c r="F10" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="I10" s="22"/>
       <c r="J10" s="22"/>
       <c r="K10" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="M10" s="22"/>
       <c r="N10" s="22"/>
@@ -13993,38 +14004,38 @@
       <c r="P10" s="22"/>
       <c r="Q10" s="22"/>
       <c r="W10" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="X10" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="E11" s="22"/>
       <c r="F11" s="22"/>
       <c r="G11" s="10" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="I11" s="22"/>
       <c r="J11" s="22"/>
       <c r="K11" s="22"/>
       <c r="L11" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="M11" s="22"/>
       <c r="N11" s="22"/>
@@ -14032,29 +14043,29 @@
       <c r="P11" s="22"/>
       <c r="Q11" s="22"/>
       <c r="W11" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="E12" s="22"/>
       <c r="F12" s="22"/>
       <c r="G12" s="10" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="I12" s="22"/>
       <c r="J12" s="22"/>
@@ -14066,29 +14077,29 @@
       <c r="P12" s="22"/>
       <c r="Q12" s="22"/>
       <c r="W12" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="E13" s="22"/>
       <c r="F13" s="22"/>
       <c r="G13" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="I13" s="22"/>
       <c r="J13" s="22"/>
@@ -14102,24 +14113,24 @@
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E14" s="22"/>
       <c r="F14" s="22"/>
       <c r="G14" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="I14" s="22"/>
       <c r="J14" s="22"/>
@@ -14133,24 +14144,24 @@
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="E15" s="22"/>
       <c r="F15" s="22"/>
       <c r="G15" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="I15" s="22"/>
       <c r="J15" s="22"/>
@@ -14164,20 +14175,20 @@
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
       <c r="F16" s="22"/>
       <c r="G16" s="22"/>
       <c r="H16" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="I16" s="22"/>
       <c r="J16" s="22"/>
@@ -14191,20 +14202,20 @@
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D17" s="22"/>
       <c r="E17" s="22"/>
       <c r="F17" s="22"/>
       <c r="G17" s="22"/>
       <c r="H17" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="I17" s="22"/>
       <c r="J17" s="22"/>
@@ -14218,13 +14229,13 @@
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="D18" s="22"/>
       <c r="E18" s="22"/>
@@ -14243,13 +14254,13 @@
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="D19" s="22"/>
       <c r="E19" s="22"/>
@@ -14268,13 +14279,13 @@
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="D20" s="22"/>
       <c r="E20" s="22"/>
@@ -14293,13 +14304,13 @@
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="D21" s="22"/>
       <c r="E21" s="22"/>
@@ -14318,13 +14329,13 @@
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="22"/>
@@ -14343,13 +14354,13 @@
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="D23" s="22"/>
       <c r="E23" s="22"/>
@@ -14368,13 +14379,13 @@
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="D24" s="22"/>
       <c r="E24" s="22"/>
@@ -14393,13 +14404,13 @@
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D25" s="22"/>
       <c r="E25" s="22"/>
@@ -14418,13 +14429,13 @@
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="22"/>
@@ -14443,13 +14454,13 @@
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="D27" s="22"/>
       <c r="E27" s="22"/>
@@ -14468,13 +14479,13 @@
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="D28" s="22"/>
       <c r="E28" s="22"/>
@@ -14493,13 +14504,13 @@
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="D29" s="22"/>
       <c r="E29" s="22"/>
@@ -14518,13 +14529,13 @@
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="D30" s="22"/>
       <c r="E30" s="22"/>
@@ -14543,13 +14554,13 @@
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="D31" s="22"/>
       <c r="E31" s="22"/>
@@ -14568,13 +14579,13 @@
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D32" s="22"/>
       <c r="E32" s="22"/>
@@ -14593,13 +14604,13 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="D33" s="22"/>
       <c r="E33" s="22"/>
@@ -14618,13 +14629,13 @@
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B34" s="22" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="D34" s="22"/>
       <c r="E34" s="22"/>
@@ -14643,13 +14654,13 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="D35" s="22"/>
       <c r="E35" s="22"/>
@@ -14668,13 +14679,13 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="D36" s="22"/>
       <c r="E36" s="22"/>
@@ -14693,10 +14704,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="C37" s="22"/>
       <c r="D37" s="22"/>
@@ -14716,10 +14727,10 @@
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="C38" s="22"/>
       <c r="D38" s="22"/>
@@ -14739,10 +14750,10 @@
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="C39" s="22"/>
       <c r="D39" s="22"/>
@@ -14762,7 +14773,7 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B40" s="22"/>
       <c r="C40" s="22"/>
@@ -14783,7 +14794,7 @@
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B41" s="22"/>
       <c r="C41" s="22"/>
@@ -14804,7 +14815,7 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
   </sheetData>
@@ -14832,92 +14843,92 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="24" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="24" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14927,7 +14938,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
   </sheetData>
@@ -14956,159 +14967,159 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B3" s="24" t="s">
         <v>1224</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>1223</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B15" s="24" t="s">
         <v>1247</v>
-      </c>
-      <c r="B15" s="24" t="s">
-        <v>1246</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B20" s="23"/>
     </row>
@@ -15140,31 +15151,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="E1" s="26"/>
     </row>
     <row r="2" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="E2" s="28"/>
     </row>
@@ -15173,13 +15184,13 @@
         <v>143</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="E3" s="28"/>
     </row>
@@ -15188,43 +15199,43 @@
         <v>93</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="E4" s="28"/>
     </row>
     <row r="5" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="E5" s="28"/>
     </row>
     <row r="6" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="E6" s="28"/>
     </row>
@@ -15233,13 +15244,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="E7" s="28"/>
     </row>
@@ -15248,43 +15259,43 @@
         <v>28</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="E8" s="28"/>
     </row>
     <row r="9" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="E9" s="28"/>
     </row>
     <row r="10" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="E10" s="28"/>
     </row>
@@ -15293,73 +15304,73 @@
         <v>111</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="E11" s="28"/>
     </row>
     <row r="12" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="E12" s="28"/>
     </row>
     <row r="13" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="E13" s="28"/>
     </row>
     <row r="14" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="E14" s="28"/>
     </row>
     <row r="15" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="E15" s="28"/>
     </row>
@@ -15368,13 +15379,13 @@
         <v>97</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="E16" s="28"/>
     </row>
@@ -15383,13 +15394,13 @@
         <v>6</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="E17" s="28"/>
     </row>
@@ -15398,22 +15409,22 @@
         <v>43</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E18" s="28"/>
     </row>
     <row r="19" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="C19" s="27"/>
       <c r="D19" s="27"/>
@@ -15421,16 +15432,16 @@
     </row>
     <row r="20" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="27" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E20" s="28"/>
     </row>
@@ -15439,13 +15450,13 @@
         <v>125</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="E21" s="28"/>
     </row>
@@ -15454,43 +15465,43 @@
         <v>182</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E22" s="28"/>
     </row>
     <row r="23" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="30" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="E23" s="28"/>
     </row>
     <row r="24" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="E24" s="28"/>
     </row>
@@ -15499,67 +15510,67 @@
         <v>74</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="E25" s="28"/>
     </row>
     <row r="26" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="27" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B26" s="30" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="E26" s="28"/>
     </row>
     <row r="27" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="E27" s="28"/>
     </row>
     <row r="28" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="27" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="E28" s="28"/>
     </row>
     <row r="29" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="C29" s="27"/>
       <c r="D29" s="27"/>
@@ -15570,7 +15581,7 @@
         <v>160</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="C30" s="27"/>
       <c r="D30" s="27"/>
@@ -15581,13 +15592,13 @@
         <v>99</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="E31" s="28"/>
     </row>
@@ -15596,7 +15607,7 @@
         <v>262</v>
       </c>
       <c r="B32" s="32" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
@@ -15604,16 +15615,16 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="26" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="E33" s="26"/>
     </row>
@@ -15622,7 +15633,7 @@
         <v>46</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="C34" s="26"/>
       <c r="D34" s="26"/>
@@ -15630,10 +15641,10 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="26" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="C35" s="26"/>
       <c r="D35" s="26"/>
@@ -15641,16 +15652,16 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="26" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="E36" s="26"/>
     </row>
@@ -15659,7 +15670,7 @@
         <v>202</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="C37" s="26"/>
       <c r="D37" s="26"/>
@@ -15670,7 +15681,7 @@
         <v>205</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="C38" s="26"/>
       <c r="D38" s="26"/>
@@ -15681,7 +15692,7 @@
         <v>140</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="C39" s="26"/>
       <c r="D39" s="26"/>
@@ -15689,25 +15700,25 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="26" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="E40" s="26"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="26" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="C41" s="26"/>
       <c r="D41" s="26"/>
@@ -15715,16 +15726,16 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="26" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="B42" s="26" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="D42" s="26" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="E42" s="26"/>
     </row>
@@ -15733,7 +15744,7 @@
         <v>350</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="C43" s="26"/>
       <c r="D43" s="26"/>
@@ -15741,34 +15752,34 @@
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="26" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="E44" s="26"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="26" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="D45" s="26" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15776,7 +15787,7 @@
         <v>133</v>
       </c>
       <c r="B46" s="26" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="C46" s="26"/>
       <c r="D46" s="26"/>
@@ -15784,10 +15795,10 @@
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="26" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="C47" s="26"/>
       <c r="D47" s="26"/>
@@ -15798,7 +15809,7 @@
         <v>128</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="C48" s="26"/>
       <c r="D48" s="26"/>
@@ -15809,67 +15820,67 @@
         <v>95</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="E49" s="26"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="26" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="D50" s="26" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="E50" s="26"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="26" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="D51" s="26" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E51" s="26"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="26" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="B52" s="26" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="C52" s="26" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="D52" s="26" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="E52" s="26"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="26" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="C53" s="26"/>
       <c r="D53" s="26"/>
@@ -15877,10 +15888,10 @@
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="26" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="C54" s="26"/>
       <c r="D54" s="26"/>
@@ -15888,10 +15899,10 @@
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="26" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="C55" s="26"/>
       <c r="D55" s="26"/>
@@ -15899,10 +15910,10 @@
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="26" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="C56" s="26"/>
       <c r="D56" s="26"/>
@@ -15910,10 +15921,10 @@
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="26" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="C57" s="26"/>
       <c r="D57" s="26"/>
@@ -15921,10 +15932,10 @@
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="26" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="C58" s="26"/>
       <c r="D58" s="26"/>
@@ -15935,10 +15946,10 @@
         <v>456</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="D59" s="26"/>
       <c r="E59" s="26"/>
@@ -15972,99 +15983,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="34" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="C1" s="34" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="D1" s="34" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="E1" s="34" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F1" s="34" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="G1" s="34" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="H1" s="34" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="I1" s="34" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="J1" s="34" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="K1" s="34" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="L1" s="34" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="M1" s="34" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="N1" s="34" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="O1" s="34" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="P1" s="34" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="Q1" s="34" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="R1" s="34" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="S1" s="34" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="T1" s="34" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="U1" s="34" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="V1" s="34" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="W1" s="34" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="X1" s="34" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="Y1" s="34" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="Z1" s="34" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="35" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="E2" s="35" t="s">
         <v>160</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="G2" s="36"/>
       <c r="H2" s="36"/>
@@ -16092,7 +16103,7 @@
         <v>143</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="C3" s="35"/>
       <c r="D3" s="35"/>
@@ -16124,64 +16135,64 @@
         <v>93</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="G4" s="36" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="H4" s="36" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="I4" s="36" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="K4" s="36" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="L4" s="36" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="M4" s="36" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="N4" s="36" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="O4" s="36" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="P4" s="36" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="Q4" s="36" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="R4" s="36" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="S4" s="36" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="T4" s="36" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="U4" s="36" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="V4" s="36"/>
       <c r="W4" s="36"/>
@@ -16194,22 +16205,22 @@
         <v>136</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="H5" s="36"/>
       <c r="I5" s="36"/>
@@ -16239,16 +16250,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
@@ -16279,25 +16290,25 @@
         <v>5</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="G7" s="36" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="H7" s="36" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="I7" s="36" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="J7" s="36"/>
       <c r="K7" s="36"/>
@@ -16319,16 +16330,16 @@
     </row>
     <row r="8" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="35" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="E8" s="35" t="s">
         <v>245</v>
@@ -16360,13 +16371,13 @@
         <v>28</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="E9" s="35"/>
       <c r="F9" s="35"/>
@@ -16393,25 +16404,25 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="35" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="G10" s="36" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H10" s="36"/>
       <c r="I10" s="36"/>
@@ -16438,10 +16449,10 @@
         <v>111</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
@@ -16469,28 +16480,28 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="37" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="G12" s="36" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="H12" s="36" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="I12" s="36"/>
       <c r="J12" s="36"/>
@@ -16516,10 +16527,10 @@
         <v>42</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="37"/>
@@ -16550,16 +16561,16 @@
         <v>97</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="F14" s="37"/>
       <c r="G14" s="36"/>
@@ -16591,25 +16602,25 @@
         <v>5</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="G15" s="36" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="H15" s="36" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="I15" s="36" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="J15" s="36"/>
       <c r="K15" s="36"/>
@@ -16631,19 +16642,19 @@
     </row>
     <row r="16" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="37" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="C16" s="37" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="F16" s="37"/>
       <c r="G16" s="36"/>
@@ -16669,13 +16680,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="37" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="37"/>
@@ -16706,7 +16717,7 @@
         <v>125</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="C18" s="37"/>
       <c r="D18" s="37"/>
@@ -16735,10 +16746,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="37" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
@@ -16770,7 +16781,7 @@
         <v>182</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="37"/>
@@ -16799,10 +16810,10 @@
     </row>
     <row r="21" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="37" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="37"/>
@@ -16837,43 +16848,43 @@
         <v>5</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="G22" s="36" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H22" s="36" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="I22" s="36" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="J22" s="36" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="K22" s="36" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="L22" s="36" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="M22" s="36" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="N22" s="36" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="O22" s="36" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="P22" s="36"/>
       <c r="Q22" s="36"/>
@@ -16889,10 +16900,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="37" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="C23" s="37"/>
       <c r="D23" s="37"/>
@@ -16924,28 +16935,28 @@
         <v>99</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="G24" s="36" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="H24" s="36" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="J24" s="36"/>
       <c r="K24" s="36"/>
@@ -16970,7 +16981,7 @@
         <v>262</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="C25" s="37"/>
       <c r="D25" s="37"/>
@@ -17002,10 +17013,10 @@
         <v>46</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="D26" s="37"/>
       <c r="E26" s="37"/>
@@ -17033,10 +17044,10 @@
     </row>
     <row r="27" customFormat="false" ht="31.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="37" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="C27" s="37"/>
       <c r="D27" s="37"/>
@@ -17068,7 +17079,7 @@
         <v>202</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="C28" s="37"/>
       <c r="D28" s="37"/>
@@ -17100,7 +17111,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="C29" s="37"/>
       <c r="D29" s="37"/>
@@ -17132,7 +17143,7 @@
         <v>140</v>
       </c>
       <c r="B30" s="37" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="C30" s="37"/>
       <c r="D30" s="37"/>
@@ -17167,25 +17178,25 @@
         <v>5</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="D31" s="36" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="G31" s="36" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="H31" s="36" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="I31" s="36" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="J31" s="37"/>
       <c r="K31" s="37"/>
@@ -17245,43 +17256,43 @@
         <v>5</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="G33" s="36" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H33" s="36" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="I33" s="36" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="J33" s="36" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="K33" s="36" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="L33" s="36" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="M33" s="36" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="N33" s="36" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="O33" s="36" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="P33" s="36"/>
       <c r="Q33" s="37"/>
@@ -17297,10 +17308,10 @@
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="37" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -17332,7 +17343,7 @@
         <v>282</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="C35" s="37"/>
       <c r="D35" s="37"/>
@@ -17364,7 +17375,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="37" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="C36" s="37"/>
       <c r="D36" s="37"/>
@@ -17393,10 +17404,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="37" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B37" s="37" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="C37" s="37"/>
       <c r="D37" s="37"/>
@@ -17428,16 +17439,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="F38" s="37"/>
       <c r="G38" s="36"/>
@@ -17466,22 +17477,22 @@
         <v>95</v>
       </c>
       <c r="B39" s="37" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="C39" s="37" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="G39" s="36" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="H39" s="36"/>
       <c r="I39" s="36"/>
@@ -17505,25 +17516,25 @@
     </row>
     <row r="40" customFormat="false" ht="31.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="37" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B40" s="37" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="G40" s="36" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="H40" s="36"/>
       <c r="I40" s="36"/>
@@ -17547,10 +17558,10 @@
     </row>
     <row r="41" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="37" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B41" s="37" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="C41" s="37"/>
       <c r="D41" s="37"/>
@@ -17579,10 +17590,10 @@
     </row>
     <row r="42" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="37" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B42" s="37" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="C42" s="37"/>
       <c r="D42" s="37"/>
@@ -17614,13 +17625,13 @@
         <v>123</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="D43" s="37" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="E43" s="37"/>
       <c r="F43" s="37"/>
@@ -17650,7 +17661,7 @@
         <v>228</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -17679,13 +17690,13 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="37" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B45" s="37" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="C45" s="37" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="D45" s="37"/>
       <c r="E45" s="37"/>
@@ -17716,58 +17727,58 @@
         <v>456</v>
       </c>
       <c r="B46" s="37" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="C46" s="37" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="E46" s="37" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="G46" s="36" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="H46" s="36" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="I46" s="36" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="J46" s="36" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="K46" s="36" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="L46" s="36" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="M46" s="36" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="N46" s="36" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="O46" s="36" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="P46" s="36" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="Q46" s="36" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="R46" s="36" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="S46" s="36" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="T46" s="36"/>
       <c r="U46" s="36"/>

--- a/REFERENCE.xlsx
+++ b/REFERENCE.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="MATERIALS" sheetId="1" state="visible" r:id="rId2"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2461" uniqueCount="1622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2463" uniqueCount="1624">
   <si>
     <t xml:space="preserve">MATERIAL NAME</t>
   </si>
@@ -2518,6 +2518,12 @@
   </si>
   <si>
     <t xml:space="preserve">C160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESERT YELLOW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C161</t>
   </si>
   <si>
     <t xml:space="preserve">RAL COLOUR NAME</t>
@@ -6753,178 +6759,178 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="38" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="B1" s="38" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="39" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="39" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="B3" s="40" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="39" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="39" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="39" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="39" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="39" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="39" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="39" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="39" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="39" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="39" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="39" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="39" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="39" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="39" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="39" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="39" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="39" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="39" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="39" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="B22" s="40" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
     </row>
   </sheetData>
@@ -6956,99 +6962,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="41" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="C1" s="41" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="D1" s="41" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E1" s="41" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="F1" s="41" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="G1" s="41" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="H1" s="41" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="I1" s="41" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="J1" s="41" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="K1" s="41" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="L1" s="41" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="M1" s="41" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="N1" s="41" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="O1" s="41" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="P1" s="41" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="Q1" s="41" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="R1" s="41" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="S1" s="41" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="T1" s="41" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="U1" s="41" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="V1" s="41" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="W1" s="41" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="X1" s="41" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="Y1" s="41" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="Z1" s="41" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="35" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="E2" s="35" t="s">
         <v>160</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="G2" s="36"/>
       <c r="H2" s="36"/>
@@ -7076,10 +7082,10 @@
         <v>143</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="D3" s="35"/>
       <c r="E3" s="35"/>
@@ -7110,64 +7116,64 @@
         <v>93</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="G4" s="36" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="H4" s="36" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="I4" s="36" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="K4" s="36" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="L4" s="36" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="M4" s="36" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="N4" s="36" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="O4" s="36" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="P4" s="36" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="Q4" s="36" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="R4" s="36" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="S4" s="36" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="T4" s="36" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="U4" s="43" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="V4" s="36"/>
       <c r="W4" s="42"/>
@@ -7180,22 +7186,22 @@
         <v>136</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="H5" s="36"/>
       <c r="I5" s="36"/>
@@ -7222,19 +7228,19 @@
         <v>23</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
@@ -7262,13 +7268,13 @@
         <v>85</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="E7" s="35"/>
       <c r="F7" s="35"/>
@@ -7295,16 +7301,16 @@
     </row>
     <row r="8" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="35" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="E8" s="35" t="s">
         <v>245</v>
@@ -7336,13 +7342,13 @@
         <v>28</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="E9" s="35"/>
       <c r="F9" s="35"/>
@@ -7369,25 +7375,25 @@
     </row>
     <row r="10" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="35" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="G10" s="36" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="H10" s="36"/>
       <c r="I10" s="36"/>
@@ -7414,10 +7420,10 @@
         <v>111</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
@@ -7445,28 +7451,28 @@
     </row>
     <row r="12" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="37" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="G12" s="36" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="H12" s="36" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="I12" s="36"/>
       <c r="J12" s="36"/>
@@ -7492,10 +7498,10 @@
         <v>42</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="37"/>
@@ -7526,16 +7532,16 @@
         <v>97</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="F14" s="37"/>
       <c r="G14" s="36"/>
@@ -7564,96 +7570,96 @@
         <v>6</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="G15" s="36" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="H15" s="36" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="I15" s="36" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="J15" s="36" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="K15" s="36" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="L15" s="36" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="M15" s="36" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="N15" s="36" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="O15" s="36" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="P15" s="36" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="Q15" s="36" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="R15" s="36" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="S15" s="36" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="T15" s="36" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="U15" s="36" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="V15" s="36" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="W15" s="36" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="X15" s="36" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="Y15" s="36" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="Z15" s="44" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="37" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="C16" s="37" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="F16" s="37"/>
       <c r="G16" s="36"/>
@@ -7679,13 +7685,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="37" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="37"/>
@@ -7716,7 +7722,7 @@
         <v>125</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="C18" s="37"/>
       <c r="D18" s="37"/>
@@ -7745,10 +7751,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="37" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
@@ -7780,7 +7786,7 @@
         <v>182</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="37"/>
@@ -7809,10 +7815,10 @@
     </row>
     <row r="21" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="37" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="37"/>
@@ -7844,28 +7850,28 @@
         <v>74</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="M22" s="36"/>
       <c r="N22" s="36"/>
@@ -7884,10 +7890,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="37" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="C23" s="37"/>
       <c r="D23" s="37"/>
@@ -7919,28 +7925,28 @@
         <v>99</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="G24" s="36" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="H24" s="36" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="J24" s="36"/>
       <c r="K24" s="36"/>
@@ -7965,7 +7971,7 @@
         <v>262</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="C25" s="37"/>
       <c r="D25" s="37"/>
@@ -7997,10 +8003,10 @@
         <v>46</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="D26" s="37"/>
       <c r="E26" s="37"/>
@@ -8028,10 +8034,10 @@
     </row>
     <row r="27" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="37" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="C27" s="37"/>
       <c r="D27" s="37"/>
@@ -8063,7 +8069,7 @@
         <v>202</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="C28" s="37"/>
       <c r="D28" s="37"/>
@@ -8095,7 +8101,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="C29" s="37"/>
       <c r="D29" s="37"/>
@@ -8127,7 +8133,7 @@
         <v>140</v>
       </c>
       <c r="B30" s="37" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="C30" s="37"/>
       <c r="D30" s="37"/>
@@ -8159,76 +8165,76 @@
         <v>8</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="C31" s="36" t="s">
+        <v>1600</v>
+      </c>
+      <c r="D31" s="36" t="s">
+        <v>1595</v>
+      </c>
+      <c r="E31" s="36" t="s">
+        <v>1601</v>
+      </c>
+      <c r="F31" s="37" t="s">
+        <v>1597</v>
+      </c>
+      <c r="G31" s="37" t="s">
+        <v>1531</v>
+      </c>
+      <c r="H31" s="37" t="s">
         <v>1598</v>
       </c>
-      <c r="D31" s="36" t="s">
-        <v>1593</v>
-      </c>
-      <c r="E31" s="36" t="s">
-        <v>1599</v>
-      </c>
-      <c r="F31" s="37" t="s">
-        <v>1595</v>
-      </c>
-      <c r="G31" s="37" t="s">
-        <v>1529</v>
-      </c>
-      <c r="H31" s="37" t="s">
-        <v>1596</v>
-      </c>
       <c r="I31" s="37" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="J31" s="37" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="K31" s="37" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="L31" s="37" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="M31" s="37" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="N31" s="36" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="O31" s="37" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="P31" s="36" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="Q31" s="36" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="R31" s="36" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="S31" s="36" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="T31" s="36" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="U31" s="36" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="V31" s="36" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="W31" s="36" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="X31" s="36" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="Y31" s="36" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
@@ -8278,79 +8284,79 @@
         <v>3</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="J33" s="36" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="K33" s="36" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="L33" s="36" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="M33" s="36" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="N33" s="36" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="O33" s="36" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="P33" s="36" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="Q33" s="37" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="R33" s="37" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="S33" s="37" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="T33" s="36" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="U33" s="36" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="V33" s="36" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="W33" s="36" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="X33" s="36" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="Y33" s="36" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="Z33" s="36" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
@@ -8365,10 +8371,10 @@
     </row>
     <row r="34" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="37" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -8400,7 +8406,7 @@
         <v>282</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="C35" s="37"/>
       <c r="D35" s="37"/>
@@ -8432,7 +8438,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="37" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="C36" s="37"/>
       <c r="D36" s="37"/>
@@ -8461,10 +8467,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="37" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="B37" s="37" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="C37" s="37"/>
       <c r="D37" s="37"/>
@@ -8496,16 +8502,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="F38" s="37"/>
       <c r="G38" s="36"/>
@@ -8534,22 +8540,22 @@
         <v>95</v>
       </c>
       <c r="B39" s="37" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="C39" s="37" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="G39" s="36" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="H39" s="36"/>
       <c r="I39" s="36"/>
@@ -8573,25 +8579,25 @@
     </row>
     <row r="40" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="37" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="B40" s="37" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="G40" s="36" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="H40" s="36"/>
       <c r="I40" s="36"/>
@@ -8615,10 +8621,10 @@
     </row>
     <row r="41" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="37" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="B41" s="37" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="C41" s="37"/>
       <c r="D41" s="37"/>
@@ -8647,10 +8653,10 @@
     </row>
     <row r="42" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="37" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="B42" s="37" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="C42" s="37"/>
       <c r="D42" s="37"/>
@@ -8682,13 +8688,13 @@
         <v>123</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="D43" s="37" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="E43" s="37"/>
       <c r="F43" s="37"/>
@@ -8718,7 +8724,7 @@
         <v>228</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -8747,13 +8753,13 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="37" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="B45" s="37" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="C45" s="37" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="D45" s="37"/>
       <c r="E45" s="37"/>
@@ -8784,58 +8790,58 @@
         <v>456</v>
       </c>
       <c r="B46" s="37" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="C46" s="37" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="E46" s="37" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="G46" s="36" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="H46" s="36" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="I46" s="36" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="J46" s="36" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="K46" s="36" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="L46" s="36" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="M46" s="36" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="N46" s="36" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="O46" s="36" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="P46" s="36" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="Q46" s="36" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="R46" s="36" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="S46" s="36" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="T46" s="36"/>
       <c r="U46" s="36"/>
@@ -8870,10 +8876,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="46" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="B1" s="46" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10935,7 +10941,7 @@
     <tabColor rgb="FF2F5496"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B161"/>
+  <dimension ref="A1:B162"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
@@ -12228,6 +12234,14 @@
       </c>
       <c r="B161" s="13" t="s">
         <v>828</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="B162" s="13" t="s">
+        <v>830</v>
       </c>
     </row>
   </sheetData>
@@ -12256,866 +12270,866 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="14" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="14" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="14" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="14" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="14" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="14" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="14" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="14" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="14" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="14" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="14" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="14" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="14" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="14" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="14" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="16" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="14" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="14" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="14" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="14" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="14" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="14" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="14" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="14" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="B67" s="14" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="14" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="14" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B69" s="14" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="14" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="16" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="14" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="14" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="16" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="14" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="14" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="14" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="B77" s="14" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="14" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="16" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="B79" s="14" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="14" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="14" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="14" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="B82" s="14" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="16" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="B83" s="14" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="14" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="B84" s="14" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="14" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="B85" s="14" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="14" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="B86" s="14" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="14" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="B87" s="14" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="14" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="14" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="B89" s="14" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="14" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="B90" s="14" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="14" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="16" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="B92" s="14" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="14" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="B93" s="14" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="14" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="B94" s="14" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="17" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="B95" s="14" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="16" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B96" s="18" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="14" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="B97" s="18" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="14" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="B98" s="18" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="14" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="B99" s="18" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="16" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="B100" s="18" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="14" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B101" s="18" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="14" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="B102" s="18" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="16" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="B103" s="18" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="14" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="B104" s="18" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="14" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="B105" s="18" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="19" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="B106" s="19" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="19" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="B107" s="19" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="19" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="B108" s="19" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
     </row>
   </sheetData>
@@ -13190,7 +13204,7 @@
         <v>93</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="F1" s="20" t="s">
         <v>43</v>
@@ -13205,7 +13219,7 @@
         <v>136</v>
       </c>
       <c r="J1" s="20" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="K1" s="20" t="s">
         <v>28</v>
@@ -13214,19 +13228,19 @@
         <v>111</v>
       </c>
       <c r="M1" s="20" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="N1" s="20" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="O1" s="20" t="s">
         <v>143</v>
       </c>
       <c r="P1" s="20" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="Q1" s="20" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="R1" s="21" t="s">
         <v>350</v>
@@ -13238,10 +13252,10 @@
         <v>97</v>
       </c>
       <c r="U1" s="21" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="V1" s="21" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="W1" s="21" t="s">
         <v>99</v>
@@ -13250,13 +13264,13 @@
         <v>128</v>
       </c>
       <c r="Y1" s="21" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="Z1" s="21" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="AA1" s="21" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="AB1" s="21" t="s">
         <v>182</v>
@@ -13271,7 +13285,7 @@
         <v>228</v>
       </c>
       <c r="AF1" s="21" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="AG1" s="21" t="s">
         <v>85</v>
@@ -13300,570 +13314,570 @@
     </row>
     <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="F2" s="10" t="s">
+        <v>1063</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>1064</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>1065</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>1066</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>1067</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>1068</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>1069</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>1070</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>1071</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>1071</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>1072</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>1073</v>
+      </c>
+      <c r="R2" s="10" t="s">
+        <v>1062</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>1061</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="V2" s="10" t="s">
         <v>1062</v>
       </c>
-      <c r="H2" s="10" t="s">
-        <v>1063</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>1064</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>1065</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>1066</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>1067</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>1068</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>1069</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>1069</v>
-      </c>
-      <c r="P2" s="10" t="s">
-        <v>1070</v>
-      </c>
-      <c r="Q2" s="10" t="s">
-        <v>1071</v>
-      </c>
-      <c r="R2" s="10" t="s">
-        <v>1060</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>1073</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>1059</v>
-      </c>
-      <c r="V2" s="10" t="s">
-        <v>1060</v>
-      </c>
       <c r="W2" s="1" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>456</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="AB2" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="AD2" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="AE2" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="AG2" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="AN2" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="J3" s="10" t="s">
         <v>456</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="N3" s="10" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="O3" s="10" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="P3" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="Q3" s="10" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="R3" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="S3" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="U3" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="V3" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="X3" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="Y3" s="10" t="s">
+        <v>1062</v>
+      </c>
+      <c r="Z3" s="10" t="s">
+        <v>1062</v>
+      </c>
+      <c r="AA3" s="10" t="s">
+        <v>1062</v>
+      </c>
+      <c r="AB3" s="10" t="s">
         <v>1095</v>
       </c>
-      <c r="Y3" s="10" t="s">
-        <v>1060</v>
-      </c>
-      <c r="Z3" s="10" t="s">
-        <v>1060</v>
-      </c>
-      <c r="AA3" s="10" t="s">
-        <v>1060</v>
-      </c>
-      <c r="AB3" s="10" t="s">
-        <v>1093</v>
-      </c>
       <c r="AC3" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="AD3" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="AE3" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="AG3" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="AH3" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="AI3" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="AJ3" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="AK3" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="AL3" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="AM3" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="AN3" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>1104</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>1099</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>1100</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>1101</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>1102</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>1097</v>
-      </c>
       <c r="H4" s="10" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="O4" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="P4" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="Q4" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="R4" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="S4" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="T4" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="U4" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="V4" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="Y4" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="Z4" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="AA4" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="AB4" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="AC4" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="AD4" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="AE4" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="AF4" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="AG4" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="AH4" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="AI4" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="AJ4" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="AK4" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="AL4" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="AM4" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="AN4" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="H5" s="10" t="s">
         <v>456</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="O5" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="Q5" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="S5" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="T5" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="U5" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="Y5" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="Z5" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="AA5" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="AB5" s="10"/>
       <c r="AC5" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="AD5" s="10"/>
       <c r="AF5" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="AH5" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="AK5" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="AL5" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="AM5" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="K6" s="10" t="s">
+        <v>1123</v>
+      </c>
+      <c r="L6" s="10" t="s">
         <v>1121</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>1119</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="O6" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="P6" s="22"/>
       <c r="Q6" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="T6" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="AF6" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="K7" s="10" t="s">
+        <v>1130</v>
+      </c>
+      <c r="L7" s="10" t="s">
         <v>1128</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>1126</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
@@ -13871,44 +13885,44 @@
       <c r="P7" s="22"/>
       <c r="Q7" s="22"/>
       <c r="W7" s="1" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="I8" s="22"/>
       <c r="J8" s="22"/>
       <c r="K8" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
@@ -13916,44 +13930,44 @@
       <c r="P8" s="22"/>
       <c r="Q8" s="22"/>
       <c r="W8" s="1" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="X8" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="I9" s="22"/>
       <c r="J9" s="22"/>
       <c r="K9" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="M9" s="22"/>
       <c r="N9" s="22"/>
@@ -13961,42 +13975,42 @@
       <c r="P9" s="22"/>
       <c r="Q9" s="22"/>
       <c r="W9" s="1" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="X9" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="E10" s="22"/>
       <c r="F10" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="I10" s="22"/>
       <c r="J10" s="22"/>
       <c r="K10" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="M10" s="22"/>
       <c r="N10" s="22"/>
@@ -14004,38 +14018,38 @@
       <c r="P10" s="22"/>
       <c r="Q10" s="22"/>
       <c r="W10" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="X10" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="E11" s="22"/>
       <c r="F11" s="22"/>
       <c r="G11" s="10" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="I11" s="22"/>
       <c r="J11" s="22"/>
       <c r="K11" s="22"/>
       <c r="L11" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="M11" s="22"/>
       <c r="N11" s="22"/>
@@ -14043,29 +14057,29 @@
       <c r="P11" s="22"/>
       <c r="Q11" s="22"/>
       <c r="W11" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="E12" s="22"/>
       <c r="F12" s="22"/>
       <c r="G12" s="10" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="I12" s="22"/>
       <c r="J12" s="22"/>
@@ -14077,29 +14091,29 @@
       <c r="P12" s="22"/>
       <c r="Q12" s="22"/>
       <c r="W12" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="E13" s="22"/>
       <c r="F13" s="22"/>
       <c r="G13" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="I13" s="22"/>
       <c r="J13" s="22"/>
@@ -14113,24 +14127,24 @@
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="E14" s="22"/>
       <c r="F14" s="22"/>
       <c r="G14" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="I14" s="22"/>
       <c r="J14" s="22"/>
@@ -14144,24 +14158,24 @@
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="E15" s="22"/>
       <c r="F15" s="22"/>
       <c r="G15" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="I15" s="22"/>
       <c r="J15" s="22"/>
@@ -14175,20 +14189,20 @@
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
       <c r="F16" s="22"/>
       <c r="G16" s="22"/>
       <c r="H16" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="I16" s="22"/>
       <c r="J16" s="22"/>
@@ -14202,20 +14216,20 @@
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="D17" s="22"/>
       <c r="E17" s="22"/>
       <c r="F17" s="22"/>
       <c r="G17" s="22"/>
       <c r="H17" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="I17" s="22"/>
       <c r="J17" s="22"/>
@@ -14229,13 +14243,13 @@
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="D18" s="22"/>
       <c r="E18" s="22"/>
@@ -14254,13 +14268,13 @@
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="D19" s="22"/>
       <c r="E19" s="22"/>
@@ -14279,13 +14293,13 @@
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="D20" s="22"/>
       <c r="E20" s="22"/>
@@ -14304,13 +14318,13 @@
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="D21" s="22"/>
       <c r="E21" s="22"/>
@@ -14329,13 +14343,13 @@
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="22"/>
@@ -14354,13 +14368,13 @@
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="D23" s="22"/>
       <c r="E23" s="22"/>
@@ -14379,13 +14393,13 @@
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="D24" s="22"/>
       <c r="E24" s="22"/>
@@ -14404,13 +14418,13 @@
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="D25" s="22"/>
       <c r="E25" s="22"/>
@@ -14429,13 +14443,13 @@
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="22"/>
@@ -14454,13 +14468,13 @@
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="D27" s="22"/>
       <c r="E27" s="22"/>
@@ -14479,13 +14493,13 @@
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="D28" s="22"/>
       <c r="E28" s="22"/>
@@ -14504,13 +14518,13 @@
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="D29" s="22"/>
       <c r="E29" s="22"/>
@@ -14529,13 +14543,13 @@
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="D30" s="22"/>
       <c r="E30" s="22"/>
@@ -14554,13 +14568,13 @@
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="D31" s="22"/>
       <c r="E31" s="22"/>
@@ -14579,13 +14593,13 @@
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="D32" s="22"/>
       <c r="E32" s="22"/>
@@ -14604,13 +14618,13 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="D33" s="22"/>
       <c r="E33" s="22"/>
@@ -14629,13 +14643,13 @@
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="B34" s="22" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="D34" s="22"/>
       <c r="E34" s="22"/>
@@ -14654,13 +14668,13 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="D35" s="22"/>
       <c r="E35" s="22"/>
@@ -14679,13 +14693,13 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="D36" s="22"/>
       <c r="E36" s="22"/>
@@ -14704,10 +14718,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="C37" s="22"/>
       <c r="D37" s="22"/>
@@ -14727,10 +14741,10 @@
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="C38" s="22"/>
       <c r="D38" s="22"/>
@@ -14750,10 +14764,10 @@
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="C39" s="22"/>
       <c r="D39" s="22"/>
@@ -14773,7 +14787,7 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="B40" s="22"/>
       <c r="C40" s="22"/>
@@ -14794,7 +14808,7 @@
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="B41" s="22"/>
       <c r="C41" s="22"/>
@@ -14815,7 +14829,7 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
     </row>
   </sheetData>
@@ -14843,92 +14857,92 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="24" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="24" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14938,7 +14952,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
     </row>
   </sheetData>
@@ -14967,159 +14981,159 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B16" s="23" t="s">
         <v>1249</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>1247</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="B20" s="23"/>
     </row>
@@ -15151,31 +15165,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="E1" s="26"/>
     </row>
     <row r="2" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="E2" s="28"/>
     </row>
@@ -15184,13 +15198,13 @@
         <v>143</v>
       </c>
       <c r="B3" s="27" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C3" s="27" t="s">
         <v>1262</v>
       </c>
-      <c r="C3" s="27" t="s">
-        <v>1260</v>
-      </c>
       <c r="D3" s="27" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="E3" s="28"/>
     </row>
@@ -15199,43 +15213,43 @@
         <v>93</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="E4" s="28"/>
     </row>
     <row r="5" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="E5" s="28"/>
     </row>
     <row r="6" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="E6" s="28"/>
     </row>
@@ -15244,13 +15258,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="E7" s="28"/>
     </row>
@@ -15259,43 +15273,43 @@
         <v>28</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="E8" s="28"/>
     </row>
     <row r="9" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="B9" s="27" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D9" s="27" t="s">
         <v>1272</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>1273</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>1270</v>
       </c>
       <c r="E9" s="28"/>
     </row>
     <row r="10" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="E10" s="28"/>
     </row>
@@ -15304,73 +15318,73 @@
         <v>111</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="E11" s="28"/>
     </row>
     <row r="12" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="E12" s="28"/>
     </row>
     <row r="13" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="E13" s="28"/>
     </row>
     <row r="14" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="E14" s="28"/>
     </row>
     <row r="15" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="E15" s="28"/>
     </row>
@@ -15379,13 +15393,13 @@
         <v>97</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="E16" s="28"/>
     </row>
@@ -15394,13 +15408,13 @@
         <v>6</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="E17" s="28"/>
     </row>
@@ -15409,22 +15423,22 @@
         <v>43</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="E18" s="28"/>
     </row>
     <row r="19" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="C19" s="27"/>
       <c r="D19" s="27"/>
@@ -15432,16 +15446,16 @@
     </row>
     <row r="20" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="27" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D20" s="27" t="s">
         <v>1301</v>
-      </c>
-      <c r="B20" s="27" t="s">
-        <v>1297</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>1298</v>
-      </c>
-      <c r="D20" s="27" t="s">
-        <v>1299</v>
       </c>
       <c r="E20" s="28"/>
     </row>
@@ -15450,13 +15464,13 @@
         <v>125</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="E21" s="28"/>
     </row>
@@ -15465,43 +15479,43 @@
         <v>182</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="E22" s="28"/>
     </row>
     <row r="23" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="30" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="B23" s="31" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D23" s="27" t="s">
         <v>1307</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>1308</v>
-      </c>
-      <c r="D23" s="27" t="s">
-        <v>1305</v>
       </c>
       <c r="E23" s="28"/>
     </row>
     <row r="24" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="E24" s="28"/>
     </row>
@@ -15510,67 +15524,67 @@
         <v>74</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="E25" s="28"/>
     </row>
     <row r="26" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="27" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="B26" s="30" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="E26" s="28"/>
     </row>
     <row r="27" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="B27" s="27" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D27" s="27" t="s">
         <v>1285</v>
-      </c>
-      <c r="C27" s="27" t="s">
-        <v>1282</v>
-      </c>
-      <c r="D27" s="27" t="s">
-        <v>1283</v>
       </c>
       <c r="E27" s="28"/>
     </row>
     <row r="28" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="27" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="E28" s="28"/>
     </row>
     <row r="29" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="C29" s="27"/>
       <c r="D29" s="27"/>
@@ -15581,7 +15595,7 @@
         <v>160</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="C30" s="27"/>
       <c r="D30" s="27"/>
@@ -15592,13 +15606,13 @@
         <v>99</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="E31" s="28"/>
     </row>
@@ -15607,7 +15621,7 @@
         <v>262</v>
       </c>
       <c r="B32" s="32" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
@@ -15615,16 +15629,16 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="26" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="E33" s="26"/>
     </row>
@@ -15633,7 +15647,7 @@
         <v>46</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C34" s="26"/>
       <c r="D34" s="26"/>
@@ -15641,10 +15655,10 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="26" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="C35" s="26"/>
       <c r="D35" s="26"/>
@@ -15652,16 +15666,16 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="26" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="E36" s="26"/>
     </row>
@@ -15670,7 +15684,7 @@
         <v>202</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="C37" s="26"/>
       <c r="D37" s="26"/>
@@ -15681,7 +15695,7 @@
         <v>205</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="C38" s="26"/>
       <c r="D38" s="26"/>
@@ -15692,7 +15706,7 @@
         <v>140</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="C39" s="26"/>
       <c r="D39" s="26"/>
@@ -15700,25 +15714,25 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="26" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="E40" s="26"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="26" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="C41" s="26"/>
       <c r="D41" s="26"/>
@@ -15726,16 +15740,16 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="26" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="B42" s="26" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="D42" s="26" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="E42" s="26"/>
     </row>
@@ -15744,7 +15758,7 @@
         <v>350</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="C43" s="26"/>
       <c r="D43" s="26"/>
@@ -15752,34 +15766,34 @@
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="26" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="E44" s="26"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="26" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="C45" s="26" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D45" s="26" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E45" s="26" t="s">
         <v>1302</v>
-      </c>
-      <c r="D45" s="26" t="s">
-        <v>1303</v>
-      </c>
-      <c r="E45" s="26" t="s">
-        <v>1300</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15787,7 +15801,7 @@
         <v>133</v>
       </c>
       <c r="B46" s="26" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="C46" s="26"/>
       <c r="D46" s="26"/>
@@ -15795,10 +15809,10 @@
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="26" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="C47" s="26"/>
       <c r="D47" s="26"/>
@@ -15809,7 +15823,7 @@
         <v>128</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="C48" s="26"/>
       <c r="D48" s="26"/>
@@ -15820,67 +15834,67 @@
         <v>95</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="E49" s="26"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="26" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="D50" s="26" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="E50" s="26"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="26" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="D51" s="26" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="E51" s="26"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="26" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="B52" s="26" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="C52" s="26" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="D52" s="26" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="E52" s="26"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="26" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="C53" s="26"/>
       <c r="D53" s="26"/>
@@ -15888,10 +15902,10 @@
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="26" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="C54" s="26"/>
       <c r="D54" s="26"/>
@@ -15899,10 +15913,10 @@
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="26" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="C55" s="26"/>
       <c r="D55" s="26"/>
@@ -15910,10 +15924,10 @@
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="26" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="C56" s="26"/>
       <c r="D56" s="26"/>
@@ -15921,10 +15935,10 @@
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="26" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="C57" s="26"/>
       <c r="D57" s="26"/>
@@ -15932,10 +15946,10 @@
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="26" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="C58" s="26"/>
       <c r="D58" s="26"/>
@@ -15946,10 +15960,10 @@
         <v>456</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="D59" s="26"/>
       <c r="E59" s="26"/>
@@ -15983,99 +15997,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="34" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="C1" s="34" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="D1" s="34" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="E1" s="34" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="F1" s="34" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="G1" s="34" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="H1" s="34" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="I1" s="34" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="J1" s="34" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="K1" s="34" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="L1" s="34" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="M1" s="34" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="N1" s="34" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="O1" s="34" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="P1" s="34" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="Q1" s="34" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="R1" s="34" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="S1" s="34" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="T1" s="34" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="U1" s="34" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="V1" s="34" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="W1" s="34" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="X1" s="34" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="Y1" s="34" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="Z1" s="34" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="35" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="E2" s="35" t="s">
         <v>160</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="G2" s="36"/>
       <c r="H2" s="36"/>
@@ -16103,7 +16117,7 @@
         <v>143</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="C3" s="35"/>
       <c r="D3" s="35"/>
@@ -16135,64 +16149,64 @@
         <v>93</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="G4" s="36" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="H4" s="36" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="I4" s="36" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="K4" s="36" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="L4" s="36" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="M4" s="36" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="N4" s="36" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="O4" s="36" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="P4" s="36" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="Q4" s="36" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="R4" s="36" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="S4" s="36" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="T4" s="36" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="U4" s="36" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="V4" s="36"/>
       <c r="W4" s="36"/>
@@ -16205,22 +16219,22 @@
         <v>136</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="H5" s="36"/>
       <c r="I5" s="36"/>
@@ -16250,16 +16264,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
@@ -16290,25 +16304,25 @@
         <v>5</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="G7" s="36" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="H7" s="36" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="I7" s="36" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="J7" s="36"/>
       <c r="K7" s="36"/>
@@ -16330,16 +16344,16 @@
     </row>
     <row r="8" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="35" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="E8" s="35" t="s">
         <v>245</v>
@@ -16371,13 +16385,13 @@
         <v>28</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="E9" s="35"/>
       <c r="F9" s="35"/>
@@ -16404,25 +16418,25 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="35" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="G10" s="36" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="H10" s="36"/>
       <c r="I10" s="36"/>
@@ -16449,10 +16463,10 @@
         <v>111</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
@@ -16480,28 +16494,28 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="37" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="G12" s="36" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="H12" s="36" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="I12" s="36"/>
       <c r="J12" s="36"/>
@@ -16527,10 +16541,10 @@
         <v>42</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="37"/>
@@ -16561,16 +16575,16 @@
         <v>97</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="F14" s="37"/>
       <c r="G14" s="36"/>
@@ -16602,25 +16616,25 @@
         <v>5</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="G15" s="36" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="H15" s="36" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="I15" s="36" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="J15" s="36"/>
       <c r="K15" s="36"/>
@@ -16642,19 +16656,19 @@
     </row>
     <row r="16" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="37" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="C16" s="37" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="F16" s="37"/>
       <c r="G16" s="36"/>
@@ -16680,13 +16694,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="37" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="37"/>
@@ -16717,7 +16731,7 @@
         <v>125</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="C18" s="37"/>
       <c r="D18" s="37"/>
@@ -16746,10 +16760,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="37" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
@@ -16781,7 +16795,7 @@
         <v>182</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="37"/>
@@ -16810,10 +16824,10 @@
     </row>
     <row r="21" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="37" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="37"/>
@@ -16848,43 +16862,43 @@
         <v>5</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="G22" s="36" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="H22" s="36" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="I22" s="36" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="J22" s="36" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="K22" s="36" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="L22" s="36" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="M22" s="36" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="N22" s="36" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="O22" s="36" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="P22" s="36"/>
       <c r="Q22" s="36"/>
@@ -16900,10 +16914,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="37" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="C23" s="37"/>
       <c r="D23" s="37"/>
@@ -16935,28 +16949,28 @@
         <v>99</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="G24" s="36" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="H24" s="36" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="J24" s="36"/>
       <c r="K24" s="36"/>
@@ -16981,7 +16995,7 @@
         <v>262</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="C25" s="37"/>
       <c r="D25" s="37"/>
@@ -17013,10 +17027,10 @@
         <v>46</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="D26" s="37"/>
       <c r="E26" s="37"/>
@@ -17044,10 +17058,10 @@
     </row>
     <row r="27" customFormat="false" ht="31.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="37" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="C27" s="37"/>
       <c r="D27" s="37"/>
@@ -17079,7 +17093,7 @@
         <v>202</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="C28" s="37"/>
       <c r="D28" s="37"/>
@@ -17111,7 +17125,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="C29" s="37"/>
       <c r="D29" s="37"/>
@@ -17143,7 +17157,7 @@
         <v>140</v>
       </c>
       <c r="B30" s="37" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="C30" s="37"/>
       <c r="D30" s="37"/>
@@ -17178,25 +17192,25 @@
         <v>5</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="D31" s="36" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="G31" s="36" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="H31" s="36" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="I31" s="36" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="J31" s="37"/>
       <c r="K31" s="37"/>
@@ -17256,43 +17270,43 @@
         <v>5</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="G33" s="36" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="H33" s="36" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="I33" s="36" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="J33" s="36" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="K33" s="36" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="L33" s="36" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="M33" s="36" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="N33" s="36" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="O33" s="36" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="P33" s="36"/>
       <c r="Q33" s="37"/>
@@ -17308,10 +17322,10 @@
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="37" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -17343,7 +17357,7 @@
         <v>282</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="C35" s="37"/>
       <c r="D35" s="37"/>
@@ -17375,7 +17389,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="37" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="C36" s="37"/>
       <c r="D36" s="37"/>
@@ -17404,10 +17418,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="37" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="B37" s="37" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="C37" s="37"/>
       <c r="D37" s="37"/>
@@ -17439,16 +17453,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="F38" s="37"/>
       <c r="G38" s="36"/>
@@ -17477,22 +17491,22 @@
         <v>95</v>
       </c>
       <c r="B39" s="37" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="C39" s="37" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="G39" s="36" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="H39" s="36"/>
       <c r="I39" s="36"/>
@@ -17516,25 +17530,25 @@
     </row>
     <row r="40" customFormat="false" ht="31.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="37" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="B40" s="37" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="G40" s="36" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="H40" s="36"/>
       <c r="I40" s="36"/>
@@ -17558,10 +17572,10 @@
     </row>
     <row r="41" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="37" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="B41" s="37" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="C41" s="37"/>
       <c r="D41" s="37"/>
@@ -17590,10 +17604,10 @@
     </row>
     <row r="42" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="37" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="B42" s="37" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="C42" s="37"/>
       <c r="D42" s="37"/>
@@ -17625,13 +17639,13 @@
         <v>123</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="D43" s="37" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="E43" s="37"/>
       <c r="F43" s="37"/>
@@ -17661,7 +17675,7 @@
         <v>228</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -17690,13 +17704,13 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="37" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="B45" s="37" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="C45" s="37" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="D45" s="37"/>
       <c r="E45" s="37"/>
@@ -17727,58 +17741,58 @@
         <v>456</v>
       </c>
       <c r="B46" s="37" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="C46" s="37" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="E46" s="37" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="G46" s="36" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="H46" s="36" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="I46" s="36" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="J46" s="36" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="K46" s="36" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="L46" s="36" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="M46" s="36" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="N46" s="36" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="O46" s="36" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="P46" s="36" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="Q46" s="36" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="R46" s="36" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="S46" s="36" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="T46" s="36"/>
       <c r="U46" s="36"/>

--- a/REFERENCE.xlsx
+++ b/REFERENCE.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2463" uniqueCount="1624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2469" uniqueCount="1630">
   <si>
     <t xml:space="preserve">MATERIAL NAME</t>
   </si>
@@ -2526,6 +2526,12 @@
     <t xml:space="preserve">C161</t>
   </si>
   <si>
+    <t xml:space="preserve">CLAY BROWN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C162</t>
+  </si>
+  <si>
     <t xml:space="preserve">RAL COLOUR NAME</t>
   </si>
   <si>
@@ -3169,6 +3175,18 @@
   </si>
   <si>
     <t xml:space="preserve">R206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAL 8022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAL 4647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R208</t>
   </si>
   <si>
     <t xml:space="preserve">TEAKWOOD</t>
@@ -6759,178 +6777,178 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="38" t="s">
-        <v>1504</v>
+        <v>1510</v>
       </c>
       <c r="B1" s="38" t="s">
-        <v>1505</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="39" t="s">
-        <v>1226</v>
+        <v>1232</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>1506</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="39" t="s">
-        <v>1507</v>
+        <v>1513</v>
       </c>
       <c r="B3" s="40" t="s">
-        <v>1508</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="39" t="s">
-        <v>1509</v>
+        <v>1515</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>1510</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="39" t="s">
-        <v>1247</v>
+        <v>1253</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>1511</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="39" t="s">
-        <v>1512</v>
+        <v>1518</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>1513</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="39" t="s">
-        <v>1514</v>
+        <v>1520</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>1515</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="39" t="s">
-        <v>1516</v>
+        <v>1522</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>1517</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="39" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>1278</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="39" t="s">
-        <v>1518</v>
+        <v>1524</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>1413</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="39" t="s">
-        <v>1519</v>
+        <v>1525</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>1520</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="39" t="s">
-        <v>1521</v>
+        <v>1527</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>1522</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="39" t="s">
-        <v>1523</v>
+        <v>1529</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>1524</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="39" t="s">
-        <v>1243</v>
+        <v>1249</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="39" t="s">
-        <v>1525</v>
+        <v>1531</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>1526</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="39" t="s">
-        <v>1527</v>
+        <v>1533</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>1528</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="39" t="s">
-        <v>1253</v>
+        <v>1259</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>1529</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="39" t="s">
-        <v>1530</v>
+        <v>1536</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>1531</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="39" t="s">
-        <v>1532</v>
+        <v>1538</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>1533</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="39" t="s">
-        <v>1534</v>
+        <v>1540</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>1535</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="39" t="s">
-        <v>1536</v>
+        <v>1542</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>1537</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="39" t="s">
-        <v>1233</v>
+        <v>1239</v>
       </c>
       <c r="B22" s="40" t="s">
-        <v>1538</v>
+        <v>1544</v>
       </c>
     </row>
   </sheetData>
@@ -6962,99 +6980,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="41" t="s">
-        <v>1539</v>
+        <v>1545</v>
       </c>
       <c r="C1" s="41" t="s">
-        <v>1540</v>
+        <v>1546</v>
       </c>
       <c r="D1" s="41" t="s">
-        <v>1541</v>
+        <v>1547</v>
       </c>
       <c r="E1" s="41" t="s">
-        <v>1542</v>
+        <v>1548</v>
       </c>
       <c r="F1" s="41" t="s">
-        <v>1543</v>
+        <v>1549</v>
       </c>
       <c r="G1" s="41" t="s">
-        <v>1544</v>
+        <v>1550</v>
       </c>
       <c r="H1" s="41" t="s">
-        <v>1545</v>
+        <v>1551</v>
       </c>
       <c r="I1" s="41" t="s">
-        <v>1546</v>
+        <v>1552</v>
       </c>
       <c r="J1" s="41" t="s">
-        <v>1547</v>
+        <v>1553</v>
       </c>
       <c r="K1" s="41" t="s">
-        <v>1548</v>
+        <v>1554</v>
       </c>
       <c r="L1" s="41" t="s">
-        <v>1549</v>
+        <v>1555</v>
       </c>
       <c r="M1" s="41" t="s">
-        <v>1550</v>
+        <v>1556</v>
       </c>
       <c r="N1" s="41" t="s">
-        <v>1551</v>
+        <v>1557</v>
       </c>
       <c r="O1" s="41" t="s">
-        <v>1552</v>
+        <v>1558</v>
       </c>
       <c r="P1" s="41" t="s">
-        <v>1553</v>
+        <v>1559</v>
       </c>
       <c r="Q1" s="41" t="s">
-        <v>1554</v>
+        <v>1560</v>
       </c>
       <c r="R1" s="41" t="s">
-        <v>1555</v>
+        <v>1561</v>
       </c>
       <c r="S1" s="41" t="s">
-        <v>1556</v>
+        <v>1562</v>
       </c>
       <c r="T1" s="41" t="s">
-        <v>1557</v>
+        <v>1563</v>
       </c>
       <c r="U1" s="41" t="s">
-        <v>1558</v>
+        <v>1564</v>
       </c>
       <c r="V1" s="41" t="s">
-        <v>1559</v>
+        <v>1565</v>
       </c>
       <c r="W1" s="41" t="s">
-        <v>1560</v>
+        <v>1566</v>
       </c>
       <c r="X1" s="41" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="Y1" s="41" t="s">
-        <v>1562</v>
+        <v>1568</v>
       </c>
       <c r="Z1" s="41" t="s">
-        <v>1563</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="35" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>1564</v>
+        <v>1570</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>1386</v>
+        <v>1392</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>1254</v>
+        <v>1260</v>
       </c>
       <c r="E2" s="35" t="s">
         <v>160</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>1387</v>
+        <v>1393</v>
       </c>
       <c r="G2" s="36"/>
       <c r="H2" s="36"/>
@@ -7082,10 +7100,10 @@
         <v>143</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>1565</v>
+        <v>1571</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>1566</v>
+        <v>1572</v>
       </c>
       <c r="D3" s="35"/>
       <c r="E3" s="35"/>
@@ -7116,64 +7134,64 @@
         <v>93</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>1387</v>
+        <v>1393</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>1254</v>
+        <v>1260</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1390</v>
+        <v>1396</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1391</v>
+        <v>1397</v>
       </c>
       <c r="G4" s="36" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="H4" s="36" t="s">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="I4" s="36" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>1395</v>
+        <v>1401</v>
       </c>
       <c r="K4" s="36" t="s">
-        <v>1396</v>
+        <v>1402</v>
       </c>
       <c r="L4" s="36" t="s">
-        <v>1397</v>
+        <v>1403</v>
       </c>
       <c r="M4" s="36" t="s">
-        <v>1398</v>
+        <v>1404</v>
       </c>
       <c r="N4" s="36" t="s">
-        <v>1399</v>
+        <v>1405</v>
       </c>
       <c r="O4" s="36" t="s">
-        <v>1400</v>
+        <v>1406</v>
       </c>
       <c r="P4" s="36" t="s">
-        <v>1401</v>
+        <v>1407</v>
       </c>
       <c r="Q4" s="36" t="s">
-        <v>1402</v>
+        <v>1408</v>
       </c>
       <c r="R4" s="36" t="s">
-        <v>1403</v>
+        <v>1409</v>
       </c>
       <c r="S4" s="36" t="s">
-        <v>1404</v>
+        <v>1410</v>
       </c>
       <c r="T4" s="36" t="s">
-        <v>1405</v>
+        <v>1411</v>
       </c>
       <c r="U4" s="43" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
       <c r="V4" s="36"/>
       <c r="W4" s="42"/>
@@ -7186,22 +7204,22 @@
         <v>136</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>1409</v>
+        <v>1415</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1410</v>
+        <v>1416</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1411</v>
+        <v>1417</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>1412</v>
+        <v>1418</v>
       </c>
       <c r="H5" s="36"/>
       <c r="I5" s="36"/>
@@ -7228,19 +7246,19 @@
         <v>23</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>1273</v>
+        <v>1279</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>1567</v>
+        <v>1573</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>1569</v>
+        <v>1575</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>1570</v>
+        <v>1576</v>
       </c>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
@@ -7268,13 +7286,13 @@
         <v>85</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>1571</v>
+        <v>1577</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>1228</v>
+        <v>1234</v>
       </c>
       <c r="E7" s="35"/>
       <c r="F7" s="35"/>
@@ -7301,16 +7319,16 @@
     </row>
     <row r="8" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="35" t="s">
-        <v>1418</v>
+        <v>1424</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>1419</v>
+        <v>1425</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>1420</v>
+        <v>1426</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="E8" s="35" t="s">
         <v>245</v>
@@ -7342,13 +7360,13 @@
         <v>28</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>1421</v>
+        <v>1427</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>1422</v>
+        <v>1428</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>1423</v>
+        <v>1429</v>
       </c>
       <c r="E9" s="35"/>
       <c r="F9" s="35"/>
@@ -7375,25 +7393,25 @@
     </row>
     <row r="10" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="35" t="s">
-        <v>1279</v>
+        <v>1285</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>1424</v>
+        <v>1430</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>1240</v>
+        <v>1246</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1425</v>
+        <v>1431</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1426</v>
+        <v>1432</v>
       </c>
       <c r="G10" s="36" t="s">
-        <v>1427</v>
+        <v>1433</v>
       </c>
       <c r="H10" s="36"/>
       <c r="I10" s="36"/>
@@ -7420,10 +7438,10 @@
         <v>111</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>1428</v>
+        <v>1434</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>1234</v>
+        <v>1240</v>
       </c>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
@@ -7451,28 +7469,28 @@
     </row>
     <row r="12" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="37" t="s">
-        <v>1049</v>
+        <v>1055</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>1429</v>
+        <v>1435</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>1430</v>
+        <v>1436</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>1431</v>
+        <v>1437</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>1432</v>
+        <v>1438</v>
       </c>
       <c r="G12" s="36" t="s">
-        <v>1228</v>
+        <v>1234</v>
       </c>
       <c r="H12" s="36" t="s">
-        <v>1433</v>
+        <v>1439</v>
       </c>
       <c r="I12" s="36"/>
       <c r="J12" s="36"/>
@@ -7498,10 +7516,10 @@
         <v>42</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>1246</v>
+        <v>1252</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>1228</v>
+        <v>1234</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="37"/>
@@ -7532,16 +7550,16 @@
         <v>97</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>1434</v>
+        <v>1440</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>1435</v>
+        <v>1441</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>1436</v>
+        <v>1442</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="F14" s="37"/>
       <c r="G14" s="36"/>
@@ -7570,96 +7588,96 @@
         <v>6</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>1572</v>
+        <v>1578</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>1573</v>
+        <v>1579</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>1574</v>
+        <v>1580</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>1575</v>
+        <v>1581</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>1576</v>
+        <v>1582</v>
       </c>
       <c r="G15" s="36" t="s">
-        <v>1577</v>
+        <v>1583</v>
       </c>
       <c r="H15" s="36" t="s">
-        <v>1578</v>
+        <v>1584</v>
       </c>
       <c r="I15" s="36" t="s">
-        <v>1579</v>
+        <v>1585</v>
       </c>
       <c r="J15" s="36" t="s">
-        <v>1580</v>
+        <v>1586</v>
       </c>
       <c r="K15" s="36" t="s">
-        <v>1411</v>
+        <v>1417</v>
       </c>
       <c r="L15" s="36" t="s">
-        <v>1581</v>
+        <v>1587</v>
       </c>
       <c r="M15" s="36" t="s">
-        <v>1582</v>
+        <v>1588</v>
       </c>
       <c r="N15" s="36" t="s">
-        <v>1583</v>
+        <v>1589</v>
       </c>
       <c r="O15" s="36" t="s">
-        <v>1584</v>
+        <v>1590</v>
       </c>
       <c r="P15" s="36" t="s">
-        <v>1585</v>
+        <v>1591</v>
       </c>
       <c r="Q15" s="36" t="s">
-        <v>1586</v>
+        <v>1592</v>
       </c>
       <c r="R15" s="36" t="s">
-        <v>1413</v>
+        <v>1419</v>
       </c>
       <c r="S15" s="36" t="s">
-        <v>1587</v>
+        <v>1593</v>
       </c>
       <c r="T15" s="36" t="s">
-        <v>1588</v>
+        <v>1594</v>
       </c>
       <c r="U15" s="36" t="s">
-        <v>1589</v>
+        <v>1595</v>
       </c>
       <c r="V15" s="36" t="s">
-        <v>1590</v>
+        <v>1596</v>
       </c>
       <c r="W15" s="36" t="s">
-        <v>1415</v>
+        <v>1421</v>
       </c>
       <c r="X15" s="36" t="s">
-        <v>1591</v>
+        <v>1597</v>
       </c>
       <c r="Y15" s="36" t="s">
-        <v>1592</v>
+        <v>1598</v>
       </c>
       <c r="Z15" s="44" t="s">
-        <v>1593</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="37" t="s">
-        <v>1438</v>
+        <v>1444</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>1439</v>
+        <v>1445</v>
       </c>
       <c r="C16" s="37" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>1234</v>
+        <v>1240</v>
       </c>
       <c r="F16" s="37"/>
       <c r="G16" s="36"/>
@@ -7685,13 +7703,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="37" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>1440</v>
+        <v>1446</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>1441</v>
+        <v>1447</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="37"/>
@@ -7722,7 +7740,7 @@
         <v>125</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>1442</v>
+        <v>1448</v>
       </c>
       <c r="C18" s="37"/>
       <c r="D18" s="37"/>
@@ -7751,10 +7769,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="37" t="s">
-        <v>1443</v>
+        <v>1449</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>1444</v>
+        <v>1450</v>
       </c>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
@@ -7786,7 +7804,7 @@
         <v>182</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>1445</v>
+        <v>1451</v>
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="37"/>
@@ -7815,10 +7833,10 @@
     </row>
     <row r="21" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="37" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>1446</v>
+        <v>1452</v>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="37"/>
@@ -7850,28 +7868,28 @@
         <v>74</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>1594</v>
+        <v>1600</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>1228</v>
+        <v>1234</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>1595</v>
+        <v>1601</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>1596</v>
+        <v>1602</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>1597</v>
+        <v>1603</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>1531</v>
+        <v>1537</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>1598</v>
+        <v>1604</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>1599</v>
+        <v>1605</v>
       </c>
       <c r="M22" s="36"/>
       <c r="N22" s="36"/>
@@ -7890,10 +7908,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="37" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>1453</v>
+        <v>1459</v>
       </c>
       <c r="C23" s="37"/>
       <c r="D23" s="37"/>
@@ -7925,28 +7943,28 @@
         <v>99</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>1457</v>
+        <v>1463</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>1458</v>
+        <v>1464</v>
       </c>
       <c r="G24" s="36" t="s">
-        <v>1459</v>
+        <v>1465</v>
       </c>
       <c r="H24" s="36" t="s">
-        <v>1460</v>
+        <v>1466</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>1461</v>
+        <v>1467</v>
       </c>
       <c r="J24" s="36"/>
       <c r="K24" s="36"/>
@@ -7971,7 +7989,7 @@
         <v>262</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="C25" s="37"/>
       <c r="D25" s="37"/>
@@ -8003,10 +8021,10 @@
         <v>46</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>1462</v>
+        <v>1468</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>1463</v>
+        <v>1469</v>
       </c>
       <c r="D26" s="37"/>
       <c r="E26" s="37"/>
@@ -8034,10 +8052,10 @@
     </row>
     <row r="27" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="37" t="s">
-        <v>1324</v>
+        <v>1330</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>1464</v>
+        <v>1470</v>
       </c>
       <c r="C27" s="37"/>
       <c r="D27" s="37"/>
@@ -8069,7 +8087,7 @@
         <v>202</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>1465</v>
+        <v>1471</v>
       </c>
       <c r="C28" s="37"/>
       <c r="D28" s="37"/>
@@ -8101,7 +8119,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>1466</v>
+        <v>1472</v>
       </c>
       <c r="C29" s="37"/>
       <c r="D29" s="37"/>
@@ -8133,7 +8151,7 @@
         <v>140</v>
       </c>
       <c r="B30" s="37" t="s">
-        <v>1429</v>
+        <v>1435</v>
       </c>
       <c r="C30" s="37"/>
       <c r="D30" s="37"/>
@@ -8165,76 +8183,76 @@
         <v>8</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>1594</v>
+        <v>1600</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>1600</v>
+        <v>1606</v>
       </c>
       <c r="D31" s="36" t="s">
-        <v>1595</v>
+        <v>1601</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>1601</v>
+        <v>1607</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>1597</v>
+        <v>1603</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>1531</v>
+        <v>1537</v>
       </c>
       <c r="H31" s="37" t="s">
-        <v>1598</v>
+        <v>1604</v>
       </c>
       <c r="I31" s="37" t="s">
-        <v>1602</v>
+        <v>1608</v>
       </c>
       <c r="J31" s="37" t="s">
-        <v>1603</v>
+        <v>1609</v>
       </c>
       <c r="K31" s="37" t="s">
-        <v>1604</v>
+        <v>1610</v>
       </c>
       <c r="L31" s="37" t="s">
-        <v>1605</v>
+        <v>1611</v>
       </c>
       <c r="M31" s="37" t="s">
-        <v>1606</v>
+        <v>1612</v>
       </c>
       <c r="N31" s="36" t="s">
-        <v>1607</v>
+        <v>1613</v>
       </c>
       <c r="O31" s="37" t="s">
-        <v>1608</v>
+        <v>1614</v>
       </c>
       <c r="P31" s="36" t="s">
-        <v>1419</v>
+        <v>1425</v>
       </c>
       <c r="Q31" s="36" t="s">
-        <v>1609</v>
+        <v>1615</v>
       </c>
       <c r="R31" s="36" t="s">
-        <v>1610</v>
+        <v>1616</v>
       </c>
       <c r="S31" s="36" t="s">
-        <v>1586</v>
+        <v>1592</v>
       </c>
       <c r="T31" s="36" t="s">
-        <v>1611</v>
+        <v>1617</v>
       </c>
       <c r="U31" s="36" t="s">
-        <v>1590</v>
+        <v>1596</v>
       </c>
       <c r="V31" s="36" t="s">
-        <v>1415</v>
+        <v>1421</v>
       </c>
       <c r="W31" s="36" t="s">
-        <v>1612</v>
+        <v>1618</v>
       </c>
       <c r="X31" s="36" t="s">
-        <v>1613</v>
+        <v>1619</v>
       </c>
       <c r="Y31" s="36" t="s">
-        <v>1614</v>
+        <v>1620</v>
       </c>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
@@ -8284,79 +8302,79 @@
         <v>3</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1594</v>
+        <v>1600</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>1228</v>
+        <v>1234</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>1595</v>
+        <v>1601</v>
       </c>
       <c r="E33" s="36" t="s">
+        <v>1602</v>
+      </c>
+      <c r="F33" s="37" t="s">
+        <v>1603</v>
+      </c>
+      <c r="G33" s="37" t="s">
+        <v>1537</v>
+      </c>
+      <c r="H33" s="37" t="s">
+        <v>1604</v>
+      </c>
+      <c r="I33" s="37" t="s">
+        <v>1605</v>
+      </c>
+      <c r="J33" s="36" t="s">
+        <v>1621</v>
+      </c>
+      <c r="K33" s="36" t="s">
+        <v>1453</v>
+      </c>
+      <c r="L33" s="36" t="s">
+        <v>1454</v>
+      </c>
+      <c r="M33" s="36" t="s">
+        <v>1455</v>
+      </c>
+      <c r="N33" s="36" t="s">
+        <v>1456</v>
+      </c>
+      <c r="O33" s="36" t="s">
+        <v>1457</v>
+      </c>
+      <c r="P33" s="36" t="s">
+        <v>1458</v>
+      </c>
+      <c r="Q33" s="37" t="s">
+        <v>1432</v>
+      </c>
+      <c r="R33" s="37" t="s">
+        <v>1246</v>
+      </c>
+      <c r="S33" s="37" t="s">
+        <v>1622</v>
+      </c>
+      <c r="T33" s="36" t="s">
+        <v>1623</v>
+      </c>
+      <c r="U33" s="36" t="s">
+        <v>1261</v>
+      </c>
+      <c r="V33" s="36" t="s">
+        <v>1624</v>
+      </c>
+      <c r="W33" s="36" t="s">
+        <v>1625</v>
+      </c>
+      <c r="X33" s="36" t="s">
+        <v>1626</v>
+      </c>
+      <c r="Y33" s="36" t="s">
         <v>1596</v>
       </c>
-      <c r="F33" s="37" t="s">
-        <v>1597</v>
-      </c>
-      <c r="G33" s="37" t="s">
-        <v>1531</v>
-      </c>
-      <c r="H33" s="37" t="s">
-        <v>1598</v>
-      </c>
-      <c r="I33" s="37" t="s">
-        <v>1599</v>
-      </c>
-      <c r="J33" s="36" t="s">
-        <v>1615</v>
-      </c>
-      <c r="K33" s="36" t="s">
-        <v>1447</v>
-      </c>
-      <c r="L33" s="36" t="s">
-        <v>1448</v>
-      </c>
-      <c r="M33" s="36" t="s">
-        <v>1449</v>
-      </c>
-      <c r="N33" s="36" t="s">
-        <v>1450</v>
-      </c>
-      <c r="O33" s="36" t="s">
-        <v>1451</v>
-      </c>
-      <c r="P33" s="36" t="s">
-        <v>1452</v>
-      </c>
-      <c r="Q33" s="37" t="s">
-        <v>1426</v>
-      </c>
-      <c r="R33" s="37" t="s">
-        <v>1240</v>
-      </c>
-      <c r="S33" s="37" t="s">
-        <v>1616</v>
-      </c>
-      <c r="T33" s="36" t="s">
-        <v>1617</v>
-      </c>
-      <c r="U33" s="36" t="s">
-        <v>1255</v>
-      </c>
-      <c r="V33" s="36" t="s">
-        <v>1618</v>
-      </c>
-      <c r="W33" s="36" t="s">
-        <v>1619</v>
-      </c>
-      <c r="X33" s="36" t="s">
-        <v>1620</v>
-      </c>
-      <c r="Y33" s="36" t="s">
-        <v>1590</v>
-      </c>
       <c r="Z33" s="36" t="s">
-        <v>1621</v>
+        <v>1627</v>
       </c>
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
@@ -8371,10 +8389,10 @@
     </row>
     <row r="34" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="37" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>1467</v>
+        <v>1473</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -8406,7 +8424,7 @@
         <v>282</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>1445</v>
+        <v>1451</v>
       </c>
       <c r="C35" s="37"/>
       <c r="D35" s="37"/>
@@ -8438,7 +8456,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="37" t="s">
-        <v>1429</v>
+        <v>1435</v>
       </c>
       <c r="C36" s="37"/>
       <c r="D36" s="37"/>
@@ -8467,10 +8485,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="37" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="B37" s="37" t="s">
-        <v>1468</v>
+        <v>1474</v>
       </c>
       <c r="C37" s="37"/>
       <c r="D37" s="37"/>
@@ -8502,16 +8520,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>1469</v>
+        <v>1475</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>1470</v>
+        <v>1476</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>1472</v>
+        <v>1478</v>
       </c>
       <c r="F38" s="37"/>
       <c r="G38" s="36"/>
@@ -8540,22 +8558,22 @@
         <v>95</v>
       </c>
       <c r="B39" s="37" t="s">
-        <v>1473</v>
+        <v>1479</v>
       </c>
       <c r="C39" s="37" t="s">
-        <v>1444</v>
+        <v>1450</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>1474</v>
+        <v>1480</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>1334</v>
+        <v>1340</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>1475</v>
+        <v>1481</v>
       </c>
       <c r="G39" s="36" t="s">
-        <v>1476</v>
+        <v>1482</v>
       </c>
       <c r="H39" s="36"/>
       <c r="I39" s="36"/>
@@ -8579,25 +8597,25 @@
     </row>
     <row r="40" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="37" t="s">
-        <v>1348</v>
+        <v>1354</v>
       </c>
       <c r="B40" s="37" t="s">
-        <v>1477</v>
+        <v>1483</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>1240</v>
+        <v>1246</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>1478</v>
+        <v>1484</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>1479</v>
+        <v>1485</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>1480</v>
+        <v>1486</v>
       </c>
       <c r="G40" s="36" t="s">
-        <v>1255</v>
+        <v>1261</v>
       </c>
       <c r="H40" s="36"/>
       <c r="I40" s="36"/>
@@ -8621,10 +8639,10 @@
     </row>
     <row r="41" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="37" t="s">
-        <v>1046</v>
+        <v>1052</v>
       </c>
       <c r="B41" s="37" t="s">
-        <v>1481</v>
+        <v>1487</v>
       </c>
       <c r="C41" s="37"/>
       <c r="D41" s="37"/>
@@ -8653,10 +8671,10 @@
     </row>
     <row r="42" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="37" t="s">
-        <v>1352</v>
+        <v>1358</v>
       </c>
       <c r="B42" s="37" t="s">
-        <v>1482</v>
+        <v>1488</v>
       </c>
       <c r="C42" s="37"/>
       <c r="D42" s="37"/>
@@ -8688,13 +8706,13 @@
         <v>123</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>1483</v>
+        <v>1489</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>1240</v>
+        <v>1246</v>
       </c>
       <c r="D43" s="37" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="E43" s="37"/>
       <c r="F43" s="37"/>
@@ -8724,7 +8742,7 @@
         <v>228</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>1484</v>
+        <v>1490</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -8753,13 +8771,13 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="37" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="B45" s="37" t="s">
-        <v>1485</v>
+        <v>1491</v>
       </c>
       <c r="C45" s="37" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="D45" s="37"/>
       <c r="E45" s="37"/>
@@ -8790,58 +8808,58 @@
         <v>456</v>
       </c>
       <c r="B46" s="37" t="s">
-        <v>1487</v>
+        <v>1493</v>
       </c>
       <c r="C46" s="37" t="s">
-        <v>1488</v>
+        <v>1494</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>1477</v>
+        <v>1483</v>
       </c>
       <c r="E46" s="37" t="s">
-        <v>1489</v>
+        <v>1495</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>1490</v>
+        <v>1496</v>
       </c>
       <c r="G46" s="36" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="H46" s="36" t="s">
-        <v>1492</v>
+        <v>1498</v>
       </c>
       <c r="I46" s="36" t="s">
-        <v>1493</v>
+        <v>1499</v>
       </c>
       <c r="J46" s="36" t="s">
-        <v>1494</v>
+        <v>1500</v>
       </c>
       <c r="K46" s="36" t="s">
-        <v>1495</v>
+        <v>1501</v>
       </c>
       <c r="L46" s="36" t="s">
-        <v>1496</v>
+        <v>1502</v>
       </c>
       <c r="M46" s="36" t="s">
-        <v>1497</v>
+        <v>1503</v>
       </c>
       <c r="N46" s="36" t="s">
-        <v>1498</v>
+        <v>1504</v>
       </c>
       <c r="O46" s="36" t="s">
-        <v>1499</v>
+        <v>1505</v>
       </c>
       <c r="P46" s="36" t="s">
-        <v>1500</v>
+        <v>1506</v>
       </c>
       <c r="Q46" s="36" t="s">
-        <v>1501</v>
+        <v>1507</v>
       </c>
       <c r="R46" s="36" t="s">
-        <v>1502</v>
+        <v>1508</v>
       </c>
       <c r="S46" s="36" t="s">
-        <v>1503</v>
+        <v>1509</v>
       </c>
       <c r="T46" s="36"/>
       <c r="U46" s="36"/>
@@ -8876,10 +8894,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="46" t="s">
-        <v>1622</v>
+        <v>1628</v>
       </c>
       <c r="B1" s="46" t="s">
-        <v>1623</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10941,7 +10959,7 @@
     <tabColor rgb="FF2F5496"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B162"/>
+  <dimension ref="A1:B163"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
@@ -12242,6 +12260,14 @@
       </c>
       <c r="B162" s="13" t="s">
         <v>830</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="B163" s="13" t="s">
+        <v>832</v>
       </c>
     </row>
   </sheetData>
@@ -12261,7 +12287,7 @@
     <tabColor rgb="FF2F5496"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B108"/>
+  <dimension ref="A1:B110"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
@@ -12270,866 +12296,882 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="14" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="14" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="14" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="14" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="14" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="14" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="14" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="14" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="14" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="14" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="14" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="14" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="14" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="14" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="14" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="16" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="14" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="14" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="14" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="14" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="14" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="14" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="14" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="14" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="B67" s="14" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="14" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="14" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="B69" s="14" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="14" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="16" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="14" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="14" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="16" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="14" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="14" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="14" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="B77" s="14" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="14" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="16" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B79" s="14" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="14" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="14" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="14" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="B82" s="14" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="16" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="B83" s="14" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="14" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="B84" s="14" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="14" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="B85" s="14" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="14" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="B86" s="14" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="14" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="B87" s="14" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="14" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="14" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="B89" s="14" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="14" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="B90" s="14" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="14" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="16" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="B92" s="14" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="14" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="B93" s="14" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="14" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="B94" s="14" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="17" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B95" s="14" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="16" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="B96" s="18" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="14" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="B97" s="18" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="14" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="B98" s="18" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="14" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="B99" s="18" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="16" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B100" s="18" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="14" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="B101" s="18" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="14" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="B102" s="18" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="16" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="B103" s="18" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="14" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="B104" s="18" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="14" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="B105" s="18" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="19" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="B106" s="19" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="19" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="B107" s="19" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="19" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="B108" s="19" t="s">
-        <v>1045</v>
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="19" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B109" s="19" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="19" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B110" s="19" t="s">
+        <v>1051</v>
       </c>
     </row>
   </sheetData>
@@ -13204,7 +13246,7 @@
         <v>93</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>1046</v>
+        <v>1052</v>
       </c>
       <c r="F1" s="20" t="s">
         <v>43</v>
@@ -13219,7 +13261,7 @@
         <v>136</v>
       </c>
       <c r="J1" s="20" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="K1" s="20" t="s">
         <v>28</v>
@@ -13228,19 +13270,19 @@
         <v>111</v>
       </c>
       <c r="M1" s="20" t="s">
-        <v>1048</v>
+        <v>1054</v>
       </c>
       <c r="N1" s="20" t="s">
-        <v>1049</v>
+        <v>1055</v>
       </c>
       <c r="O1" s="20" t="s">
         <v>143</v>
       </c>
       <c r="P1" s="20" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
       <c r="Q1" s="20" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="R1" s="21" t="s">
         <v>350</v>
@@ -13252,10 +13294,10 @@
         <v>97</v>
       </c>
       <c r="U1" s="21" t="s">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="V1" s="21" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="W1" s="21" t="s">
         <v>99</v>
@@ -13264,13 +13306,13 @@
         <v>128</v>
       </c>
       <c r="Y1" s="21" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
       <c r="Z1" s="21" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="AA1" s="21" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="AB1" s="21" t="s">
         <v>182</v>
@@ -13285,7 +13327,7 @@
         <v>228</v>
       </c>
       <c r="AF1" s="21" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="AG1" s="21" t="s">
         <v>85</v>
@@ -13314,570 +13356,570 @@
     </row>
     <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>1065</v>
+        <v>1071</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>1066</v>
+        <v>1072</v>
       </c>
       <c r="J2" s="10" t="s">
+        <v>1073</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>1074</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>1075</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>1076</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>1077</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>1077</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>1078</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>1079</v>
+      </c>
+      <c r="R2" s="10" t="s">
+        <v>1068</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>1067</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="V2" s="10" t="s">
         <v>1068</v>
       </c>
-      <c r="L2" s="10" t="s">
-        <v>1069</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>1070</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>1071</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>1071</v>
-      </c>
-      <c r="P2" s="10" t="s">
-        <v>1072</v>
-      </c>
-      <c r="Q2" s="10" t="s">
-        <v>1073</v>
-      </c>
-      <c r="R2" s="10" t="s">
-        <v>1062</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>1074</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>1061</v>
-      </c>
-      <c r="V2" s="10" t="s">
-        <v>1062</v>
-      </c>
       <c r="W2" s="1" t="s">
-        <v>1075</v>
+        <v>1081</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>1077</v>
+        <v>1083</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>456</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
       <c r="AB2" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="AD2" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="AE2" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
       <c r="AG2" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>1080</v>
+        <v>1086</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>1081</v>
+        <v>1087</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>1081</v>
+        <v>1087</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="AN2" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>1088</v>
+        <v>1094</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>1067</v>
+        <v>1073</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>1090</v>
+        <v>1096</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
       <c r="J3" s="10" t="s">
         <v>456</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="N3" s="10" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="O3" s="10" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="P3" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="Q3" s="10" t="s">
-        <v>1094</v>
+        <v>1100</v>
       </c>
       <c r="R3" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="S3" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="U3" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="V3" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="Y3" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="Z3" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="AA3" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="AB3" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="AC3" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="AD3" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="AE3" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>1098</v>
+        <v>1104</v>
       </c>
       <c r="AG3" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="AH3" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="AI3" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="AJ3" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="AK3" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="AL3" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="AM3" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="AN3" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>1099</v>
+        <v>1105</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1100</v>
+        <v>1106</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>1110</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>1105</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I4" s="22" t="s">
+        <v>1111</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>1088</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>1065</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>1105</v>
+      </c>
+      <c r="M4" s="10" t="s">
         <v>1101</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>1102</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>1103</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>1104</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>1099</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>1063</v>
-      </c>
-      <c r="I4" s="22" t="s">
-        <v>1105</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>1082</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>1059</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>1099</v>
-      </c>
-      <c r="M4" s="10" t="s">
-        <v>1095</v>
-      </c>
       <c r="N4" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="O4" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="P4" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="Q4" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="R4" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="S4" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="T4" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="U4" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="V4" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>1090</v>
+        <v>1096</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>1107</v>
+        <v>1113</v>
       </c>
       <c r="Y4" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="Z4" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="AA4" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="AB4" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="AC4" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="AD4" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="AE4" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="AF4" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="AG4" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="AH4" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="AI4" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="AJ4" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="AK4" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="AL4" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="AM4" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="AN4" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>1108</v>
+        <v>1114</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>1111</v>
+        <v>1117</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>1113</v>
+        <v>1119</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="H5" s="10" t="s">
         <v>456</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>1115</v>
+        <v>1121</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="O5" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="Q5" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="S5" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="T5" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="U5" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>1116</v>
+        <v>1122</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>1115</v>
+        <v>1121</v>
       </c>
       <c r="Y5" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="Z5" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="AA5" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="AB5" s="10"/>
       <c r="AC5" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="AD5" s="10"/>
       <c r="AF5" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="AH5" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="AK5" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="AL5" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="AM5" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>1117</v>
+        <v>1123</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>1119</v>
+        <v>1125</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>1123</v>
+        <v>1129</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="O6" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="P6" s="22"/>
       <c r="Q6" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="T6" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>1124</v>
+        <v>1130</v>
       </c>
       <c r="AF6" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>1125</v>
+        <v>1131</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F7" s="22" t="s">
         <v>1118</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>1126</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>1127</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>1062</v>
-      </c>
-      <c r="F7" s="22" t="s">
+      <c r="G7" s="10" t="s">
+        <v>1134</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>1135</v>
+      </c>
+      <c r="I7" s="10" t="s">
         <v>1112</v>
       </c>
-      <c r="G7" s="10" t="s">
-        <v>1128</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>1129</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>1106</v>
-      </c>
       <c r="J7" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>1130</v>
+        <v>1136</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>1128</v>
+        <v>1134</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
@@ -13885,44 +13927,44 @@
       <c r="P7" s="22"/>
       <c r="Q7" s="22"/>
       <c r="W7" s="1" t="s">
-        <v>1125</v>
+        <v>1131</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>1130</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>1131</v>
+        <v>1137</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1132</v>
+        <v>1138</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>1090</v>
+        <v>1096</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>1133</v>
+        <v>1139</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>1134</v>
+        <v>1140</v>
       </c>
       <c r="I8" s="22"/>
       <c r="J8" s="22"/>
       <c r="K8" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>1133</v>
+        <v>1139</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
@@ -13930,44 +13972,44 @@
       <c r="P8" s="22"/>
       <c r="Q8" s="22"/>
       <c r="W8" s="1" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="X8" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>1135</v>
+        <v>1141</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1132</v>
+        <v>1138</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>1137</v>
+        <v>1143</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>1138</v>
+        <v>1144</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>1139</v>
+        <v>1145</v>
       </c>
       <c r="I9" s="22"/>
       <c r="J9" s="22"/>
       <c r="K9" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="M9" s="22"/>
       <c r="N9" s="22"/>
@@ -13975,42 +14017,42 @@
       <c r="P9" s="22"/>
       <c r="Q9" s="22"/>
       <c r="W9" s="1" t="s">
-        <v>1140</v>
+        <v>1146</v>
       </c>
       <c r="X9" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>1141</v>
+        <v>1147</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1142</v>
+        <v>1148</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1143</v>
+        <v>1149</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>1144</v>
+        <v>1150</v>
       </c>
       <c r="E10" s="22"/>
       <c r="F10" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>1145</v>
+        <v>1151</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>1146</v>
+        <v>1152</v>
       </c>
       <c r="I10" s="22"/>
       <c r="J10" s="22"/>
       <c r="K10" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="M10" s="22"/>
       <c r="N10" s="22"/>
@@ -14018,38 +14060,38 @@
       <c r="P10" s="22"/>
       <c r="Q10" s="22"/>
       <c r="W10" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="X10" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1098</v>
+        <v>1104</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>1147</v>
+        <v>1153</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="E11" s="22"/>
       <c r="F11" s="22"/>
       <c r="G11" s="10" t="s">
-        <v>1148</v>
+        <v>1154</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>1149</v>
+        <v>1155</v>
       </c>
       <c r="I11" s="22"/>
       <c r="J11" s="22"/>
       <c r="K11" s="22"/>
       <c r="L11" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="M11" s="22"/>
       <c r="N11" s="22"/>
@@ -14057,29 +14099,29 @@
       <c r="P11" s="22"/>
       <c r="Q11" s="22"/>
       <c r="W11" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>1150</v>
+        <v>1156</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1151</v>
+        <v>1157</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>1152</v>
+        <v>1158</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>1153</v>
+        <v>1159</v>
       </c>
       <c r="E12" s="22"/>
       <c r="F12" s="22"/>
       <c r="G12" s="10" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>1154</v>
+        <v>1160</v>
       </c>
       <c r="I12" s="22"/>
       <c r="J12" s="22"/>
@@ -14091,29 +14133,29 @@
       <c r="P12" s="22"/>
       <c r="Q12" s="22"/>
       <c r="W12" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>1143</v>
+        <v>1149</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1155</v>
+        <v>1161</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="E13" s="22"/>
       <c r="F13" s="22"/>
       <c r="G13" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>1156</v>
+        <v>1162</v>
       </c>
       <c r="I13" s="22"/>
       <c r="J13" s="22"/>
@@ -14127,24 +14169,24 @@
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>1157</v>
+        <v>1163</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1158</v>
+        <v>1164</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>1159</v>
+        <v>1165</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="E14" s="22"/>
       <c r="F14" s="22"/>
       <c r="G14" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>1160</v>
+        <v>1166</v>
       </c>
       <c r="I14" s="22"/>
       <c r="J14" s="22"/>
@@ -14158,24 +14200,24 @@
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>1161</v>
+        <v>1167</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1162</v>
+        <v>1168</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>1163</v>
+        <v>1169</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="E15" s="22"/>
       <c r="F15" s="22"/>
       <c r="G15" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="I15" s="22"/>
       <c r="J15" s="22"/>
@@ -14189,20 +14231,20 @@
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>1164</v>
+        <v>1170</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>1165</v>
+        <v>1171</v>
       </c>
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
       <c r="F16" s="22"/>
       <c r="G16" s="22"/>
       <c r="H16" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="I16" s="22"/>
       <c r="J16" s="22"/>
@@ -14216,20 +14258,20 @@
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>1159</v>
+        <v>1165</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1156</v>
+        <v>1162</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>1166</v>
+        <v>1172</v>
       </c>
       <c r="D17" s="22"/>
       <c r="E17" s="22"/>
       <c r="F17" s="22"/>
       <c r="G17" s="22"/>
       <c r="H17" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="I17" s="22"/>
       <c r="J17" s="22"/>
@@ -14243,13 +14285,13 @@
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>1167</v>
+        <v>1173</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1168</v>
+        <v>1174</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>1169</v>
+        <v>1175</v>
       </c>
       <c r="D18" s="22"/>
       <c r="E18" s="22"/>
@@ -14268,13 +14310,13 @@
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>1170</v>
+        <v>1176</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1171</v>
+        <v>1177</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>1172</v>
+        <v>1178</v>
       </c>
       <c r="D19" s="22"/>
       <c r="E19" s="22"/>
@@ -14293,13 +14335,13 @@
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>1173</v>
+        <v>1179</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>1175</v>
+        <v>1181</v>
       </c>
       <c r="D20" s="22"/>
       <c r="E20" s="22"/>
@@ -14318,13 +14360,13 @@
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>1176</v>
+        <v>1182</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1147</v>
+        <v>1153</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>1177</v>
+        <v>1183</v>
       </c>
       <c r="D21" s="22"/>
       <c r="E21" s="22"/>
@@ -14343,13 +14385,13 @@
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B22" s="22" t="s">
         <v>1178</v>
       </c>
-      <c r="B22" s="22" t="s">
-        <v>1172</v>
-      </c>
       <c r="C22" s="10" t="s">
-        <v>1179</v>
+        <v>1185</v>
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="22"/>
@@ -14368,13 +14410,13 @@
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>1180</v>
+        <v>1186</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>1175</v>
+        <v>1181</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>1181</v>
+        <v>1187</v>
       </c>
       <c r="D23" s="22"/>
       <c r="E23" s="22"/>
@@ -14393,13 +14435,13 @@
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>1182</v>
+        <v>1188</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>1177</v>
+        <v>1183</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>1183</v>
+        <v>1189</v>
       </c>
       <c r="D24" s="22"/>
       <c r="E24" s="22"/>
@@ -14418,13 +14460,13 @@
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>1184</v>
+        <v>1190</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>1179</v>
+        <v>1185</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>1166</v>
+        <v>1172</v>
       </c>
       <c r="D25" s="22"/>
       <c r="E25" s="22"/>
@@ -14443,13 +14485,13 @@
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>1185</v>
+        <v>1191</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>1181</v>
+        <v>1187</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>1186</v>
+        <v>1192</v>
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="22"/>
@@ -14468,13 +14510,13 @@
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>1187</v>
+        <v>1193</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>1183</v>
+        <v>1189</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>1188</v>
+        <v>1194</v>
       </c>
       <c r="D27" s="22"/>
       <c r="E27" s="22"/>
@@ -14493,13 +14535,13 @@
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>1189</v>
+        <v>1195</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>1166</v>
+        <v>1172</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>1190</v>
+        <v>1196</v>
       </c>
       <c r="D28" s="22"/>
       <c r="E28" s="22"/>
@@ -14518,13 +14560,13 @@
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>1191</v>
+        <v>1197</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>1186</v>
+        <v>1192</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>1192</v>
+        <v>1198</v>
       </c>
       <c r="D29" s="22"/>
       <c r="E29" s="22"/>
@@ -14543,13 +14585,13 @@
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>1193</v>
+        <v>1199</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>1188</v>
+        <v>1194</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>1194</v>
+        <v>1200</v>
       </c>
       <c r="D30" s="22"/>
       <c r="E30" s="22"/>
@@ -14568,13 +14610,13 @@
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>1190</v>
+        <v>1196</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>1196</v>
+        <v>1202</v>
       </c>
       <c r="D31" s="22"/>
       <c r="E31" s="22"/>
@@ -14593,13 +14635,13 @@
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>1192</v>
+        <v>1198</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
       <c r="D32" s="22"/>
       <c r="E32" s="22"/>
@@ -14618,13 +14660,13 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>1199</v>
+        <v>1205</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>1194</v>
+        <v>1200</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>1200</v>
+        <v>1206</v>
       </c>
       <c r="D33" s="22"/>
       <c r="E33" s="22"/>
@@ -14643,13 +14685,13 @@
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>1201</v>
+        <v>1207</v>
       </c>
       <c r="B34" s="22" t="s">
-        <v>1196</v>
+        <v>1202</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="D34" s="22"/>
       <c r="E34" s="22"/>
@@ -14668,13 +14710,13 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>1202</v>
+        <v>1208</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="D35" s="22"/>
       <c r="E35" s="22"/>
@@ -14693,13 +14735,13 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>1203</v>
+        <v>1209</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>1200</v>
+        <v>1206</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="D36" s="22"/>
       <c r="E36" s="22"/>
@@ -14718,10 +14760,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>1204</v>
+        <v>1210</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="C37" s="22"/>
       <c r="D37" s="22"/>
@@ -14741,10 +14783,10 @@
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>1205</v>
+        <v>1211</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="C38" s="22"/>
       <c r="D38" s="22"/>
@@ -14764,10 +14806,10 @@
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="s">
-        <v>1206</v>
+        <v>1212</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="C39" s="22"/>
       <c r="D39" s="22"/>
@@ -14787,7 +14829,7 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="B40" s="22"/>
       <c r="C40" s="22"/>
@@ -14808,7 +14850,7 @@
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="B41" s="22"/>
       <c r="C41" s="22"/>
@@ -14829,7 +14871,7 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
     </row>
   </sheetData>
@@ -14857,92 +14899,92 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1207</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="24" t="s">
-        <v>1208</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>1209</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>1210</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>1211</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>1212</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>1215</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>1216</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="24" t="s">
-        <v>1217</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
-        <v>1220</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>1221</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>1222</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14952,7 +14994,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
     </row>
   </sheetData>
@@ -14981,159 +15023,159 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1223</v>
+        <v>1229</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>1225</v>
+        <v>1231</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>1226</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>1227</v>
+        <v>1233</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>1226</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>1228</v>
+        <v>1234</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>1229</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>1232</v>
+        <v>1238</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>1233</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>1234</v>
+        <v>1240</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>1235</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>1236</v>
+        <v>1242</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>1237</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>1238</v>
+        <v>1244</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>1239</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>1240</v>
+        <v>1246</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>1241</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>1243</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>1244</v>
+        <v>1250</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>1246</v>
+        <v>1252</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>1247</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>1248</v>
+        <v>1254</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>1249</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>1250</v>
+        <v>1256</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>1249</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>1251</v>
+        <v>1257</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>1249</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>1252</v>
+        <v>1258</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>1253</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>1254</v>
+        <v>1260</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>1243</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>1255</v>
+        <v>1261</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>1226</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="B20" s="23"/>
     </row>
@@ -15165,31 +15207,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>1258</v>
+        <v>1264</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>1260</v>
+        <v>1266</v>
       </c>
       <c r="E1" s="26"/>
     </row>
     <row r="2" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>1261</v>
+        <v>1267</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>1262</v>
+        <v>1268</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="E2" s="28"/>
     </row>
@@ -15198,13 +15240,13 @@
         <v>143</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>1262</v>
+        <v>1268</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>1265</v>
+        <v>1271</v>
       </c>
       <c r="E3" s="28"/>
     </row>
@@ -15213,43 +15255,43 @@
         <v>93</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>1267</v>
+        <v>1273</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>1268</v>
+        <v>1274</v>
       </c>
       <c r="E4" s="28"/>
     </row>
     <row r="5" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1269</v>
+        <v>1275</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1271</v>
+        <v>1277</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1272</v>
+        <v>1278</v>
       </c>
       <c r="E5" s="28"/>
     </row>
     <row r="6" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>1273</v>
+        <v>1279</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>1262</v>
+        <v>1268</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>1265</v>
+        <v>1271</v>
       </c>
       <c r="E6" s="28"/>
     </row>
@@ -15258,13 +15300,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1275</v>
+        <v>1281</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="E7" s="28"/>
     </row>
@@ -15273,43 +15315,43 @@
         <v>28</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>1271</v>
+        <v>1277</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>1277</v>
+        <v>1283</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="E8" s="28"/>
     </row>
     <row r="9" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D9" s="27" t="s">
         <v>1278</v>
-      </c>
-      <c r="B9" s="27" t="s">
-        <v>1274</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>1275</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>1272</v>
       </c>
       <c r="E9" s="28"/>
     </row>
     <row r="10" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>1279</v>
+        <v>1285</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>1262</v>
+        <v>1268</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="E10" s="28"/>
     </row>
@@ -15318,73 +15360,73 @@
         <v>111</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1280</v>
+        <v>1286</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1281</v>
+        <v>1287</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1282</v>
+        <v>1288</v>
       </c>
       <c r="E11" s="28"/>
     </row>
     <row r="12" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>1049</v>
+        <v>1055</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>1283</v>
+        <v>1289</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>1284</v>
+        <v>1290</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="E12" s="28"/>
     </row>
     <row r="13" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1286</v>
+        <v>1292</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1287</v>
+        <v>1293</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1288</v>
+        <v>1294</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
       <c r="E13" s="28"/>
     </row>
     <row r="14" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
-        <v>1290</v>
+        <v>1296</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>1275</v>
+        <v>1281</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="E14" s="28"/>
     </row>
     <row r="15" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1291</v>
+        <v>1297</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1292</v>
+        <v>1298</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1293</v>
+        <v>1299</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1294</v>
+        <v>1300</v>
       </c>
       <c r="E15" s="28"/>
     </row>
@@ -15393,13 +15435,13 @@
         <v>97</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>1295</v>
+        <v>1301</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>1296</v>
+        <v>1302</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>1297</v>
+        <v>1303</v>
       </c>
       <c r="E16" s="28"/>
     </row>
@@ -15408,13 +15450,13 @@
         <v>6</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>1298</v>
+        <v>1304</v>
       </c>
       <c r="C17" s="27" t="s">
+        <v>1280</v>
+      </c>
+      <c r="D17" s="27" t="s">
         <v>1274</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>1268</v>
       </c>
       <c r="E17" s="28"/>
     </row>
@@ -15423,22 +15465,22 @@
         <v>43</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>1299</v>
+        <v>1305</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>1300</v>
+        <v>1306</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>1301</v>
+        <v>1307</v>
       </c>
       <c r="E18" s="28"/>
     </row>
     <row r="19" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>1302</v>
+        <v>1308</v>
       </c>
       <c r="C19" s="27"/>
       <c r="D19" s="27"/>
@@ -15446,16 +15488,16 @@
     </row>
     <row r="20" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="27" t="s">
-        <v>1303</v>
+        <v>1309</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>1299</v>
+        <v>1305</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>1300</v>
+        <v>1306</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>1301</v>
+        <v>1307</v>
       </c>
       <c r="E20" s="28"/>
     </row>
@@ -15464,13 +15506,13 @@
         <v>125</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>1302</v>
+        <v>1308</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>1305</v>
+        <v>1311</v>
       </c>
       <c r="E21" s="28"/>
     </row>
@@ -15479,43 +15521,43 @@
         <v>182</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>1306</v>
+        <v>1312</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>1307</v>
+        <v>1313</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>1308</v>
+        <v>1314</v>
       </c>
       <c r="E22" s="28"/>
     </row>
     <row r="23" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="30" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>1309</v>
+        <v>1315</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>1310</v>
+        <v>1316</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>1307</v>
+        <v>1313</v>
       </c>
       <c r="E23" s="28"/>
     </row>
     <row r="24" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
-        <v>1311</v>
+        <v>1317</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>1262</v>
+        <v>1268</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="E24" s="28"/>
     </row>
@@ -15524,67 +15566,67 @@
         <v>74</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>1312</v>
+        <v>1318</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>1277</v>
+        <v>1283</v>
       </c>
       <c r="E25" s="28"/>
     </row>
     <row r="26" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="27" t="s">
-        <v>1238</v>
+        <v>1244</v>
       </c>
       <c r="B26" s="30" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>1281</v>
+        <v>1287</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>1282</v>
+        <v>1288</v>
       </c>
       <c r="E26" s="28"/>
     </row>
     <row r="27" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>1313</v>
+        <v>1319</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>1287</v>
+        <v>1293</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>1284</v>
+        <v>1290</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="E27" s="28"/>
     </row>
     <row r="28" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="27" t="s">
-        <v>1314</v>
+        <v>1320</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>1300</v>
+        <v>1306</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>1315</v>
+        <v>1321</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>1316</v>
+        <v>1322</v>
       </c>
       <c r="E28" s="28"/>
     </row>
     <row r="29" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>1309</v>
+        <v>1315</v>
       </c>
       <c r="C29" s="27"/>
       <c r="D29" s="27"/>
@@ -15595,7 +15637,7 @@
         <v>160</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>1317</v>
+        <v>1323</v>
       </c>
       <c r="C30" s="27"/>
       <c r="D30" s="27"/>
@@ -15606,13 +15648,13 @@
         <v>99</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>1295</v>
+        <v>1301</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>1318</v>
+        <v>1324</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>1319</v>
+        <v>1325</v>
       </c>
       <c r="E31" s="28"/>
     </row>
@@ -15621,7 +15663,7 @@
         <v>262</v>
       </c>
       <c r="B32" s="32" t="s">
-        <v>1320</v>
+        <v>1326</v>
       </c>
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
@@ -15629,16 +15671,16 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="26" t="s">
-        <v>1321</v>
+        <v>1327</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>1322</v>
+        <v>1328</v>
       </c>
       <c r="E33" s="26"/>
     </row>
@@ -15647,7 +15689,7 @@
         <v>46</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>1323</v>
+        <v>1329</v>
       </c>
       <c r="C34" s="26"/>
       <c r="D34" s="26"/>
@@ -15655,10 +15697,10 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="26" t="s">
-        <v>1324</v>
+        <v>1330</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>1271</v>
+        <v>1277</v>
       </c>
       <c r="C35" s="26"/>
       <c r="D35" s="26"/>
@@ -15666,16 +15708,16 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="26" t="s">
-        <v>1325</v>
+        <v>1331</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>1326</v>
+        <v>1332</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>1327</v>
+        <v>1333</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>1328</v>
+        <v>1334</v>
       </c>
       <c r="E36" s="26"/>
     </row>
@@ -15684,7 +15726,7 @@
         <v>202</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>1329</v>
+        <v>1335</v>
       </c>
       <c r="C37" s="26"/>
       <c r="D37" s="26"/>
@@ -15695,7 +15737,7 @@
         <v>205</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>1330</v>
+        <v>1336</v>
       </c>
       <c r="C38" s="26"/>
       <c r="D38" s="26"/>
@@ -15706,7 +15748,7 @@
         <v>140</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>1283</v>
+        <v>1289</v>
       </c>
       <c r="C39" s="26"/>
       <c r="D39" s="26"/>
@@ -15714,25 +15756,25 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="26" t="s">
-        <v>1331</v>
+        <v>1337</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>1332</v>
+        <v>1338</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>1333</v>
+        <v>1339</v>
       </c>
       <c r="E40" s="26"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="26" t="s">
-        <v>1334</v>
+        <v>1340</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>1335</v>
+        <v>1341</v>
       </c>
       <c r="C41" s="26"/>
       <c r="D41" s="26"/>
@@ -15740,16 +15782,16 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="26" t="s">
-        <v>1336</v>
+        <v>1342</v>
       </c>
       <c r="B42" s="26" t="s">
-        <v>1298</v>
+        <v>1304</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>1337</v>
+        <v>1343</v>
       </c>
       <c r="D42" s="26" t="s">
-        <v>1338</v>
+        <v>1344</v>
       </c>
       <c r="E42" s="26"/>
     </row>
@@ -15758,7 +15800,7 @@
         <v>350</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>1317</v>
+        <v>1323</v>
       </c>
       <c r="C43" s="26"/>
       <c r="D43" s="26"/>
@@ -15766,34 +15808,34 @@
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="26" t="s">
-        <v>1339</v>
+        <v>1345</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>1298</v>
+        <v>1304</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>1340</v>
+        <v>1346</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>1341</v>
+        <v>1347</v>
       </c>
       <c r="E44" s="26"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="26" t="s">
-        <v>1342</v>
+        <v>1348</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>1343</v>
+        <v>1349</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="D45" s="26" t="s">
-        <v>1305</v>
+        <v>1311</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>1302</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15801,7 +15843,7 @@
         <v>133</v>
       </c>
       <c r="B46" s="26" t="s">
-        <v>1344</v>
+        <v>1350</v>
       </c>
       <c r="C46" s="26"/>
       <c r="D46" s="26"/>
@@ -15809,10 +15851,10 @@
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="26" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>1320</v>
+        <v>1326</v>
       </c>
       <c r="C47" s="26"/>
       <c r="D47" s="26"/>
@@ -15823,7 +15865,7 @@
         <v>128</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>1309</v>
+        <v>1315</v>
       </c>
       <c r="C48" s="26"/>
       <c r="D48" s="26"/>
@@ -15834,67 +15876,67 @@
         <v>95</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>1345</v>
+        <v>1351</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>1346</v>
+        <v>1352</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>1347</v>
+        <v>1353</v>
       </c>
       <c r="E49" s="26"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="26" t="s">
-        <v>1348</v>
+        <v>1354</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>1349</v>
+        <v>1355</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="D50" s="26" t="s">
-        <v>1309</v>
+        <v>1315</v>
       </c>
       <c r="E50" s="26"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="26" t="s">
-        <v>1350</v>
+        <v>1356</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>1307</v>
+        <v>1313</v>
       </c>
       <c r="D51" s="26" t="s">
-        <v>1308</v>
+        <v>1314</v>
       </c>
       <c r="E51" s="26"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="26" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="B52" s="26" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="C52" s="26" t="s">
-        <v>1310</v>
+        <v>1316</v>
       </c>
       <c r="D52" s="26" t="s">
-        <v>1307</v>
+        <v>1313</v>
       </c>
       <c r="E52" s="26"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="26" t="s">
-        <v>1046</v>
+        <v>1052</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>1302</v>
+        <v>1308</v>
       </c>
       <c r="C53" s="26"/>
       <c r="D53" s="26"/>
@@ -15902,10 +15944,10 @@
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="26" t="s">
-        <v>1352</v>
+        <v>1358</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>1353</v>
+        <v>1359</v>
       </c>
       <c r="C54" s="26"/>
       <c r="D54" s="26"/>
@@ -15913,10 +15955,10 @@
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="26" t="s">
-        <v>1354</v>
+        <v>1360</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>1355</v>
+        <v>1361</v>
       </c>
       <c r="C55" s="26"/>
       <c r="D55" s="26"/>
@@ -15924,10 +15966,10 @@
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="26" t="s">
-        <v>1356</v>
+        <v>1362</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>1357</v>
+        <v>1363</v>
       </c>
       <c r="C56" s="26"/>
       <c r="D56" s="26"/>
@@ -15935,10 +15977,10 @@
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="26" t="s">
-        <v>1358</v>
+        <v>1364</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="C57" s="26"/>
       <c r="D57" s="26"/>
@@ -15946,10 +15988,10 @@
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="26" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="C58" s="26"/>
       <c r="D58" s="26"/>
@@ -15960,10 +16002,10 @@
         <v>456</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>1359</v>
+        <v>1365</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>1261</v>
+        <v>1267</v>
       </c>
       <c r="D59" s="26"/>
       <c r="E59" s="26"/>
@@ -15997,99 +16039,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="34" t="s">
-        <v>1360</v>
+        <v>1366</v>
       </c>
       <c r="C1" s="34" t="s">
-        <v>1361</v>
+        <v>1367</v>
       </c>
       <c r="D1" s="34" t="s">
-        <v>1362</v>
+        <v>1368</v>
       </c>
       <c r="E1" s="34" t="s">
-        <v>1363</v>
+        <v>1369</v>
       </c>
       <c r="F1" s="34" t="s">
-        <v>1364</v>
+        <v>1370</v>
       </c>
       <c r="G1" s="34" t="s">
-        <v>1365</v>
+        <v>1371</v>
       </c>
       <c r="H1" s="34" t="s">
-        <v>1366</v>
+        <v>1372</v>
       </c>
       <c r="I1" s="34" t="s">
-        <v>1367</v>
+        <v>1373</v>
       </c>
       <c r="J1" s="34" t="s">
-        <v>1368</v>
+        <v>1374</v>
       </c>
       <c r="K1" s="34" t="s">
-        <v>1369</v>
+        <v>1375</v>
       </c>
       <c r="L1" s="34" t="s">
-        <v>1370</v>
+        <v>1376</v>
       </c>
       <c r="M1" s="34" t="s">
-        <v>1371</v>
+        <v>1377</v>
       </c>
       <c r="N1" s="34" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="O1" s="34" t="s">
-        <v>1373</v>
+        <v>1379</v>
       </c>
       <c r="P1" s="34" t="s">
-        <v>1374</v>
+        <v>1380</v>
       </c>
       <c r="Q1" s="34" t="s">
-        <v>1375</v>
+        <v>1381</v>
       </c>
       <c r="R1" s="34" t="s">
-        <v>1376</v>
+        <v>1382</v>
       </c>
       <c r="S1" s="34" t="s">
-        <v>1377</v>
+        <v>1383</v>
       </c>
       <c r="T1" s="34" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="U1" s="34" t="s">
-        <v>1379</v>
+        <v>1385</v>
       </c>
       <c r="V1" s="34" t="s">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="W1" s="34" t="s">
-        <v>1381</v>
+        <v>1387</v>
       </c>
       <c r="X1" s="34" t="s">
-        <v>1382</v>
+        <v>1388</v>
       </c>
       <c r="Y1" s="34" t="s">
-        <v>1383</v>
+        <v>1389</v>
       </c>
       <c r="Z1" s="34" t="s">
-        <v>1384</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="35" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>1385</v>
+        <v>1391</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>1386</v>
+        <v>1392</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>1254</v>
+        <v>1260</v>
       </c>
       <c r="E2" s="35" t="s">
         <v>160</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>1387</v>
+        <v>1393</v>
       </c>
       <c r="G2" s="36"/>
       <c r="H2" s="36"/>
@@ -16117,7 +16159,7 @@
         <v>143</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="C3" s="35"/>
       <c r="D3" s="35"/>
@@ -16149,64 +16191,64 @@
         <v>93</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>1387</v>
+        <v>1393</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>1254</v>
+        <v>1260</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1390</v>
+        <v>1396</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1391</v>
+        <v>1397</v>
       </c>
       <c r="G4" s="36" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="H4" s="36" t="s">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="I4" s="36" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>1395</v>
+        <v>1401</v>
       </c>
       <c r="K4" s="36" t="s">
-        <v>1396</v>
+        <v>1402</v>
       </c>
       <c r="L4" s="36" t="s">
-        <v>1397</v>
+        <v>1403</v>
       </c>
       <c r="M4" s="36" t="s">
-        <v>1398</v>
+        <v>1404</v>
       </c>
       <c r="N4" s="36" t="s">
-        <v>1399</v>
+        <v>1405</v>
       </c>
       <c r="O4" s="36" t="s">
-        <v>1400</v>
+        <v>1406</v>
       </c>
       <c r="P4" s="36" t="s">
-        <v>1401</v>
+        <v>1407</v>
       </c>
       <c r="Q4" s="36" t="s">
-        <v>1402</v>
+        <v>1408</v>
       </c>
       <c r="R4" s="36" t="s">
-        <v>1403</v>
+        <v>1409</v>
       </c>
       <c r="S4" s="36" t="s">
-        <v>1404</v>
+        <v>1410</v>
       </c>
       <c r="T4" s="36" t="s">
-        <v>1405</v>
+        <v>1411</v>
       </c>
       <c r="U4" s="36" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
       <c r="V4" s="36"/>
       <c r="W4" s="36"/>
@@ -16219,22 +16261,22 @@
         <v>136</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>1409</v>
+        <v>1415</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1410</v>
+        <v>1416</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1411</v>
+        <v>1417</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>1412</v>
+        <v>1418</v>
       </c>
       <c r="H5" s="36"/>
       <c r="I5" s="36"/>
@@ -16264,16 +16306,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>1273</v>
+        <v>1279</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>1413</v>
+        <v>1419</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>1414</v>
+        <v>1420</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>1415</v>
+        <v>1421</v>
       </c>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
@@ -16304,25 +16346,25 @@
         <v>5</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>1273</v>
+        <v>1279</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>1413</v>
+        <v>1419</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>1414</v>
+        <v>1420</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>1415</v>
+        <v>1421</v>
       </c>
       <c r="G7" s="36" t="s">
-        <v>1416</v>
+        <v>1422</v>
       </c>
       <c r="H7" s="36" t="s">
-        <v>1417</v>
+        <v>1423</v>
       </c>
       <c r="I7" s="36" t="s">
-        <v>1278</v>
+        <v>1284</v>
       </c>
       <c r="J7" s="36"/>
       <c r="K7" s="36"/>
@@ -16344,16 +16386,16 @@
     </row>
     <row r="8" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="35" t="s">
-        <v>1418</v>
+        <v>1424</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>1419</v>
+        <v>1425</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>1420</v>
+        <v>1426</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="E8" s="35" t="s">
         <v>245</v>
@@ -16385,13 +16427,13 @@
         <v>28</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>1421</v>
+        <v>1427</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>1422</v>
+        <v>1428</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>1423</v>
+        <v>1429</v>
       </c>
       <c r="E9" s="35"/>
       <c r="F9" s="35"/>
@@ -16418,25 +16460,25 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="35" t="s">
-        <v>1279</v>
+        <v>1285</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>1424</v>
+        <v>1430</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>1240</v>
+        <v>1246</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1425</v>
+        <v>1431</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1426</v>
+        <v>1432</v>
       </c>
       <c r="G10" s="36" t="s">
-        <v>1427</v>
+        <v>1433</v>
       </c>
       <c r="H10" s="36"/>
       <c r="I10" s="36"/>
@@ -16463,10 +16505,10 @@
         <v>111</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>1428</v>
+        <v>1434</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>1234</v>
+        <v>1240</v>
       </c>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
@@ -16494,28 +16536,28 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="37" t="s">
-        <v>1049</v>
+        <v>1055</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>1429</v>
+        <v>1435</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>1430</v>
+        <v>1436</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>1431</v>
+        <v>1437</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>1432</v>
+        <v>1438</v>
       </c>
       <c r="G12" s="36" t="s">
-        <v>1228</v>
+        <v>1234</v>
       </c>
       <c r="H12" s="36" t="s">
-        <v>1433</v>
+        <v>1439</v>
       </c>
       <c r="I12" s="36"/>
       <c r="J12" s="36"/>
@@ -16541,10 +16583,10 @@
         <v>42</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>1246</v>
+        <v>1252</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>1228</v>
+        <v>1234</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="37"/>
@@ -16575,16 +16617,16 @@
         <v>97</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>1434</v>
+        <v>1440</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>1435</v>
+        <v>1441</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>1436</v>
+        <v>1442</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="F14" s="37"/>
       <c r="G14" s="36"/>
@@ -16616,25 +16658,25 @@
         <v>5</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>1273</v>
+        <v>1279</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>1413</v>
+        <v>1419</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>1414</v>
+        <v>1420</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>1415</v>
+        <v>1421</v>
       </c>
       <c r="G15" s="36" t="s">
-        <v>1416</v>
+        <v>1422</v>
       </c>
       <c r="H15" s="36" t="s">
-        <v>1417</v>
+        <v>1423</v>
       </c>
       <c r="I15" s="36" t="s">
-        <v>1278</v>
+        <v>1284</v>
       </c>
       <c r="J15" s="36"/>
       <c r="K15" s="36"/>
@@ -16656,19 +16698,19 @@
     </row>
     <row r="16" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="37" t="s">
-        <v>1438</v>
+        <v>1444</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>1439</v>
+        <v>1445</v>
       </c>
       <c r="C16" s="37" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>1234</v>
+        <v>1240</v>
       </c>
       <c r="F16" s="37"/>
       <c r="G16" s="36"/>
@@ -16694,13 +16736,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="37" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>1440</v>
+        <v>1446</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>1441</v>
+        <v>1447</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="37"/>
@@ -16731,7 +16773,7 @@
         <v>125</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>1442</v>
+        <v>1448</v>
       </c>
       <c r="C18" s="37"/>
       <c r="D18" s="37"/>
@@ -16760,10 +16802,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="37" t="s">
-        <v>1443</v>
+        <v>1449</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>1444</v>
+        <v>1450</v>
       </c>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
@@ -16795,7 +16837,7 @@
         <v>182</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>1445</v>
+        <v>1451</v>
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="37"/>
@@ -16824,10 +16866,10 @@
     </row>
     <row r="21" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="37" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>1446</v>
+        <v>1452</v>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="37"/>
@@ -16862,43 +16904,43 @@
         <v>5</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>1273</v>
+        <v>1279</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>1413</v>
+        <v>1419</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>1414</v>
+        <v>1420</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>1415</v>
+        <v>1421</v>
       </c>
       <c r="G22" s="36" t="s">
-        <v>1447</v>
+        <v>1453</v>
       </c>
       <c r="H22" s="36" t="s">
-        <v>1448</v>
+        <v>1454</v>
       </c>
       <c r="I22" s="36" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="J22" s="36" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="K22" s="36" t="s">
-        <v>1451</v>
+        <v>1457</v>
       </c>
       <c r="L22" s="36" t="s">
-        <v>1452</v>
+        <v>1458</v>
       </c>
       <c r="M22" s="36" t="s">
-        <v>1416</v>
+        <v>1422</v>
       </c>
       <c r="N22" s="36" t="s">
-        <v>1417</v>
+        <v>1423</v>
       </c>
       <c r="O22" s="36" t="s">
-        <v>1278</v>
+        <v>1284</v>
       </c>
       <c r="P22" s="36"/>
       <c r="Q22" s="36"/>
@@ -16914,10 +16956,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="37" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>1453</v>
+        <v>1459</v>
       </c>
       <c r="C23" s="37"/>
       <c r="D23" s="37"/>
@@ -16949,28 +16991,28 @@
         <v>99</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>1457</v>
+        <v>1463</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>1458</v>
+        <v>1464</v>
       </c>
       <c r="G24" s="36" t="s">
-        <v>1459</v>
+        <v>1465</v>
       </c>
       <c r="H24" s="36" t="s">
-        <v>1460</v>
+        <v>1466</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>1461</v>
+        <v>1467</v>
       </c>
       <c r="J24" s="36"/>
       <c r="K24" s="36"/>
@@ -16995,7 +17037,7 @@
         <v>262</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="C25" s="37"/>
       <c r="D25" s="37"/>
@@ -17027,10 +17069,10 @@
         <v>46</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>1462</v>
+        <v>1468</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>1463</v>
+        <v>1469</v>
       </c>
       <c r="D26" s="37"/>
       <c r="E26" s="37"/>
@@ -17058,10 +17100,10 @@
     </row>
     <row r="27" customFormat="false" ht="31.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="37" t="s">
-        <v>1324</v>
+        <v>1330</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>1464</v>
+        <v>1470</v>
       </c>
       <c r="C27" s="37"/>
       <c r="D27" s="37"/>
@@ -17093,7 +17135,7 @@
         <v>202</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>1465</v>
+        <v>1471</v>
       </c>
       <c r="C28" s="37"/>
       <c r="D28" s="37"/>
@@ -17125,7 +17167,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>1466</v>
+        <v>1472</v>
       </c>
       <c r="C29" s="37"/>
       <c r="D29" s="37"/>
@@ -17157,7 +17199,7 @@
         <v>140</v>
       </c>
       <c r="B30" s="37" t="s">
-        <v>1429</v>
+        <v>1435</v>
       </c>
       <c r="C30" s="37"/>
       <c r="D30" s="37"/>
@@ -17192,25 +17234,25 @@
         <v>5</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>1273</v>
+        <v>1279</v>
       </c>
       <c r="D31" s="36" t="s">
-        <v>1413</v>
+        <v>1419</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>1414</v>
+        <v>1420</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>1415</v>
+        <v>1421</v>
       </c>
       <c r="G31" s="36" t="s">
-        <v>1416</v>
+        <v>1422</v>
       </c>
       <c r="H31" s="36" t="s">
-        <v>1417</v>
+        <v>1423</v>
       </c>
       <c r="I31" s="36" t="s">
-        <v>1278</v>
+        <v>1284</v>
       </c>
       <c r="J31" s="37"/>
       <c r="K31" s="37"/>
@@ -17270,43 +17312,43 @@
         <v>5</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>1273</v>
+        <v>1279</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>1413</v>
+        <v>1419</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>1414</v>
+        <v>1420</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>1415</v>
+        <v>1421</v>
       </c>
       <c r="G33" s="36" t="s">
-        <v>1447</v>
+        <v>1453</v>
       </c>
       <c r="H33" s="36" t="s">
-        <v>1448</v>
+        <v>1454</v>
       </c>
       <c r="I33" s="36" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="J33" s="36" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="K33" s="36" t="s">
-        <v>1451</v>
+        <v>1457</v>
       </c>
       <c r="L33" s="36" t="s">
-        <v>1452</v>
+        <v>1458</v>
       </c>
       <c r="M33" s="36" t="s">
-        <v>1416</v>
+        <v>1422</v>
       </c>
       <c r="N33" s="36" t="s">
-        <v>1417</v>
+        <v>1423</v>
       </c>
       <c r="O33" s="36" t="s">
-        <v>1278</v>
+        <v>1284</v>
       </c>
       <c r="P33" s="36"/>
       <c r="Q33" s="37"/>
@@ -17322,10 +17364,10 @@
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="37" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>1467</v>
+        <v>1473</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -17357,7 +17399,7 @@
         <v>282</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>1445</v>
+        <v>1451</v>
       </c>
       <c r="C35" s="37"/>
       <c r="D35" s="37"/>
@@ -17389,7 +17431,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="37" t="s">
-        <v>1429</v>
+        <v>1435</v>
       </c>
       <c r="C36" s="37"/>
       <c r="D36" s="37"/>
@@ -17418,10 +17460,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="37" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="B37" s="37" t="s">
-        <v>1468</v>
+        <v>1474</v>
       </c>
       <c r="C37" s="37"/>
       <c r="D37" s="37"/>
@@ -17453,16 +17495,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>1469</v>
+        <v>1475</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>1470</v>
+        <v>1476</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>1472</v>
+        <v>1478</v>
       </c>
       <c r="F38" s="37"/>
       <c r="G38" s="36"/>
@@ -17491,22 +17533,22 @@
         <v>95</v>
       </c>
       <c r="B39" s="37" t="s">
-        <v>1473</v>
+        <v>1479</v>
       </c>
       <c r="C39" s="37" t="s">
-        <v>1444</v>
+        <v>1450</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>1474</v>
+        <v>1480</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>1334</v>
+        <v>1340</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>1475</v>
+        <v>1481</v>
       </c>
       <c r="G39" s="36" t="s">
-        <v>1476</v>
+        <v>1482</v>
       </c>
       <c r="H39" s="36"/>
       <c r="I39" s="36"/>
@@ -17530,25 +17572,25 @@
     </row>
     <row r="40" customFormat="false" ht="31.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="37" t="s">
-        <v>1348</v>
+        <v>1354</v>
       </c>
       <c r="B40" s="37" t="s">
-        <v>1477</v>
+        <v>1483</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>1240</v>
+        <v>1246</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>1478</v>
+        <v>1484</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>1479</v>
+        <v>1485</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>1480</v>
+        <v>1486</v>
       </c>
       <c r="G40" s="36" t="s">
-        <v>1255</v>
+        <v>1261</v>
       </c>
       <c r="H40" s="36"/>
       <c r="I40" s="36"/>
@@ -17572,10 +17614,10 @@
     </row>
     <row r="41" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="37" t="s">
-        <v>1046</v>
+        <v>1052</v>
       </c>
       <c r="B41" s="37" t="s">
-        <v>1481</v>
+        <v>1487</v>
       </c>
       <c r="C41" s="37"/>
       <c r="D41" s="37"/>
@@ -17604,10 +17646,10 @@
     </row>
     <row r="42" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="37" t="s">
-        <v>1352</v>
+        <v>1358</v>
       </c>
       <c r="B42" s="37" t="s">
-        <v>1482</v>
+        <v>1488</v>
       </c>
       <c r="C42" s="37"/>
       <c r="D42" s="37"/>
@@ -17639,13 +17681,13 @@
         <v>123</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>1483</v>
+        <v>1489</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>1240</v>
+        <v>1246</v>
       </c>
       <c r="D43" s="37" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="E43" s="37"/>
       <c r="F43" s="37"/>
@@ -17675,7 +17717,7 @@
         <v>228</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>1484</v>
+        <v>1490</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -17704,13 +17746,13 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="37" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="B45" s="37" t="s">
-        <v>1485</v>
+        <v>1491</v>
       </c>
       <c r="C45" s="37" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="D45" s="37"/>
       <c r="E45" s="37"/>
@@ -17741,58 +17783,58 @@
         <v>456</v>
       </c>
       <c r="B46" s="37" t="s">
-        <v>1487</v>
+        <v>1493</v>
       </c>
       <c r="C46" s="37" t="s">
-        <v>1488</v>
+        <v>1494</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>1477</v>
+        <v>1483</v>
       </c>
       <c r="E46" s="37" t="s">
-        <v>1489</v>
+        <v>1495</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>1490</v>
+        <v>1496</v>
       </c>
       <c r="G46" s="36" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="H46" s="36" t="s">
-        <v>1492</v>
+        <v>1498</v>
       </c>
       <c r="I46" s="36" t="s">
-        <v>1493</v>
+        <v>1499</v>
       </c>
       <c r="J46" s="36" t="s">
-        <v>1494</v>
+        <v>1500</v>
       </c>
       <c r="K46" s="36" t="s">
-        <v>1495</v>
+        <v>1501</v>
       </c>
       <c r="L46" s="36" t="s">
-        <v>1496</v>
+        <v>1502</v>
       </c>
       <c r="M46" s="36" t="s">
-        <v>1497</v>
+        <v>1503</v>
       </c>
       <c r="N46" s="36" t="s">
-        <v>1498</v>
+        <v>1504</v>
       </c>
       <c r="O46" s="36" t="s">
-        <v>1499</v>
+        <v>1505</v>
       </c>
       <c r="P46" s="36" t="s">
-        <v>1500</v>
+        <v>1506</v>
       </c>
       <c r="Q46" s="36" t="s">
-        <v>1501</v>
+        <v>1507</v>
       </c>
       <c r="R46" s="36" t="s">
-        <v>1502</v>
+        <v>1508</v>
       </c>
       <c r="S46" s="36" t="s">
-        <v>1503</v>
+        <v>1509</v>
       </c>
       <c r="T46" s="36"/>
       <c r="U46" s="36"/>

--- a/REFERENCE.xlsx
+++ b/REFERENCE.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="MATERIALS" sheetId="1" state="visible" r:id="rId2"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2469" uniqueCount="1630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2471" uniqueCount="1632">
   <si>
     <t xml:space="preserve">MATERIAL NAME</t>
   </si>
@@ -3187,6 +3187,12 @@
   </si>
   <si>
     <t xml:space="preserve">R208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAL 6037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R209</t>
   </si>
   <si>
     <t xml:space="preserve">TEAKWOOD</t>
@@ -6777,178 +6783,178 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="38" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="B1" s="38" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="39" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="39" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="B3" s="40" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="39" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="39" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="39" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="39" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="39" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="39" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="39" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="39" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="39" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="39" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="39" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="39" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="39" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="39" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="39" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="39" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="39" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="39" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="39" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="B22" s="40" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
     </row>
   </sheetData>
@@ -6980,99 +6986,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="41" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="C1" s="41" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="D1" s="41" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="E1" s="41" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="F1" s="41" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="G1" s="41" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="H1" s="41" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="I1" s="41" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="J1" s="41" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="K1" s="41" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="L1" s="41" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="M1" s="41" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="N1" s="41" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="O1" s="41" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="P1" s="41" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="Q1" s="41" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="R1" s="41" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="S1" s="41" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="T1" s="41" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="U1" s="41" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="V1" s="41" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="W1" s="41" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="X1" s="41" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="Y1" s="41" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="Z1" s="41" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="35" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="E2" s="35" t="s">
         <v>160</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="G2" s="36"/>
       <c r="H2" s="36"/>
@@ -7100,10 +7106,10 @@
         <v>143</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="D3" s="35"/>
       <c r="E3" s="35"/>
@@ -7134,64 +7140,64 @@
         <v>93</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="G4" s="36" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="H4" s="36" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="I4" s="36" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="K4" s="36" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="L4" s="36" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="M4" s="36" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="N4" s="36" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="O4" s="36" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="P4" s="36" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="Q4" s="36" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="R4" s="36" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="S4" s="36" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="T4" s="36" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="U4" s="43" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="V4" s="36"/>
       <c r="W4" s="42"/>
@@ -7204,22 +7210,22 @@
         <v>136</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="H5" s="36"/>
       <c r="I5" s="36"/>
@@ -7246,19 +7252,19 @@
         <v>23</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
@@ -7286,13 +7292,13 @@
         <v>85</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="E7" s="35"/>
       <c r="F7" s="35"/>
@@ -7319,16 +7325,16 @@
     </row>
     <row r="8" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="35" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="E8" s="35" t="s">
         <v>245</v>
@@ -7360,13 +7366,13 @@
         <v>28</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="E9" s="35"/>
       <c r="F9" s="35"/>
@@ -7393,25 +7399,25 @@
     </row>
     <row r="10" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="35" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="G10" s="36" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="H10" s="36"/>
       <c r="I10" s="36"/>
@@ -7438,10 +7444,10 @@
         <v>111</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
@@ -7469,28 +7475,28 @@
     </row>
     <row r="12" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="37" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="G12" s="36" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="H12" s="36" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="I12" s="36"/>
       <c r="J12" s="36"/>
@@ -7516,10 +7522,10 @@
         <v>42</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="37"/>
@@ -7550,16 +7556,16 @@
         <v>97</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="F14" s="37"/>
       <c r="G14" s="36"/>
@@ -7588,96 +7594,96 @@
         <v>6</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="G15" s="36" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="H15" s="36" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="I15" s="36" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="J15" s="36" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="K15" s="36" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="L15" s="36" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="M15" s="36" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="N15" s="36" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="O15" s="36" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="P15" s="36" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="Q15" s="36" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="R15" s="36" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="S15" s="36" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="T15" s="36" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="U15" s="36" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="V15" s="36" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="W15" s="36" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="X15" s="36" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="Y15" s="36" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="Z15" s="44" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="37" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="C16" s="37" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="F16" s="37"/>
       <c r="G16" s="36"/>
@@ -7703,13 +7709,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="37" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="37"/>
@@ -7740,7 +7746,7 @@
         <v>125</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="C18" s="37"/>
       <c r="D18" s="37"/>
@@ -7769,10 +7775,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="37" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
@@ -7804,7 +7810,7 @@
         <v>182</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="37"/>
@@ -7833,10 +7839,10 @@
     </row>
     <row r="21" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="37" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="37"/>
@@ -7868,28 +7874,28 @@
         <v>74</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="M22" s="36"/>
       <c r="N22" s="36"/>
@@ -7908,10 +7914,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="37" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="C23" s="37"/>
       <c r="D23" s="37"/>
@@ -7943,28 +7949,28 @@
         <v>99</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="G24" s="36" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="H24" s="36" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="J24" s="36"/>
       <c r="K24" s="36"/>
@@ -7989,7 +7995,7 @@
         <v>262</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="C25" s="37"/>
       <c r="D25" s="37"/>
@@ -8021,10 +8027,10 @@
         <v>46</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="D26" s="37"/>
       <c r="E26" s="37"/>
@@ -8052,10 +8058,10 @@
     </row>
     <row r="27" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="37" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="C27" s="37"/>
       <c r="D27" s="37"/>
@@ -8087,7 +8093,7 @@
         <v>202</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="C28" s="37"/>
       <c r="D28" s="37"/>
@@ -8119,7 +8125,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="C29" s="37"/>
       <c r="D29" s="37"/>
@@ -8151,7 +8157,7 @@
         <v>140</v>
       </c>
       <c r="B30" s="37" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="C30" s="37"/>
       <c r="D30" s="37"/>
@@ -8183,76 +8189,76 @@
         <v>8</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="C31" s="36" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D31" s="36" t="s">
+        <v>1603</v>
+      </c>
+      <c r="E31" s="36" t="s">
+        <v>1609</v>
+      </c>
+      <c r="F31" s="37" t="s">
+        <v>1605</v>
+      </c>
+      <c r="G31" s="37" t="s">
+        <v>1539</v>
+      </c>
+      <c r="H31" s="37" t="s">
         <v>1606</v>
       </c>
-      <c r="D31" s="36" t="s">
-        <v>1601</v>
-      </c>
-      <c r="E31" s="36" t="s">
-        <v>1607</v>
-      </c>
-      <c r="F31" s="37" t="s">
-        <v>1603</v>
-      </c>
-      <c r="G31" s="37" t="s">
-        <v>1537</v>
-      </c>
-      <c r="H31" s="37" t="s">
-        <v>1604</v>
-      </c>
       <c r="I31" s="37" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="J31" s="37" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="K31" s="37" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="L31" s="37" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="M31" s="37" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="N31" s="36" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="O31" s="37" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="P31" s="36" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="Q31" s="36" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="R31" s="36" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="S31" s="36" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="T31" s="36" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="U31" s="36" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="V31" s="36" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="W31" s="36" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="X31" s="36" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="Y31" s="36" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
@@ -8302,79 +8308,79 @@
         <v>3</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="J33" s="36" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="K33" s="36" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="L33" s="36" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="M33" s="36" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="N33" s="36" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="O33" s="36" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="P33" s="36" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="Q33" s="37" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="R33" s="37" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="S33" s="37" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="T33" s="36" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="U33" s="36" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="V33" s="36" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="W33" s="36" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
       <c r="X33" s="36" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="Y33" s="36" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="Z33" s="36" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
@@ -8389,10 +8395,10 @@
     </row>
     <row r="34" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="37" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -8424,7 +8430,7 @@
         <v>282</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="C35" s="37"/>
       <c r="D35" s="37"/>
@@ -8456,7 +8462,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="37" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="C36" s="37"/>
       <c r="D36" s="37"/>
@@ -8485,10 +8491,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="37" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="B37" s="37" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="C37" s="37"/>
       <c r="D37" s="37"/>
@@ -8520,16 +8526,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="F38" s="37"/>
       <c r="G38" s="36"/>
@@ -8558,22 +8564,22 @@
         <v>95</v>
       </c>
       <c r="B39" s="37" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="C39" s="37" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="G39" s="36" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="H39" s="36"/>
       <c r="I39" s="36"/>
@@ -8597,25 +8603,25 @@
     </row>
     <row r="40" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="37" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="B40" s="37" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="G40" s="36" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="H40" s="36"/>
       <c r="I40" s="36"/>
@@ -8639,10 +8645,10 @@
     </row>
     <row r="41" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="37" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="B41" s="37" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="C41" s="37"/>
       <c r="D41" s="37"/>
@@ -8671,10 +8677,10 @@
     </row>
     <row r="42" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="37" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="B42" s="37" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="C42" s="37"/>
       <c r="D42" s="37"/>
@@ -8706,13 +8712,13 @@
         <v>123</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="D43" s="37" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="E43" s="37"/>
       <c r="F43" s="37"/>
@@ -8742,7 +8748,7 @@
         <v>228</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -8771,13 +8777,13 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="37" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="B45" s="37" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="C45" s="37" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="D45" s="37"/>
       <c r="E45" s="37"/>
@@ -8808,58 +8814,58 @@
         <v>456</v>
       </c>
       <c r="B46" s="37" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="C46" s="37" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="E46" s="37" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="G46" s="36" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="H46" s="36" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="I46" s="36" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="J46" s="36" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="K46" s="36" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="L46" s="36" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="M46" s="36" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="N46" s="36" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="O46" s="36" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="P46" s="36" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="Q46" s="36" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="R46" s="36" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="S46" s="36" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="T46" s="36"/>
       <c r="U46" s="36"/>
@@ -8894,10 +8900,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="46" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="B1" s="46" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12287,7 +12293,7 @@
     <tabColor rgb="FF2F5496"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B110"/>
+  <dimension ref="A1:B111"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
@@ -13172,6 +13178,14 @@
       </c>
       <c r="B110" s="19" t="s">
         <v>1051</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="19" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B111" s="19" t="s">
+        <v>1053</v>
       </c>
     </row>
   </sheetData>
@@ -13246,7 +13260,7 @@
         <v>93</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="F1" s="20" t="s">
         <v>43</v>
@@ -13261,7 +13275,7 @@
         <v>136</v>
       </c>
       <c r="J1" s="20" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="K1" s="20" t="s">
         <v>28</v>
@@ -13270,19 +13284,19 @@
         <v>111</v>
       </c>
       <c r="M1" s="20" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="N1" s="20" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="O1" s="20" t="s">
         <v>143</v>
       </c>
       <c r="P1" s="20" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="Q1" s="20" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="R1" s="21" t="s">
         <v>350</v>
@@ -13294,10 +13308,10 @@
         <v>97</v>
       </c>
       <c r="U1" s="21" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="V1" s="21" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="W1" s="21" t="s">
         <v>99</v>
@@ -13306,13 +13320,13 @@
         <v>128</v>
       </c>
       <c r="Y1" s="21" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="Z1" s="21" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="AA1" s="21" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="AB1" s="21" t="s">
         <v>182</v>
@@ -13327,7 +13341,7 @@
         <v>228</v>
       </c>
       <c r="AF1" s="21" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="AG1" s="21" t="s">
         <v>85</v>
@@ -13356,570 +13370,570 @@
     </row>
     <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="F2" s="10" t="s">
+        <v>1071</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>1072</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>1074</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>1075</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>1076</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>1077</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>1078</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>1079</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>1079</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>1080</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>1081</v>
+      </c>
+      <c r="R2" s="10" t="s">
+        <v>1070</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>1069</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="V2" s="10" t="s">
         <v>1070</v>
       </c>
-      <c r="H2" s="10" t="s">
-        <v>1071</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>1072</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>1073</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>1074</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>1075</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>1076</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>1077</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>1077</v>
-      </c>
-      <c r="P2" s="10" t="s">
-        <v>1078</v>
-      </c>
-      <c r="Q2" s="10" t="s">
-        <v>1079</v>
-      </c>
-      <c r="R2" s="10" t="s">
-        <v>1068</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>1080</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>1081</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>1067</v>
-      </c>
-      <c r="V2" s="10" t="s">
-        <v>1068</v>
-      </c>
       <c r="W2" s="1" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>456</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="AB2" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="AD2" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="AE2" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="AG2" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="AN2" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="J3" s="10" t="s">
         <v>456</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="N3" s="10" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="O3" s="10" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="P3" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="Q3" s="10" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="R3" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="S3" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="U3" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="V3" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="X3" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="Y3" s="10" t="s">
+        <v>1070</v>
+      </c>
+      <c r="Z3" s="10" t="s">
+        <v>1070</v>
+      </c>
+      <c r="AA3" s="10" t="s">
+        <v>1070</v>
+      </c>
+      <c r="AB3" s="10" t="s">
         <v>1103</v>
       </c>
-      <c r="Y3" s="10" t="s">
-        <v>1068</v>
-      </c>
-      <c r="Z3" s="10" t="s">
-        <v>1068</v>
-      </c>
-      <c r="AA3" s="10" t="s">
-        <v>1068</v>
-      </c>
-      <c r="AB3" s="10" t="s">
-        <v>1101</v>
-      </c>
       <c r="AC3" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="AD3" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="AE3" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="AG3" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="AH3" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="AI3" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="AJ3" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="AK3" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="AL3" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="AM3" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="AN3" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>1111</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>1112</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>1107</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>1108</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>1109</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>1110</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>1105</v>
-      </c>
       <c r="H4" s="10" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="O4" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="P4" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="Q4" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="R4" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="S4" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="T4" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="U4" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="V4" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="Y4" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="Z4" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="AA4" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="AB4" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="AC4" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="AD4" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="AE4" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="AF4" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="AG4" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="AH4" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="AI4" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="AJ4" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="AK4" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="AL4" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="AM4" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="AN4" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="H5" s="10" t="s">
         <v>456</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="O5" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="Q5" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="S5" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="T5" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="U5" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="Y5" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="Z5" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="AA5" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="AB5" s="10"/>
       <c r="AC5" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="AD5" s="10"/>
       <c r="AF5" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="AH5" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="AK5" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="AL5" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="AM5" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="K6" s="10" t="s">
+        <v>1131</v>
+      </c>
+      <c r="L6" s="10" t="s">
         <v>1129</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>1127</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="O6" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="P6" s="22"/>
       <c r="Q6" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="T6" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="AF6" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="K7" s="10" t="s">
+        <v>1138</v>
+      </c>
+      <c r="L7" s="10" t="s">
         <v>1136</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>1134</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
@@ -13927,44 +13941,44 @@
       <c r="P7" s="22"/>
       <c r="Q7" s="22"/>
       <c r="W7" s="1" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="I8" s="22"/>
       <c r="J8" s="22"/>
       <c r="K8" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
@@ -13972,44 +13986,44 @@
       <c r="P8" s="22"/>
       <c r="Q8" s="22"/>
       <c r="W8" s="1" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="X8" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="I9" s="22"/>
       <c r="J9" s="22"/>
       <c r="K9" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="M9" s="22"/>
       <c r="N9" s="22"/>
@@ -14017,42 +14031,42 @@
       <c r="P9" s="22"/>
       <c r="Q9" s="22"/>
       <c r="W9" s="1" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="X9" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="E10" s="22"/>
       <c r="F10" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="I10" s="22"/>
       <c r="J10" s="22"/>
       <c r="K10" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="M10" s="22"/>
       <c r="N10" s="22"/>
@@ -14060,38 +14074,38 @@
       <c r="P10" s="22"/>
       <c r="Q10" s="22"/>
       <c r="W10" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="X10" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="E11" s="22"/>
       <c r="F11" s="22"/>
       <c r="G11" s="10" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="I11" s="22"/>
       <c r="J11" s="22"/>
       <c r="K11" s="22"/>
       <c r="L11" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="M11" s="22"/>
       <c r="N11" s="22"/>
@@ -14099,29 +14113,29 @@
       <c r="P11" s="22"/>
       <c r="Q11" s="22"/>
       <c r="W11" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="E12" s="22"/>
       <c r="F12" s="22"/>
       <c r="G12" s="10" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="I12" s="22"/>
       <c r="J12" s="22"/>
@@ -14133,29 +14147,29 @@
       <c r="P12" s="22"/>
       <c r="Q12" s="22"/>
       <c r="W12" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="E13" s="22"/>
       <c r="F13" s="22"/>
       <c r="G13" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="I13" s="22"/>
       <c r="J13" s="22"/>
@@ -14169,24 +14183,24 @@
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="E14" s="22"/>
       <c r="F14" s="22"/>
       <c r="G14" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="I14" s="22"/>
       <c r="J14" s="22"/>
@@ -14200,24 +14214,24 @@
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="E15" s="22"/>
       <c r="F15" s="22"/>
       <c r="G15" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="I15" s="22"/>
       <c r="J15" s="22"/>
@@ -14231,20 +14245,20 @@
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
       <c r="F16" s="22"/>
       <c r="G16" s="22"/>
       <c r="H16" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="I16" s="22"/>
       <c r="J16" s="22"/>
@@ -14258,20 +14272,20 @@
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="D17" s="22"/>
       <c r="E17" s="22"/>
       <c r="F17" s="22"/>
       <c r="G17" s="22"/>
       <c r="H17" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="I17" s="22"/>
       <c r="J17" s="22"/>
@@ -14285,13 +14299,13 @@
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="D18" s="22"/>
       <c r="E18" s="22"/>
@@ -14310,13 +14324,13 @@
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="D19" s="22"/>
       <c r="E19" s="22"/>
@@ -14335,13 +14349,13 @@
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="D20" s="22"/>
       <c r="E20" s="22"/>
@@ -14360,13 +14374,13 @@
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="D21" s="22"/>
       <c r="E21" s="22"/>
@@ -14385,13 +14399,13 @@
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="22"/>
@@ -14410,13 +14424,13 @@
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="D23" s="22"/>
       <c r="E23" s="22"/>
@@ -14435,13 +14449,13 @@
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="D24" s="22"/>
       <c r="E24" s="22"/>
@@ -14460,13 +14474,13 @@
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="D25" s="22"/>
       <c r="E25" s="22"/>
@@ -14485,13 +14499,13 @@
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="22"/>
@@ -14510,13 +14524,13 @@
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="D27" s="22"/>
       <c r="E27" s="22"/>
@@ -14535,13 +14549,13 @@
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="D28" s="22"/>
       <c r="E28" s="22"/>
@@ -14560,13 +14574,13 @@
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="D29" s="22"/>
       <c r="E29" s="22"/>
@@ -14585,13 +14599,13 @@
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="D30" s="22"/>
       <c r="E30" s="22"/>
@@ -14610,13 +14624,13 @@
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="D31" s="22"/>
       <c r="E31" s="22"/>
@@ -14635,13 +14649,13 @@
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="D32" s="22"/>
       <c r="E32" s="22"/>
@@ -14660,13 +14674,13 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="D33" s="22"/>
       <c r="E33" s="22"/>
@@ -14685,13 +14699,13 @@
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="B34" s="22" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="D34" s="22"/>
       <c r="E34" s="22"/>
@@ -14710,13 +14724,13 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="D35" s="22"/>
       <c r="E35" s="22"/>
@@ -14735,13 +14749,13 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="D36" s="22"/>
       <c r="E36" s="22"/>
@@ -14760,10 +14774,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="C37" s="22"/>
       <c r="D37" s="22"/>
@@ -14783,10 +14797,10 @@
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C38" s="22"/>
       <c r="D38" s="22"/>
@@ -14806,10 +14820,10 @@
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="C39" s="22"/>
       <c r="D39" s="22"/>
@@ -14829,7 +14843,7 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B40" s="22"/>
       <c r="C40" s="22"/>
@@ -14850,7 +14864,7 @@
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="B41" s="22"/>
       <c r="C41" s="22"/>
@@ -14871,7 +14885,7 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
     </row>
   </sheetData>
@@ -14899,92 +14913,92 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="24" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="24" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14994,7 +15008,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
     </row>
   </sheetData>
@@ -15023,159 +15037,159 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B16" s="23" t="s">
         <v>1257</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="B20" s="23"/>
     </row>
@@ -15207,31 +15221,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="E1" s="26"/>
     </row>
     <row r="2" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="E2" s="28"/>
     </row>
@@ -15240,13 +15254,13 @@
         <v>143</v>
       </c>
       <c r="B3" s="27" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C3" s="27" t="s">
         <v>1270</v>
       </c>
-      <c r="C3" s="27" t="s">
-        <v>1268</v>
-      </c>
       <c r="D3" s="27" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="E3" s="28"/>
     </row>
@@ -15255,43 +15269,43 @@
         <v>93</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="E4" s="28"/>
     </row>
     <row r="5" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="E5" s="28"/>
     </row>
     <row r="6" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="E6" s="28"/>
     </row>
@@ -15300,13 +15314,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="E7" s="28"/>
     </row>
@@ -15315,43 +15329,43 @@
         <v>28</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="E8" s="28"/>
     </row>
     <row r="9" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="B9" s="27" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D9" s="27" t="s">
         <v>1280</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>1281</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>1278</v>
       </c>
       <c r="E9" s="28"/>
     </row>
     <row r="10" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="E10" s="28"/>
     </row>
@@ -15360,73 +15374,73 @@
         <v>111</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="E11" s="28"/>
     </row>
     <row r="12" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="E12" s="28"/>
     </row>
     <row r="13" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="E13" s="28"/>
     </row>
     <row r="14" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="E14" s="28"/>
     </row>
     <row r="15" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="E15" s="28"/>
     </row>
@@ -15435,13 +15449,13 @@
         <v>97</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="E16" s="28"/>
     </row>
@@ -15450,13 +15464,13 @@
         <v>6</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="E17" s="28"/>
     </row>
@@ -15465,22 +15479,22 @@
         <v>43</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="E18" s="28"/>
     </row>
     <row r="19" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="C19" s="27"/>
       <c r="D19" s="27"/>
@@ -15488,16 +15502,16 @@
     </row>
     <row r="20" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="27" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D20" s="27" t="s">
         <v>1309</v>
-      </c>
-      <c r="B20" s="27" t="s">
-        <v>1305</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>1306</v>
-      </c>
-      <c r="D20" s="27" t="s">
-        <v>1307</v>
       </c>
       <c r="E20" s="28"/>
     </row>
@@ -15506,13 +15520,13 @@
         <v>125</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="E21" s="28"/>
     </row>
@@ -15521,43 +15535,43 @@
         <v>182</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="E22" s="28"/>
     </row>
     <row r="23" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="30" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B23" s="31" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D23" s="27" t="s">
         <v>1315</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>1316</v>
-      </c>
-      <c r="D23" s="27" t="s">
-        <v>1313</v>
       </c>
       <c r="E23" s="28"/>
     </row>
     <row r="24" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="E24" s="28"/>
     </row>
@@ -15566,67 +15580,67 @@
         <v>74</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="E25" s="28"/>
     </row>
     <row r="26" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="27" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="B26" s="30" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="E26" s="28"/>
     </row>
     <row r="27" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="B27" s="27" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D27" s="27" t="s">
         <v>1293</v>
-      </c>
-      <c r="C27" s="27" t="s">
-        <v>1290</v>
-      </c>
-      <c r="D27" s="27" t="s">
-        <v>1291</v>
       </c>
       <c r="E27" s="28"/>
     </row>
     <row r="28" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="27" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="E28" s="28"/>
     </row>
     <row r="29" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="C29" s="27"/>
       <c r="D29" s="27"/>
@@ -15637,7 +15651,7 @@
         <v>160</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="C30" s="27"/>
       <c r="D30" s="27"/>
@@ -15648,13 +15662,13 @@
         <v>99</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="E31" s="28"/>
     </row>
@@ -15663,7 +15677,7 @@
         <v>262</v>
       </c>
       <c r="B32" s="32" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
@@ -15671,16 +15685,16 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="26" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="E33" s="26"/>
     </row>
@@ -15689,7 +15703,7 @@
         <v>46</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="C34" s="26"/>
       <c r="D34" s="26"/>
@@ -15697,10 +15711,10 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="26" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="C35" s="26"/>
       <c r="D35" s="26"/>
@@ -15708,16 +15722,16 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="26" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="E36" s="26"/>
     </row>
@@ -15726,7 +15740,7 @@
         <v>202</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="C37" s="26"/>
       <c r="D37" s="26"/>
@@ -15737,7 +15751,7 @@
         <v>205</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="C38" s="26"/>
       <c r="D38" s="26"/>
@@ -15748,7 +15762,7 @@
         <v>140</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="C39" s="26"/>
       <c r="D39" s="26"/>
@@ -15756,25 +15770,25 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="26" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="E40" s="26"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="26" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="C41" s="26"/>
       <c r="D41" s="26"/>
@@ -15782,16 +15796,16 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="26" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="B42" s="26" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="D42" s="26" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="E42" s="26"/>
     </row>
@@ -15800,7 +15814,7 @@
         <v>350</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="C43" s="26"/>
       <c r="D43" s="26"/>
@@ -15808,34 +15822,34 @@
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="26" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="E44" s="26"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="26" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="C45" s="26" t="s">
+        <v>1312</v>
+      </c>
+      <c r="D45" s="26" t="s">
+        <v>1313</v>
+      </c>
+      <c r="E45" s="26" t="s">
         <v>1310</v>
-      </c>
-      <c r="D45" s="26" t="s">
-        <v>1311</v>
-      </c>
-      <c r="E45" s="26" t="s">
-        <v>1308</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15843,7 +15857,7 @@
         <v>133</v>
       </c>
       <c r="B46" s="26" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="C46" s="26"/>
       <c r="D46" s="26"/>
@@ -15851,10 +15865,10 @@
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="26" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C47" s="26"/>
       <c r="D47" s="26"/>
@@ -15865,7 +15879,7 @@
         <v>128</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="C48" s="26"/>
       <c r="D48" s="26"/>
@@ -15876,67 +15890,67 @@
         <v>95</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="E49" s="26"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="26" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="D50" s="26" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="E50" s="26"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="26" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="D51" s="26" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="E51" s="26"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="26" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="B52" s="26" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="C52" s="26" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="D52" s="26" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="E52" s="26"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="26" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="C53" s="26"/>
       <c r="D53" s="26"/>
@@ -15944,10 +15958,10 @@
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="26" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="C54" s="26"/>
       <c r="D54" s="26"/>
@@ -15955,10 +15969,10 @@
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="26" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="C55" s="26"/>
       <c r="D55" s="26"/>
@@ -15966,10 +15980,10 @@
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="26" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="C56" s="26"/>
       <c r="D56" s="26"/>
@@ -15977,10 +15991,10 @@
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="26" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="C57" s="26"/>
       <c r="D57" s="26"/>
@@ -15988,10 +16002,10 @@
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="26" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="C58" s="26"/>
       <c r="D58" s="26"/>
@@ -16002,10 +16016,10 @@
         <v>456</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="D59" s="26"/>
       <c r="E59" s="26"/>
@@ -16039,99 +16053,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="34" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="C1" s="34" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="D1" s="34" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="E1" s="34" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="F1" s="34" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="G1" s="34" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="H1" s="34" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="I1" s="34" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="J1" s="34" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="K1" s="34" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="L1" s="34" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="M1" s="34" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="N1" s="34" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="O1" s="34" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="P1" s="34" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="Q1" s="34" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="R1" s="34" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="S1" s="34" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="T1" s="34" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="U1" s="34" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="V1" s="34" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="W1" s="34" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="X1" s="34" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="Y1" s="34" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="Z1" s="34" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="35" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="E2" s="35" t="s">
         <v>160</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="G2" s="36"/>
       <c r="H2" s="36"/>
@@ -16159,7 +16173,7 @@
         <v>143</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="C3" s="35"/>
       <c r="D3" s="35"/>
@@ -16191,64 +16205,64 @@
         <v>93</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="G4" s="36" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="H4" s="36" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="I4" s="36" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="K4" s="36" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="L4" s="36" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="M4" s="36" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="N4" s="36" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="O4" s="36" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="P4" s="36" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="Q4" s="36" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="R4" s="36" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="S4" s="36" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="T4" s="36" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="U4" s="36" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="V4" s="36"/>
       <c r="W4" s="36"/>
@@ -16261,22 +16275,22 @@
         <v>136</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="H5" s="36"/>
       <c r="I5" s="36"/>
@@ -16306,16 +16320,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
@@ -16346,25 +16360,25 @@
         <v>5</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="G7" s="36" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="H7" s="36" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="I7" s="36" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="J7" s="36"/>
       <c r="K7" s="36"/>
@@ -16386,16 +16400,16 @@
     </row>
     <row r="8" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="35" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="E8" s="35" t="s">
         <v>245</v>
@@ -16427,13 +16441,13 @@
         <v>28</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="E9" s="35"/>
       <c r="F9" s="35"/>
@@ -16460,25 +16474,25 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="35" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="G10" s="36" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="H10" s="36"/>
       <c r="I10" s="36"/>
@@ -16505,10 +16519,10 @@
         <v>111</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
@@ -16536,28 +16550,28 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="37" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="G12" s="36" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="H12" s="36" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="I12" s="36"/>
       <c r="J12" s="36"/>
@@ -16583,10 +16597,10 @@
         <v>42</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="37"/>
@@ -16617,16 +16631,16 @@
         <v>97</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="F14" s="37"/>
       <c r="G14" s="36"/>
@@ -16658,25 +16672,25 @@
         <v>5</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="G15" s="36" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="H15" s="36" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="I15" s="36" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="J15" s="36"/>
       <c r="K15" s="36"/>
@@ -16698,19 +16712,19 @@
     </row>
     <row r="16" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="37" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="C16" s="37" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="F16" s="37"/>
       <c r="G16" s="36"/>
@@ -16736,13 +16750,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="37" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="37"/>
@@ -16773,7 +16787,7 @@
         <v>125</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="C18" s="37"/>
       <c r="D18" s="37"/>
@@ -16802,10 +16816,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="37" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
@@ -16837,7 +16851,7 @@
         <v>182</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="37"/>
@@ -16866,10 +16880,10 @@
     </row>
     <row r="21" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="37" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="37"/>
@@ -16904,43 +16918,43 @@
         <v>5</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="G22" s="36" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="H22" s="36" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="I22" s="36" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="J22" s="36" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="K22" s="36" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="L22" s="36" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="M22" s="36" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="N22" s="36" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="O22" s="36" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="P22" s="36"/>
       <c r="Q22" s="36"/>
@@ -16956,10 +16970,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="37" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="C23" s="37"/>
       <c r="D23" s="37"/>
@@ -16991,28 +17005,28 @@
         <v>99</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="G24" s="36" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="H24" s="36" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="J24" s="36"/>
       <c r="K24" s="36"/>
@@ -17037,7 +17051,7 @@
         <v>262</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="C25" s="37"/>
       <c r="D25" s="37"/>
@@ -17069,10 +17083,10 @@
         <v>46</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="D26" s="37"/>
       <c r="E26" s="37"/>
@@ -17100,10 +17114,10 @@
     </row>
     <row r="27" customFormat="false" ht="31.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="37" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="C27" s="37"/>
       <c r="D27" s="37"/>
@@ -17135,7 +17149,7 @@
         <v>202</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="C28" s="37"/>
       <c r="D28" s="37"/>
@@ -17167,7 +17181,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="C29" s="37"/>
       <c r="D29" s="37"/>
@@ -17199,7 +17213,7 @@
         <v>140</v>
       </c>
       <c r="B30" s="37" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="C30" s="37"/>
       <c r="D30" s="37"/>
@@ -17234,25 +17248,25 @@
         <v>5</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="D31" s="36" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="G31" s="36" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="H31" s="36" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="I31" s="36" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="J31" s="37"/>
       <c r="K31" s="37"/>
@@ -17312,43 +17326,43 @@
         <v>5</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="G33" s="36" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="H33" s="36" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="I33" s="36" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="J33" s="36" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="K33" s="36" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="L33" s="36" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="M33" s="36" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="N33" s="36" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="O33" s="36" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="P33" s="36"/>
       <c r="Q33" s="37"/>
@@ -17364,10 +17378,10 @@
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="37" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -17399,7 +17413,7 @@
         <v>282</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="C35" s="37"/>
       <c r="D35" s="37"/>
@@ -17431,7 +17445,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="37" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="C36" s="37"/>
       <c r="D36" s="37"/>
@@ -17460,10 +17474,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="37" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="B37" s="37" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="C37" s="37"/>
       <c r="D37" s="37"/>
@@ -17495,16 +17509,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="F38" s="37"/>
       <c r="G38" s="36"/>
@@ -17533,22 +17547,22 @@
         <v>95</v>
       </c>
       <c r="B39" s="37" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="C39" s="37" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="G39" s="36" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="H39" s="36"/>
       <c r="I39" s="36"/>
@@ -17572,25 +17586,25 @@
     </row>
     <row r="40" customFormat="false" ht="31.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="37" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="B40" s="37" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="G40" s="36" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="H40" s="36"/>
       <c r="I40" s="36"/>
@@ -17614,10 +17628,10 @@
     </row>
     <row r="41" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="37" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="B41" s="37" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="C41" s="37"/>
       <c r="D41" s="37"/>
@@ -17646,10 +17660,10 @@
     </row>
     <row r="42" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="37" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="B42" s="37" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="C42" s="37"/>
       <c r="D42" s="37"/>
@@ -17681,13 +17695,13 @@
         <v>123</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="D43" s="37" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="E43" s="37"/>
       <c r="F43" s="37"/>
@@ -17717,7 +17731,7 @@
         <v>228</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -17746,13 +17760,13 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="37" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="B45" s="37" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="C45" s="37" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="D45" s="37"/>
       <c r="E45" s="37"/>
@@ -17783,58 +17797,58 @@
         <v>456</v>
       </c>
       <c r="B46" s="37" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="C46" s="37" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="E46" s="37" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="G46" s="36" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="H46" s="36" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="I46" s="36" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="J46" s="36" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="K46" s="36" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="L46" s="36" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="M46" s="36" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="N46" s="36" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="O46" s="36" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="P46" s="36" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="Q46" s="36" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="R46" s="36" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="S46" s="36" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="T46" s="36"/>
       <c r="U46" s="36"/>

--- a/REFERENCE.xlsx
+++ b/REFERENCE.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="MATERIALS" sheetId="1" state="visible" r:id="rId2"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2471" uniqueCount="1632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2473" uniqueCount="1634">
   <si>
     <t xml:space="preserve">MATERIAL NAME</t>
   </si>
@@ -2530,6 +2530,12 @@
   </si>
   <si>
     <t xml:space="preserve">C162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOLDEN YELLOW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C163</t>
   </si>
   <si>
     <t xml:space="preserve">RAL COLOUR NAME</t>
@@ -6783,178 +6789,178 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="38" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="B1" s="38" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="39" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="39" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="B3" s="40" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="39" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="39" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="39" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="39" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="39" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="39" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="39" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="39" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="39" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="39" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="39" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="39" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="39" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="39" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="39" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="39" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="39" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="39" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="39" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="B22" s="40" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
     </row>
   </sheetData>
@@ -6986,99 +6992,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="41" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="C1" s="41" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="D1" s="41" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="E1" s="41" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="F1" s="41" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="G1" s="41" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="H1" s="41" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="I1" s="41" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="J1" s="41" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="K1" s="41" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="L1" s="41" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="M1" s="41" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="N1" s="41" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="O1" s="41" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="P1" s="41" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="Q1" s="41" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="R1" s="41" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="S1" s="41" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="T1" s="41" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="U1" s="41" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="V1" s="41" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="W1" s="41" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="X1" s="41" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="Y1" s="41" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="Z1" s="41" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="35" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="E2" s="35" t="s">
         <v>160</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="G2" s="36"/>
       <c r="H2" s="36"/>
@@ -7106,10 +7112,10 @@
         <v>143</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="D3" s="35"/>
       <c r="E3" s="35"/>
@@ -7140,64 +7146,64 @@
         <v>93</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="G4" s="36" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="H4" s="36" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="I4" s="36" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="K4" s="36" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="L4" s="36" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="M4" s="36" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="N4" s="36" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="O4" s="36" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="P4" s="36" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="Q4" s="36" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="R4" s="36" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="S4" s="36" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="T4" s="36" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="U4" s="43" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="V4" s="36"/>
       <c r="W4" s="42"/>
@@ -7210,22 +7216,22 @@
         <v>136</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="H5" s="36"/>
       <c r="I5" s="36"/>
@@ -7252,19 +7258,19 @@
         <v>23</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
@@ -7292,13 +7298,13 @@
         <v>85</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="E7" s="35"/>
       <c r="F7" s="35"/>
@@ -7325,16 +7331,16 @@
     </row>
     <row r="8" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="35" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="E8" s="35" t="s">
         <v>245</v>
@@ -7366,13 +7372,13 @@
         <v>28</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="E9" s="35"/>
       <c r="F9" s="35"/>
@@ -7399,25 +7405,25 @@
     </row>
     <row r="10" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="35" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="G10" s="36" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="H10" s="36"/>
       <c r="I10" s="36"/>
@@ -7444,10 +7450,10 @@
         <v>111</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
@@ -7475,28 +7481,28 @@
     </row>
     <row r="12" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="37" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="G12" s="36" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="H12" s="36" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="I12" s="36"/>
       <c r="J12" s="36"/>
@@ -7522,10 +7528,10 @@
         <v>42</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="37"/>
@@ -7556,16 +7562,16 @@
         <v>97</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="F14" s="37"/>
       <c r="G14" s="36"/>
@@ -7594,96 +7600,96 @@
         <v>6</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="G15" s="36" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="H15" s="36" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="I15" s="36" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="J15" s="36" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="K15" s="36" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="L15" s="36" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="M15" s="36" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="N15" s="36" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="O15" s="36" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="P15" s="36" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="Q15" s="36" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="R15" s="36" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="S15" s="36" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="T15" s="36" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="U15" s="36" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="V15" s="36" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="W15" s="36" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="X15" s="36" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="Y15" s="36" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="Z15" s="44" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="37" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="C16" s="37" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="F16" s="37"/>
       <c r="G16" s="36"/>
@@ -7709,13 +7715,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="37" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="37"/>
@@ -7746,7 +7752,7 @@
         <v>125</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="C18" s="37"/>
       <c r="D18" s="37"/>
@@ -7775,10 +7781,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="37" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
@@ -7810,7 +7816,7 @@
         <v>182</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="37"/>
@@ -7839,10 +7845,10 @@
     </row>
     <row r="21" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="37" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="37"/>
@@ -7874,28 +7880,28 @@
         <v>74</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="M22" s="36"/>
       <c r="N22" s="36"/>
@@ -7914,10 +7920,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="37" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="C23" s="37"/>
       <c r="D23" s="37"/>
@@ -7949,28 +7955,28 @@
         <v>99</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="G24" s="36" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="H24" s="36" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="J24" s="36"/>
       <c r="K24" s="36"/>
@@ -7995,7 +8001,7 @@
         <v>262</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="C25" s="37"/>
       <c r="D25" s="37"/>
@@ -8027,10 +8033,10 @@
         <v>46</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="D26" s="37"/>
       <c r="E26" s="37"/>
@@ -8058,10 +8064,10 @@
     </row>
     <row r="27" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="37" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="C27" s="37"/>
       <c r="D27" s="37"/>
@@ -8093,7 +8099,7 @@
         <v>202</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="C28" s="37"/>
       <c r="D28" s="37"/>
@@ -8125,7 +8131,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="C29" s="37"/>
       <c r="D29" s="37"/>
@@ -8157,7 +8163,7 @@
         <v>140</v>
       </c>
       <c r="B30" s="37" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="C30" s="37"/>
       <c r="D30" s="37"/>
@@ -8189,76 +8195,76 @@
         <v>8</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="C31" s="36" t="s">
+        <v>1610</v>
+      </c>
+      <c r="D31" s="36" t="s">
+        <v>1605</v>
+      </c>
+      <c r="E31" s="36" t="s">
+        <v>1611</v>
+      </c>
+      <c r="F31" s="37" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G31" s="37" t="s">
+        <v>1541</v>
+      </c>
+      <c r="H31" s="37" t="s">
         <v>1608</v>
       </c>
-      <c r="D31" s="36" t="s">
-        <v>1603</v>
-      </c>
-      <c r="E31" s="36" t="s">
-        <v>1609</v>
-      </c>
-      <c r="F31" s="37" t="s">
-        <v>1605</v>
-      </c>
-      <c r="G31" s="37" t="s">
-        <v>1539</v>
-      </c>
-      <c r="H31" s="37" t="s">
-        <v>1606</v>
-      </c>
       <c r="I31" s="37" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="J31" s="37" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="K31" s="37" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="L31" s="37" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="M31" s="37" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="N31" s="36" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="O31" s="37" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="P31" s="36" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="Q31" s="36" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="R31" s="36" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="S31" s="36" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="T31" s="36" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="U31" s="36" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="V31" s="36" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="W31" s="36" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="X31" s="36" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="Y31" s="36" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
@@ -8308,79 +8314,79 @@
         <v>3</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="J33" s="36" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="K33" s="36" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="L33" s="36" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="M33" s="36" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="N33" s="36" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="O33" s="36" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="P33" s="36" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="Q33" s="37" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="R33" s="37" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="S33" s="37" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="T33" s="36" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
       <c r="U33" s="36" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="V33" s="36" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="W33" s="36" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="X33" s="36" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="Y33" s="36" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="Z33" s="36" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
@@ -8395,10 +8401,10 @@
     </row>
     <row r="34" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="37" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -8430,7 +8436,7 @@
         <v>282</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="C35" s="37"/>
       <c r="D35" s="37"/>
@@ -8462,7 +8468,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="37" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="C36" s="37"/>
       <c r="D36" s="37"/>
@@ -8491,10 +8497,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="37" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B37" s="37" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="C37" s="37"/>
       <c r="D37" s="37"/>
@@ -8526,16 +8532,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="F38" s="37"/>
       <c r="G38" s="36"/>
@@ -8564,22 +8570,22 @@
         <v>95</v>
       </c>
       <c r="B39" s="37" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="C39" s="37" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="G39" s="36" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="H39" s="36"/>
       <c r="I39" s="36"/>
@@ -8603,25 +8609,25 @@
     </row>
     <row r="40" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="37" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="B40" s="37" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="G40" s="36" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="H40" s="36"/>
       <c r="I40" s="36"/>
@@ -8645,10 +8651,10 @@
     </row>
     <row r="41" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="37" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="B41" s="37" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="C41" s="37"/>
       <c r="D41" s="37"/>
@@ -8677,10 +8683,10 @@
     </row>
     <row r="42" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="37" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="B42" s="37" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="C42" s="37"/>
       <c r="D42" s="37"/>
@@ -8712,13 +8718,13 @@
         <v>123</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="D43" s="37" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="E43" s="37"/>
       <c r="F43" s="37"/>
@@ -8748,7 +8754,7 @@
         <v>228</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -8777,13 +8783,13 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="37" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="B45" s="37" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="C45" s="37" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="D45" s="37"/>
       <c r="E45" s="37"/>
@@ -8814,58 +8820,58 @@
         <v>456</v>
       </c>
       <c r="B46" s="37" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="C46" s="37" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="E46" s="37" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="G46" s="36" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="H46" s="36" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="I46" s="36" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="J46" s="36" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="K46" s="36" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="L46" s="36" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="M46" s="36" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="N46" s="36" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="O46" s="36" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="P46" s="36" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="Q46" s="36" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="R46" s="36" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="S46" s="36" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="T46" s="36"/>
       <c r="U46" s="36"/>
@@ -8900,10 +8906,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="46" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="B1" s="46" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10965,7 +10971,7 @@
     <tabColor rgb="FF2F5496"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B163"/>
+  <dimension ref="A1:B164"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
@@ -12274,6 +12280,14 @@
       </c>
       <c r="B163" s="13" t="s">
         <v>832</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="B164" s="13" t="s">
+        <v>834</v>
       </c>
     </row>
   </sheetData>
@@ -12302,890 +12316,890 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="14" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="14" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="14" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="14" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="14" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="14" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="14" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="14" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="14" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="14" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="14" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="14" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="14" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="14" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="14" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="16" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="14" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="14" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="14" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="14" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="14" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="14" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="14" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="14" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B67" s="14" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="14" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="14" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="B69" s="14" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="14" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="16" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="14" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="14" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="16" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="14" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="14" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="14" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="B77" s="14" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="14" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="16" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="B79" s="14" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="14" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="14" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="14" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="B82" s="14" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="16" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="B83" s="14" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="14" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="B84" s="14" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="14" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="B85" s="14" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="14" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="B86" s="14" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="14" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="B87" s="14" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="14" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="14" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="B89" s="14" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="14" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="B90" s="14" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="14" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="16" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="B92" s="14" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="14" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="B93" s="14" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="14" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B94" s="14" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="17" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="B95" s="14" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="16" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="B96" s="18" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="14" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="B97" s="18" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="14" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="B98" s="18" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="14" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B99" s="18" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="16" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="B100" s="18" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="14" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="B101" s="18" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="14" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="B102" s="18" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="16" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="B103" s="18" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="14" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="B104" s="18" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="14" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="B105" s="18" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="19" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="B106" s="19" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="19" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="B107" s="19" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="19" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="B108" s="19" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="19" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="B109" s="19" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="19" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="B110" s="19" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="19" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="B111" s="19" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
     </row>
   </sheetData>
@@ -13260,7 +13274,7 @@
         <v>93</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="F1" s="20" t="s">
         <v>43</v>
@@ -13275,7 +13289,7 @@
         <v>136</v>
       </c>
       <c r="J1" s="20" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="K1" s="20" t="s">
         <v>28</v>
@@ -13284,19 +13298,19 @@
         <v>111</v>
       </c>
       <c r="M1" s="20" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="N1" s="20" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="O1" s="20" t="s">
         <v>143</v>
       </c>
       <c r="P1" s="20" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="Q1" s="20" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="R1" s="21" t="s">
         <v>350</v>
@@ -13308,10 +13322,10 @@
         <v>97</v>
       </c>
       <c r="U1" s="21" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="V1" s="21" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="W1" s="21" t="s">
         <v>99</v>
@@ -13320,13 +13334,13 @@
         <v>128</v>
       </c>
       <c r="Y1" s="21" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="Z1" s="21" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="AA1" s="21" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="AB1" s="21" t="s">
         <v>182</v>
@@ -13341,7 +13355,7 @@
         <v>228</v>
       </c>
       <c r="AF1" s="21" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="AG1" s="21" t="s">
         <v>85</v>
@@ -13370,570 +13384,570 @@
     </row>
     <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="F2" s="10" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>1074</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>1075</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>1076</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>1077</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>1078</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>1079</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>1080</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>1081</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>1081</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>1082</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>1083</v>
+      </c>
+      <c r="R2" s="10" t="s">
+        <v>1072</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>1071</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="V2" s="10" t="s">
         <v>1072</v>
       </c>
-      <c r="H2" s="10" t="s">
-        <v>1073</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>1074</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>1075</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>1076</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>1077</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>1078</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>1079</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>1079</v>
-      </c>
-      <c r="P2" s="10" t="s">
-        <v>1080</v>
-      </c>
-      <c r="Q2" s="10" t="s">
-        <v>1081</v>
-      </c>
-      <c r="R2" s="10" t="s">
-        <v>1070</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>1082</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>1069</v>
-      </c>
-      <c r="V2" s="10" t="s">
-        <v>1070</v>
-      </c>
       <c r="W2" s="1" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>456</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="AB2" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="AD2" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="AE2" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="AG2" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="AN2" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="J3" s="10" t="s">
         <v>456</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="N3" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="O3" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="P3" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="Q3" s="10" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="R3" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="S3" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="U3" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="V3" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="X3" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="Y3" s="10" t="s">
+        <v>1072</v>
+      </c>
+      <c r="Z3" s="10" t="s">
+        <v>1072</v>
+      </c>
+      <c r="AA3" s="10" t="s">
+        <v>1072</v>
+      </c>
+      <c r="AB3" s="10" t="s">
         <v>1105</v>
       </c>
-      <c r="Y3" s="10" t="s">
-        <v>1070</v>
-      </c>
-      <c r="Z3" s="10" t="s">
-        <v>1070</v>
-      </c>
-      <c r="AA3" s="10" t="s">
-        <v>1070</v>
-      </c>
-      <c r="AB3" s="10" t="s">
-        <v>1103</v>
-      </c>
       <c r="AC3" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="AD3" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="AE3" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="AG3" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="AH3" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="AI3" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="AJ3" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="AK3" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="AL3" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="AM3" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="AN3" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>1109</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>1110</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>1111</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>1112</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>1107</v>
-      </c>
       <c r="H4" s="10" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="O4" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="P4" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="Q4" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="R4" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="S4" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="T4" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="U4" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="V4" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="Y4" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="Z4" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="AA4" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="AB4" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="AC4" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="AD4" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="AE4" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="AF4" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="AG4" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="AH4" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="AI4" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="AJ4" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="AK4" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="AL4" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="AM4" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="AN4" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="H5" s="10" t="s">
         <v>456</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="O5" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="Q5" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="S5" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="T5" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="U5" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="Y5" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="Z5" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="AA5" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="AB5" s="10"/>
       <c r="AC5" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="AD5" s="10"/>
       <c r="AF5" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="AH5" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="AK5" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="AL5" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="AM5" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="K6" s="10" t="s">
+        <v>1133</v>
+      </c>
+      <c r="L6" s="10" t="s">
         <v>1131</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>1129</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="O6" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="P6" s="22"/>
       <c r="Q6" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="T6" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="AF6" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="K7" s="10" t="s">
+        <v>1140</v>
+      </c>
+      <c r="L7" s="10" t="s">
         <v>1138</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>1136</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
@@ -13941,44 +13955,44 @@
       <c r="P7" s="22"/>
       <c r="Q7" s="22"/>
       <c r="W7" s="1" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="I8" s="22"/>
       <c r="J8" s="22"/>
       <c r="K8" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
@@ -13986,44 +14000,44 @@
       <c r="P8" s="22"/>
       <c r="Q8" s="22"/>
       <c r="W8" s="1" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="X8" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="I9" s="22"/>
       <c r="J9" s="22"/>
       <c r="K9" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="M9" s="22"/>
       <c r="N9" s="22"/>
@@ -14031,42 +14045,42 @@
       <c r="P9" s="22"/>
       <c r="Q9" s="22"/>
       <c r="W9" s="1" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="X9" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="E10" s="22"/>
       <c r="F10" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="I10" s="22"/>
       <c r="J10" s="22"/>
       <c r="K10" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="M10" s="22"/>
       <c r="N10" s="22"/>
@@ -14074,38 +14088,38 @@
       <c r="P10" s="22"/>
       <c r="Q10" s="22"/>
       <c r="W10" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="X10" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="E11" s="22"/>
       <c r="F11" s="22"/>
       <c r="G11" s="10" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="I11" s="22"/>
       <c r="J11" s="22"/>
       <c r="K11" s="22"/>
       <c r="L11" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="M11" s="22"/>
       <c r="N11" s="22"/>
@@ -14113,29 +14127,29 @@
       <c r="P11" s="22"/>
       <c r="Q11" s="22"/>
       <c r="W11" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="E12" s="22"/>
       <c r="F12" s="22"/>
       <c r="G12" s="10" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="I12" s="22"/>
       <c r="J12" s="22"/>
@@ -14147,29 +14161,29 @@
       <c r="P12" s="22"/>
       <c r="Q12" s="22"/>
       <c r="W12" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="E13" s="22"/>
       <c r="F13" s="22"/>
       <c r="G13" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="I13" s="22"/>
       <c r="J13" s="22"/>
@@ -14183,24 +14197,24 @@
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="E14" s="22"/>
       <c r="F14" s="22"/>
       <c r="G14" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="I14" s="22"/>
       <c r="J14" s="22"/>
@@ -14214,24 +14228,24 @@
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="E15" s="22"/>
       <c r="F15" s="22"/>
       <c r="G15" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="I15" s="22"/>
       <c r="J15" s="22"/>
@@ -14245,20 +14259,20 @@
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
       <c r="F16" s="22"/>
       <c r="G16" s="22"/>
       <c r="H16" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="I16" s="22"/>
       <c r="J16" s="22"/>
@@ -14272,20 +14286,20 @@
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="D17" s="22"/>
       <c r="E17" s="22"/>
       <c r="F17" s="22"/>
       <c r="G17" s="22"/>
       <c r="H17" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="I17" s="22"/>
       <c r="J17" s="22"/>
@@ -14299,13 +14313,13 @@
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="D18" s="22"/>
       <c r="E18" s="22"/>
@@ -14324,13 +14338,13 @@
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="D19" s="22"/>
       <c r="E19" s="22"/>
@@ -14349,13 +14363,13 @@
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="D20" s="22"/>
       <c r="E20" s="22"/>
@@ -14374,13 +14388,13 @@
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="D21" s="22"/>
       <c r="E21" s="22"/>
@@ -14399,13 +14413,13 @@
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="22"/>
@@ -14424,13 +14438,13 @@
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="D23" s="22"/>
       <c r="E23" s="22"/>
@@ -14449,13 +14463,13 @@
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="D24" s="22"/>
       <c r="E24" s="22"/>
@@ -14474,13 +14488,13 @@
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="D25" s="22"/>
       <c r="E25" s="22"/>
@@ -14499,13 +14513,13 @@
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="22"/>
@@ -14524,13 +14538,13 @@
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="D27" s="22"/>
       <c r="E27" s="22"/>
@@ -14549,13 +14563,13 @@
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="D28" s="22"/>
       <c r="E28" s="22"/>
@@ -14574,13 +14588,13 @@
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="D29" s="22"/>
       <c r="E29" s="22"/>
@@ -14599,13 +14613,13 @@
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="D30" s="22"/>
       <c r="E30" s="22"/>
@@ -14624,13 +14638,13 @@
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="D31" s="22"/>
       <c r="E31" s="22"/>
@@ -14649,13 +14663,13 @@
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="D32" s="22"/>
       <c r="E32" s="22"/>
@@ -14674,13 +14688,13 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="D33" s="22"/>
       <c r="E33" s="22"/>
@@ -14699,13 +14713,13 @@
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="B34" s="22" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="D34" s="22"/>
       <c r="E34" s="22"/>
@@ -14724,13 +14738,13 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="D35" s="22"/>
       <c r="E35" s="22"/>
@@ -14749,13 +14763,13 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="D36" s="22"/>
       <c r="E36" s="22"/>
@@ -14774,10 +14788,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="C37" s="22"/>
       <c r="D37" s="22"/>
@@ -14797,10 +14811,10 @@
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="C38" s="22"/>
       <c r="D38" s="22"/>
@@ -14820,10 +14834,10 @@
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="C39" s="22"/>
       <c r="D39" s="22"/>
@@ -14843,7 +14857,7 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B40" s="22"/>
       <c r="C40" s="22"/>
@@ -14864,7 +14878,7 @@
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="B41" s="22"/>
       <c r="C41" s="22"/>
@@ -14885,7 +14899,7 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
     </row>
   </sheetData>
@@ -14913,92 +14927,92 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="24" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="24" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15008,7 +15022,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
     </row>
   </sheetData>
@@ -15037,159 +15051,159 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B16" s="23" t="s">
         <v>1259</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>1257</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="B20" s="23"/>
     </row>
@@ -15221,31 +15235,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="E1" s="26"/>
     </row>
     <row r="2" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="E2" s="28"/>
     </row>
@@ -15254,13 +15268,13 @@
         <v>143</v>
       </c>
       <c r="B3" s="27" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C3" s="27" t="s">
         <v>1272</v>
       </c>
-      <c r="C3" s="27" t="s">
-        <v>1270</v>
-      </c>
       <c r="D3" s="27" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="E3" s="28"/>
     </row>
@@ -15269,43 +15283,43 @@
         <v>93</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="E4" s="28"/>
     </row>
     <row r="5" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="E5" s="28"/>
     </row>
     <row r="6" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="E6" s="28"/>
     </row>
@@ -15314,13 +15328,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="E7" s="28"/>
     </row>
@@ -15329,43 +15343,43 @@
         <v>28</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="E8" s="28"/>
     </row>
     <row r="9" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="B9" s="27" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D9" s="27" t="s">
         <v>1282</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>1283</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>1280</v>
       </c>
       <c r="E9" s="28"/>
     </row>
     <row r="10" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="E10" s="28"/>
     </row>
@@ -15374,73 +15388,73 @@
         <v>111</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="E11" s="28"/>
     </row>
     <row r="12" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="E12" s="28"/>
     </row>
     <row r="13" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="E13" s="28"/>
     </row>
     <row r="14" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="E14" s="28"/>
     </row>
     <row r="15" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="E15" s="28"/>
     </row>
@@ -15449,13 +15463,13 @@
         <v>97</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="E16" s="28"/>
     </row>
@@ -15464,13 +15478,13 @@
         <v>6</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="E17" s="28"/>
     </row>
@@ -15479,22 +15493,22 @@
         <v>43</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="E18" s="28"/>
     </row>
     <row r="19" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="C19" s="27"/>
       <c r="D19" s="27"/>
@@ -15502,16 +15516,16 @@
     </row>
     <row r="20" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="27" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D20" s="27" t="s">
         <v>1311</v>
-      </c>
-      <c r="B20" s="27" t="s">
-        <v>1307</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>1308</v>
-      </c>
-      <c r="D20" s="27" t="s">
-        <v>1309</v>
       </c>
       <c r="E20" s="28"/>
     </row>
@@ -15520,13 +15534,13 @@
         <v>125</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="E21" s="28"/>
     </row>
@@ -15535,43 +15549,43 @@
         <v>182</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="E22" s="28"/>
     </row>
     <row r="23" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="30" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B23" s="31" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D23" s="27" t="s">
         <v>1317</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>1318</v>
-      </c>
-      <c r="D23" s="27" t="s">
-        <v>1315</v>
       </c>
       <c r="E23" s="28"/>
     </row>
     <row r="24" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="E24" s="28"/>
     </row>
@@ -15580,67 +15594,67 @@
         <v>74</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="E25" s="28"/>
     </row>
     <row r="26" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="27" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="B26" s="30" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="E26" s="28"/>
     </row>
     <row r="27" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="B27" s="27" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D27" s="27" t="s">
         <v>1295</v>
-      </c>
-      <c r="C27" s="27" t="s">
-        <v>1292</v>
-      </c>
-      <c r="D27" s="27" t="s">
-        <v>1293</v>
       </c>
       <c r="E27" s="28"/>
     </row>
     <row r="28" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="27" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="E28" s="28"/>
     </row>
     <row r="29" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="C29" s="27"/>
       <c r="D29" s="27"/>
@@ -15651,7 +15665,7 @@
         <v>160</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="C30" s="27"/>
       <c r="D30" s="27"/>
@@ -15662,13 +15676,13 @@
         <v>99</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="E31" s="28"/>
     </row>
@@ -15677,7 +15691,7 @@
         <v>262</v>
       </c>
       <c r="B32" s="32" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
@@ -15685,16 +15699,16 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="26" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="E33" s="26"/>
     </row>
@@ -15703,7 +15717,7 @@
         <v>46</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="C34" s="26"/>
       <c r="D34" s="26"/>
@@ -15711,10 +15725,10 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="26" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="C35" s="26"/>
       <c r="D35" s="26"/>
@@ -15722,16 +15736,16 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="26" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="E36" s="26"/>
     </row>
@@ -15740,7 +15754,7 @@
         <v>202</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="C37" s="26"/>
       <c r="D37" s="26"/>
@@ -15751,7 +15765,7 @@
         <v>205</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="C38" s="26"/>
       <c r="D38" s="26"/>
@@ -15762,7 +15776,7 @@
         <v>140</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="C39" s="26"/>
       <c r="D39" s="26"/>
@@ -15770,25 +15784,25 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="26" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="E40" s="26"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="26" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="C41" s="26"/>
       <c r="D41" s="26"/>
@@ -15796,16 +15810,16 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="26" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="B42" s="26" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="D42" s="26" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="E42" s="26"/>
     </row>
@@ -15814,7 +15828,7 @@
         <v>350</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="C43" s="26"/>
       <c r="D43" s="26"/>
@@ -15822,34 +15836,34 @@
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="26" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="E44" s="26"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="26" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="C45" s="26" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D45" s="26" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E45" s="26" t="s">
         <v>1312</v>
-      </c>
-      <c r="D45" s="26" t="s">
-        <v>1313</v>
-      </c>
-      <c r="E45" s="26" t="s">
-        <v>1310</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15857,7 +15871,7 @@
         <v>133</v>
       </c>
       <c r="B46" s="26" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="C46" s="26"/>
       <c r="D46" s="26"/>
@@ -15865,10 +15879,10 @@
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="26" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="C47" s="26"/>
       <c r="D47" s="26"/>
@@ -15879,7 +15893,7 @@
         <v>128</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="C48" s="26"/>
       <c r="D48" s="26"/>
@@ -15890,67 +15904,67 @@
         <v>95</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="E49" s="26"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="26" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="D50" s="26" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="E50" s="26"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="26" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="D51" s="26" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="E51" s="26"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="26" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="B52" s="26" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C52" s="26" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="D52" s="26" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="E52" s="26"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="26" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="C53" s="26"/>
       <c r="D53" s="26"/>
@@ -15958,10 +15972,10 @@
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="26" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="C54" s="26"/>
       <c r="D54" s="26"/>
@@ -15969,10 +15983,10 @@
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="26" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="C55" s="26"/>
       <c r="D55" s="26"/>
@@ -15980,10 +15994,10 @@
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="26" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="C56" s="26"/>
       <c r="D56" s="26"/>
@@ -15991,10 +16005,10 @@
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="26" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C57" s="26"/>
       <c r="D57" s="26"/>
@@ -16002,10 +16016,10 @@
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="26" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C58" s="26"/>
       <c r="D58" s="26"/>
@@ -16016,10 +16030,10 @@
         <v>456</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="D59" s="26"/>
       <c r="E59" s="26"/>
@@ -16053,99 +16067,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="34" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="C1" s="34" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="D1" s="34" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="E1" s="34" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="F1" s="34" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="G1" s="34" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="H1" s="34" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="I1" s="34" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="J1" s="34" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="K1" s="34" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="L1" s="34" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="M1" s="34" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="N1" s="34" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="O1" s="34" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="P1" s="34" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="Q1" s="34" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="R1" s="34" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="S1" s="34" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="T1" s="34" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="U1" s="34" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="V1" s="34" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="W1" s="34" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="X1" s="34" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="Y1" s="34" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="Z1" s="34" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="35" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="E2" s="35" t="s">
         <v>160</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="G2" s="36"/>
       <c r="H2" s="36"/>
@@ -16173,7 +16187,7 @@
         <v>143</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="C3" s="35"/>
       <c r="D3" s="35"/>
@@ -16205,64 +16219,64 @@
         <v>93</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="G4" s="36" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="H4" s="36" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="I4" s="36" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="K4" s="36" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="L4" s="36" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="M4" s="36" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="N4" s="36" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="O4" s="36" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="P4" s="36" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="Q4" s="36" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="R4" s="36" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="S4" s="36" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="T4" s="36" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="U4" s="36" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="V4" s="36"/>
       <c r="W4" s="36"/>
@@ -16275,22 +16289,22 @@
         <v>136</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="H5" s="36"/>
       <c r="I5" s="36"/>
@@ -16320,16 +16334,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
@@ -16360,25 +16374,25 @@
         <v>5</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="G7" s="36" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="H7" s="36" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="I7" s="36" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="J7" s="36"/>
       <c r="K7" s="36"/>
@@ -16400,16 +16414,16 @@
     </row>
     <row r="8" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="35" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="E8" s="35" t="s">
         <v>245</v>
@@ -16441,13 +16455,13 @@
         <v>28</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="E9" s="35"/>
       <c r="F9" s="35"/>
@@ -16474,25 +16488,25 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="35" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="G10" s="36" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="H10" s="36"/>
       <c r="I10" s="36"/>
@@ -16519,10 +16533,10 @@
         <v>111</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
@@ -16550,28 +16564,28 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="37" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="G12" s="36" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="H12" s="36" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="I12" s="36"/>
       <c r="J12" s="36"/>
@@ -16597,10 +16611,10 @@
         <v>42</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="37"/>
@@ -16631,16 +16645,16 @@
         <v>97</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="F14" s="37"/>
       <c r="G14" s="36"/>
@@ -16672,25 +16686,25 @@
         <v>5</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="G15" s="36" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="H15" s="36" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="I15" s="36" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="J15" s="36"/>
       <c r="K15" s="36"/>
@@ -16712,19 +16726,19 @@
     </row>
     <row r="16" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="37" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="C16" s="37" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="F16" s="37"/>
       <c r="G16" s="36"/>
@@ -16750,13 +16764,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="37" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="37"/>
@@ -16787,7 +16801,7 @@
         <v>125</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="C18" s="37"/>
       <c r="D18" s="37"/>
@@ -16816,10 +16830,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="37" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
@@ -16851,7 +16865,7 @@
         <v>182</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="37"/>
@@ -16880,10 +16894,10 @@
     </row>
     <row r="21" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="37" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="37"/>
@@ -16918,43 +16932,43 @@
         <v>5</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="G22" s="36" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="H22" s="36" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="I22" s="36" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="J22" s="36" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="K22" s="36" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="L22" s="36" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="M22" s="36" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="N22" s="36" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="O22" s="36" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="P22" s="36"/>
       <c r="Q22" s="36"/>
@@ -16970,10 +16984,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="37" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="C23" s="37"/>
       <c r="D23" s="37"/>
@@ -17005,28 +17019,28 @@
         <v>99</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="G24" s="36" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="H24" s="36" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="J24" s="36"/>
       <c r="K24" s="36"/>
@@ -17051,7 +17065,7 @@
         <v>262</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="C25" s="37"/>
       <c r="D25" s="37"/>
@@ -17083,10 +17097,10 @@
         <v>46</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="D26" s="37"/>
       <c r="E26" s="37"/>
@@ -17114,10 +17128,10 @@
     </row>
     <row r="27" customFormat="false" ht="31.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="37" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="C27" s="37"/>
       <c r="D27" s="37"/>
@@ -17149,7 +17163,7 @@
         <v>202</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="C28" s="37"/>
       <c r="D28" s="37"/>
@@ -17181,7 +17195,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="C29" s="37"/>
       <c r="D29" s="37"/>
@@ -17213,7 +17227,7 @@
         <v>140</v>
       </c>
       <c r="B30" s="37" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="C30" s="37"/>
       <c r="D30" s="37"/>
@@ -17248,25 +17262,25 @@
         <v>5</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="D31" s="36" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="G31" s="36" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="H31" s="36" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="I31" s="36" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="J31" s="37"/>
       <c r="K31" s="37"/>
@@ -17326,43 +17340,43 @@
         <v>5</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="G33" s="36" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="H33" s="36" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="I33" s="36" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="J33" s="36" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="K33" s="36" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="L33" s="36" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="M33" s="36" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="N33" s="36" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="O33" s="36" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="P33" s="36"/>
       <c r="Q33" s="37"/>
@@ -17378,10 +17392,10 @@
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="37" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -17413,7 +17427,7 @@
         <v>282</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="C35" s="37"/>
       <c r="D35" s="37"/>
@@ -17445,7 +17459,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="37" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="C36" s="37"/>
       <c r="D36" s="37"/>
@@ -17474,10 +17488,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="37" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B37" s="37" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="C37" s="37"/>
       <c r="D37" s="37"/>
@@ -17509,16 +17523,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="F38" s="37"/>
       <c r="G38" s="36"/>
@@ -17547,22 +17561,22 @@
         <v>95</v>
       </c>
       <c r="B39" s="37" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="C39" s="37" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="G39" s="36" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="H39" s="36"/>
       <c r="I39" s="36"/>
@@ -17586,25 +17600,25 @@
     </row>
     <row r="40" customFormat="false" ht="31.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="37" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="B40" s="37" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="G40" s="36" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="H40" s="36"/>
       <c r="I40" s="36"/>
@@ -17628,10 +17642,10 @@
     </row>
     <row r="41" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="37" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="B41" s="37" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="C41" s="37"/>
       <c r="D41" s="37"/>
@@ -17660,10 +17674,10 @@
     </row>
     <row r="42" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="37" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="B42" s="37" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="C42" s="37"/>
       <c r="D42" s="37"/>
@@ -17695,13 +17709,13 @@
         <v>123</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="D43" s="37" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="E43" s="37"/>
       <c r="F43" s="37"/>
@@ -17731,7 +17745,7 @@
         <v>228</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -17760,13 +17774,13 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="37" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="B45" s="37" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="C45" s="37" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="D45" s="37"/>
       <c r="E45" s="37"/>
@@ -17797,58 +17811,58 @@
         <v>456</v>
       </c>
       <c r="B46" s="37" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="C46" s="37" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="E46" s="37" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="G46" s="36" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="H46" s="36" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="I46" s="36" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="J46" s="36" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="K46" s="36" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="L46" s="36" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="M46" s="36" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="N46" s="36" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="O46" s="36" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="P46" s="36" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="Q46" s="36" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="R46" s="36" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="S46" s="36" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="T46" s="36"/>
       <c r="U46" s="36"/>
